--- a/docs/downloads/2026-09-29/bursa-report-2026-09-29.xlsx
+++ b/docs/downloads/2026-09-29/bursa-report-2026-09-29.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-29" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-29'!$A$1:$M$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-29'!$A$1:$M$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="000CA30C"/>
+      <color rgb="00898781"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="000CA30C"/>
     </font>
   </fonts>
   <fills count="3">
@@ -83,7 +83,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -543,28 +543,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.58</v>
+        <v>0.18</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0526</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>23550100</v>
+        <v>59906100</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.98</v>
+        <v>0.11</v>
       </c>
       <c r="H2" t="n">
-        <v>68.72</v>
+        <v>21.7</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.547</v>
+        <v>0.266</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.493</v>
+        <v>0.481</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -588,39 +588,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>-0.0526</v>
+        <v>0.185</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>14855000</v>
+        <v>24749700</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.03</v>
+        <v>0.54</v>
       </c>
       <c r="H3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.83</v>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.266</v>
+        <v>0.15</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.481</v>
+        <v>0.118</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>7755100</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H4" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="K4" s="2" t="n">
         <v>0.19</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>5345300</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H4" t="n">
-        <v>79.09999999999999</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0.118</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,45 +678,2243 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E5" s="10" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="E5" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>689700</v>
+        <v>5971500</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.15</v>
+        <v>0.64</v>
       </c>
       <c r="H5" t="n">
-        <v>73.42</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.06</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.889</v>
+        <v>0.449</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.852</v>
+        <v>0.41</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0468</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>UNIPAC</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.0417</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>5306800</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5216</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NEXG</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-0.0476</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>4744600</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H7" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0213</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MTAG</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>4743800</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="H8" t="n">
+        <v>69.47</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>4349600</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H9" t="n">
+        <v>68.72</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-0.0241</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>3437400</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H10" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>L&amp;G</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>2952700</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>2951200</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>2710000</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>2496200</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H14" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>2341000</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H15" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0373</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>VERDANT</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>2320600</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H16" t="n">
+        <v>86.23999999999999</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0259</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>2207500</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H17" t="n">
+        <v>66.53</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>2018200</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H18" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>1954700</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>1788000</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H20" t="n">
+        <v>64.06999999999999</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.718</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>1768700</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H21" t="n">
+        <v>62.84</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>2.507</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-0.0165</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>1735000</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H22" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>7113</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>1726400</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H23" t="n">
+        <v>53.16</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>1718200</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H24" t="n">
+        <v>56.41</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5099</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CAPITALA</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>1609000</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H25" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-0.0106</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>1546000</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H26" t="n">
+        <v>68.43000000000001</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5318</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DXN</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.0106</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1506600</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>52.58</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0191</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CABNET</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0.1064</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1490500</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="H28" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1409300</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>71.27</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1397100</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H30" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1348400</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H31" t="n">
+        <v>45.51</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0251</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SFPTECH</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1173000</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>38.96</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1117400</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H33" t="n">
+        <v>67.45999999999999</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0358</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ICTZONE</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>-0.0204</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1090200</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H34" t="n">
+        <v>41.53</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1085800</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H35" t="n">
+        <v>59.29</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1080900</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H36" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>1.741</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>1.538</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GDB</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1042900</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="H37" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>985500</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>50.19</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLMT</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>882800</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H39" t="n">
+        <v>39.59</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>870800</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H40" t="n">
+        <v>49.83</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>2.346</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>856200</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H41" t="n">
+        <v>46.51</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>832000</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H42" t="n">
+        <v>65.81</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>2.778</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>2.637</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>771100</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H43" t="n">
+        <v>82.11</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>3.617</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>3.252</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>662000</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H44" t="n">
+        <v>62.85</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>650000</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H45" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>7241</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>NGGB</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>626700</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H46" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>616800</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H47" t="n">
+        <v>90.01000000000001</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>1.974</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>-0.0172</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>598100</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H48" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>1.161</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>576200</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H49" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>1.972</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>544800</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H50" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>520200</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>90.23</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>2.262</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>1.799</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>517000</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H52" t="n">
+        <v>54.06</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>500500</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H53" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>5.772</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>5.767</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>500400</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H54" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M5"/>
+  <autoFilter ref="A1:M54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-29/bursa-report-2026-09-29.xlsx
+++ b/docs/downloads/2026-09-29/bursa-report-2026-09-29.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-29" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-29'!$A$1:$M$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-29'!$A$1:$M$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.0526</v>
+        <v>-0.1053</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>59906100</v>
+        <v>202029000</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.11</v>
+        <v>0.36</v>
       </c>
       <c r="H2" t="n">
-        <v>21.7</v>
+        <v>20.85</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.266</v>
+        <v>0.265</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.481</v>
@@ -603,10 +603,10 @@
         <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>24749700</v>
+        <v>37474600</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.54</v>
+        <v>0.82</v>
       </c>
       <c r="H3" t="n">
         <v>77.83</v>
@@ -648,10 +648,10 @@
         <v>-0.0128</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>7755100</v>
+        <v>9667100</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="H4" t="n">
         <v>76.03</v>
@@ -678,28 +678,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
+        <v>0.575</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>5971500</v>
+        <v>7867600</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.64</v>
+        <v>0.33</v>
       </c>
       <c r="H5" t="n">
-        <v>57.06</v>
+        <v>66.09</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.449</v>
+        <v>0.549</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.41</v>
+        <v>0.494</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -732,16 +732,16 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.25</v>
+        <v>0.255</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.0417</v>
+        <v>0.0625</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5306800</v>
+        <v>7141400</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -761,39 +761,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>-0.0476</v>
+        <v>0.47</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4744600</v>
+        <v>6076900</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.29</v>
+        <v>0.65</v>
       </c>
       <c r="H7" t="n">
-        <v>56.45</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.22</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.286</v>
+        <v>0.45</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.277</v>
+        <v>0.41</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -806,28 +806,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0213</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MTAG</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0.0682</v>
+        <v>0.305</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-0.0317</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>4743800</v>
+        <v>5762700</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>10.21</v>
+        <v>0.36</v>
       </c>
       <c r="H8" t="n">
-        <v>69.47</v>
+        <v>58.44</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.211</v>
+        <v>0.286</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.216</v>
+        <v>0.278</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -851,39 +851,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0213</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>MTAG</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4349600</v>
+        <v>5664300</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.18</v>
+        <v>12.19</v>
       </c>
       <c r="H9" t="n">
-        <v>68.72</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.94</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.55</v>
+        <v>0.21</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.494</v>
+        <v>0.216</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -896,28 +896,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>-0.0241</v>
+        <v>0.29</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3437400</v>
+        <v>5625500</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.32</v>
+        <v>2.53</v>
       </c>
       <c r="H10" t="n">
-        <v>46.7</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.409</v>
+        <v>0.231</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.41</v>
+        <v>0.21</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -941,39 +941,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0</v>
+        <v>0.235</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-0.0408</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2952700</v>
+        <v>5314900</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.14</v>
+        <v>1.83</v>
       </c>
       <c r="H11" t="n">
-        <v>71.25</v>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.67</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.204</v>
+        <v>0.258</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.185</v>
+        <v>0.251</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -986,39 +986,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0.026</v>
+        <v>1.28</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2951200</v>
+        <v>5138400</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="H12" t="n">
-        <v>70.45</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.16</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.375</v>
+        <v>1.362</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.371</v>
+        <v>1.292</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1031,39 +1031,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0</v>
+        <v>0.39</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0.013</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2710000</v>
+        <v>5095600</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="H13" t="n">
-        <v>26.55</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.53</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.623</v>
+        <v>0.375</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.839</v>
+        <v>0.371</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1076,28 +1076,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>-0.0156</v>
+        <v>1.4</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2496200</v>
+        <v>5000000</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.22</v>
+        <v>7.07</v>
       </c>
       <c r="H14" t="n">
-        <v>38.14</v>
+        <v>42.64</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.36</v>
+        <v>1.439</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.292</v>
+        <v>1.431</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1121,28 +1121,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.41</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2341000</v>
+        <v>4920100</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="H15" t="n">
-        <v>48.12</v>
+        <v>51.13</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.773</v>
+        <v>0.409</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.774</v>
+        <v>0.411</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1166,28 +1166,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.295</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>0.0536</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2320600</v>
+        <v>4607900</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1.04</v>
+        <v>0.78</v>
       </c>
       <c r="H16" t="n">
-        <v>86.23999999999999</v>
+        <v>65.19</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.231</v>
+        <v>0.525</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.21</v>
+        <v>0.532</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1211,40 +1211,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0.018</v>
+        <v>0.13</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2207500</v>
+        <v>4603500</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H17" t="n">
-        <v>66.53</v>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>0.532</v>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
     </row>
@@ -1256,39 +1249,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.465</v>
+        <v>0.525</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2018200</v>
+        <v>4306800</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="H18" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.55</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.467</v>
+        <v>0.623</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.471</v>
+        <v>0.839</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1301,28 +1294,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.605</v>
+        <v>0.77</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>0.0083</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1954700</v>
+        <v>3759000</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H19" t="n">
-        <v>48.47</v>
+        <v>48.12</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
@@ -1330,10 +1323,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.607</v>
+        <v>0.773</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.605</v>
+        <v>0.774</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1346,28 +1339,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.245</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1788000</v>
+        <v>3581500</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="H20" t="n">
-        <v>64.06999999999999</v>
+        <v>31.98</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -1375,10 +1368,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.718</v>
+        <v>0.273</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.325</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1391,28 +1384,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2.85</v>
+        <v>0.605</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>0.0326</v>
+        <v>0.0083</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1768700</v>
+        <v>3258000</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="H21" t="n">
-        <v>62.84</v>
+        <v>48.47</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
@@ -1420,10 +1413,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.645</v>
+        <v>0.607</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2.507</v>
+        <v>0.605</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1436,39 +1429,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>-0.0165</v>
+        <v>0.225</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1735000</v>
+        <v>3198200</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.35</v>
+        <v>0.92</v>
       </c>
       <c r="H22" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.76000000000001</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.633</v>
+        <v>0.204</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.657</v>
+        <v>0.18</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1481,39 +1474,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5265</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>OASIS</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.74</v>
+        <v>0.1</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>0.0137</v>
+        <v>0.1111</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1726400</v>
+        <v>3092800</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.04</v>
+        <v>14.12</v>
       </c>
       <c r="H23" t="n">
-        <v>53.16</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.34</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.737</v>
+        <v>0.095</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.104</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1526,39 +1519,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0.0128</v>
+        <v>0.22</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1718200</v>
+        <v>3088300</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="H24" t="n">
-        <v>56.41</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.25</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.383</v>
+        <v>0.204</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.323</v>
+        <v>0.185</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1571,28 +1564,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.235</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1609000</v>
+        <v>2819700</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="H25" t="n">
-        <v>34.72</v>
+        <v>52.63</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
@@ -1600,10 +1593,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.274</v>
+        <v>0.232</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.325</v>
+        <v>0.233</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1616,28 +1609,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>-0.0106</v>
+        <v>0.805</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0.0255</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1546000</v>
+        <v>2740700</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="H26" t="n">
-        <v>68.43000000000001</v>
+        <v>65.14</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
@@ -1645,10 +1638,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.888</v>
+        <v>0.719</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.852</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1661,28 +1654,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.465</v>
+        <v>1.06</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.0106</v>
+        <v>-0.0185</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1506600</v>
+        <v>2639300</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="H27" t="n">
-        <v>52.58</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
@@ -1690,10 +1683,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.464</v>
+        <v>1.009</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.462</v>
+        <v>0.852</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1706,39 +1699,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0191</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CABNET</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0.1064</v>
+        <v>0.73</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1490500</v>
+        <v>2635200</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>9.25</v>
+        <v>0.06</v>
       </c>
       <c r="H28" t="n">
-        <v>69.84999999999999</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.13</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.221</v>
+        <v>0.736</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.216</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1751,39 +1744,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="E29" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1409300</v>
+        <v>2400900</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="H29" t="n">
-        <v>71.27</v>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.3</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.483</v>
+        <v>0.382</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.406</v>
+        <v>0.322</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1796,28 +1789,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0.0109</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1397100</v>
+        <v>2387300</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.41</v>
+        <v>0.16</v>
       </c>
       <c r="H30" t="n">
-        <v>47.5</v>
+        <v>71.27</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -1825,10 +1818,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.928</v>
+        <v>0.483</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.969</v>
+        <v>0.406</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1841,28 +1834,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>0</v>
+        <v>0.325</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1348400</v>
+        <v>2326400</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>1.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>45.51</v>
+        <v>35.32</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1870,10 +1863,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.261</v>
+        <v>0.384</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.266</v>
+        <v>0.371</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1886,28 +1879,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.255</v>
+        <v>2.85</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.02</v>
+        <v>0.0326</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1173000</v>
+        <v>2314500</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.1</v>
+        <v>0.31</v>
       </c>
       <c r="H32" t="n">
-        <v>38.96</v>
+        <v>62.84</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
@@ -1915,10 +1908,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.27</v>
+        <v>2.645</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.313</v>
+        <v>2.507</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1931,28 +1924,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>-0.0185</v>
+        <v>0.465</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1117400</v>
+        <v>2300200</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H33" t="n">
-        <v>67.45999999999999</v>
+        <v>48.8</v>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
@@ -1960,10 +1953,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.009</v>
+        <v>0.467</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.852</v>
+        <v>0.471</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1976,39 +1969,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.24</v>
+        <v>0.365</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>-0.0204</v>
+        <v>-0.0135</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1090200</v>
+        <v>2241000</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="H34" t="n">
-        <v>41.53</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.25</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.258</v>
+        <v>0.367</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.251</v>
+        <v>0.367</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2021,39 +2014,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0.0208</v>
+        <v>0.595</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1085800</v>
+        <v>2207800</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.06</v>
+        <v>0.45</v>
       </c>
       <c r="H35" t="n">
-        <v>59.29</v>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.5</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.233</v>
+        <v>0.633</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.233</v>
+        <v>0.657</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2066,39 +2059,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="E36" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1080900</v>
+        <v>1937600</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="H36" t="n">
-        <v>59.05</v>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.92</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.741</v>
+        <v>2.122</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1.538</v>
+        <v>2.064</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2111,28 +2104,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>0</v>
+        <v>4.32</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0.0385</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1042900</v>
+        <v>1880000</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.98</v>
+        <v>0.37</v>
       </c>
       <c r="H37" t="n">
-        <v>44.97</v>
+        <v>82.38</v>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
@@ -2140,10 +2133,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.431</v>
+        <v>3.618</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.452</v>
+        <v>3.252</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2156,39 +2149,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="E38" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>985500</v>
+        <v>1872400</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H38" t="n">
-        <v>50.19</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.05</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.741</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.8080000000000001</v>
+        <v>1.538</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2201,28 +2194,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.575</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E39" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>882800</v>
+        <v>1751800</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="H39" t="n">
-        <v>39.59</v>
+        <v>50.19</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2230,10 +2223,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.586</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.587</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2246,28 +2239,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>-0.0043</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>870800</v>
+        <v>1681900</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="H40" t="n">
-        <v>49.83</v>
+        <v>61.06</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -2275,10 +2268,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2.346</v>
+        <v>0.527</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2.245</v>
+        <v>0.48</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2291,28 +2284,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.25</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>856200</v>
+        <v>1678300</v>
       </c>
       <c r="G41" s="5" t="n">
         <v>0.15</v>
       </c>
       <c r="H41" t="n">
-        <v>46.51</v>
+        <v>36.09</v>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
@@ -2320,10 +2313,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.565</v>
+        <v>0.27</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>2.54</v>
+        <v>0.313</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2336,39 +2329,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>-0.0069</v>
+        <v>0.785</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0.0467</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>832000</v>
+        <v>1667600</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.06</v>
+        <v>0.29</v>
       </c>
       <c r="H42" t="n">
-        <v>65.81</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.4</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.778</v>
+        <v>0.766</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2.637</v>
+        <v>0.753</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2381,28 +2374,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>4.3</v>
+        <v>0.93</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>0.0337</v>
+        <v>0.0109</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>771100</v>
+        <v>1648000</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.15</v>
+        <v>0.48</v>
       </c>
       <c r="H43" t="n">
-        <v>82.11</v>
+        <v>47.5</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
@@ -2410,10 +2403,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>3.617</v>
+        <v>0.928</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>3.252</v>
+        <v>0.969</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2426,28 +2419,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0.0208</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>662000</v>
+        <v>1608100</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="H44" t="n">
-        <v>62.85</v>
+        <v>70.83</v>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
@@ -2455,10 +2448,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.888</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.616</v>
+        <v>0.852</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2471,39 +2464,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.63</v>
+        <v>2.55</v>
       </c>
       <c r="E45" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>650000</v>
+        <v>1607900</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.67</v>
+        <v>0.27</v>
       </c>
       <c r="H45" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.43</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.631</v>
+        <v>2.567</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.637</v>
+        <v>2.54</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2516,39 +2509,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0.0139</v>
+        <v>0.28</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>-0.0508</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>626700</v>
+        <v>1588800</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="H46" t="n">
-        <v>60.02</v>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>60.65</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.71</v>
+        <v>0.265</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.713</v>
+        <v>0.222</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2561,28 +2554,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0.021</v>
+        <v>0.47</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>616800</v>
+        <v>1528600</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.27</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>90.01000000000001</v>
+        <v>60.57</v>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
@@ -2590,10 +2583,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.315</v>
+        <v>0.464</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1.974</v>
+        <v>0.462</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2606,28 +2599,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0191</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>CABNET</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>-0.0172</v>
+        <v>0.255</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0.0851</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>598100</v>
+        <v>1522600</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>48.59</v>
+        <v>68.41</v>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
@@ -2635,10 +2628,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.161</v>
+        <v>0.221</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1.102</v>
+        <v>0.216</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2651,40 +2644,33 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1.95</v>
+        <v>0.48</v>
       </c>
       <c r="E49" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>576200</v>
+        <v>1465800</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H49" t="n">
-        <v>45.43</v>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="K49" s="2" t="n">
-        <v>1.972</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
     </row>
@@ -2696,39 +2682,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>2.54</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0039</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>544800</v>
+        <v>1419100</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>46.45</v>
-      </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.66</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.5639999999999999</v>
+        <v>2.583</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.594</v>
+        <v>2.448</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2741,28 +2727,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>SUNSURIA</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2.97</v>
+        <v>0.295</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>0.0241</v>
+        <v>0.0351</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>520200</v>
+        <v>1408200</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.2</v>
+        <v>20.78</v>
       </c>
       <c r="H51" t="n">
-        <v>90.23</v>
+        <v>61.9</v>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
@@ -2770,10 +2756,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.262</v>
+        <v>0.279</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1.799</v>
+        <v>0.282</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2786,28 +2772,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>-0.0071</v>
+        <v>0.74</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>517000</v>
+        <v>1397900</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.42</v>
       </c>
       <c r="H52" t="n">
-        <v>54.06</v>
+        <v>63.48</v>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
@@ -2815,10 +2801,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.664</v>
+        <v>0.713</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2831,39 +2817,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>5.57</v>
+        <v>0.425</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>-0.0071</v>
+        <v>-0.0116</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>500500</v>
+        <v>1388400</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.17</v>
+        <v>1.31</v>
       </c>
       <c r="H53" t="n">
-        <v>44.28</v>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.37</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>5.772</v>
+        <v>0.431</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>5.767</v>
+        <v>0.452</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2876,45 +2862,1710 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0.0234</v>
+        <v>0.26</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>500400</v>
+        <v>1348400</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.08</v>
+        <v>1.73</v>
       </c>
       <c r="H54" t="n">
-        <v>95.56999999999999</v>
-      </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.51</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.92</v>
+        <v>0.261</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.746</v>
+        <v>0.266</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>1325200</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H55" t="n">
+        <v>47.09</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>1306100</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H56" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>10.309</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>-0.0172</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>1303100</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H57" t="n">
+        <v>62.01</v>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>2.775</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>2.637</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>5078</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>M&amp;G</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>1273400</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>54.01</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>VELESTO</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>-0.0233</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>1178800</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H59" t="n">
+        <v>27.87</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>-0.0042</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>1106600</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H60" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>4.838</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>4.954</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>1068100</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H61" t="n">
+        <v>62.85</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0397</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>5ER</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>1060900</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H62" t="n">
+        <v>37.51</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>-0.0122</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>984300</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H63" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>4.755</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>4.524</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>979300</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H64" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>2.346</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>2.245</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>906500</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H65" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CLMT</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>896000</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H66" t="n">
+        <v>39.59</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E67" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>855100</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H67" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>1.972</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>785900</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H68" t="n">
+        <v>89.68000000000001</v>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>2.312</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>1.973</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>764500</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H69" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>9059</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>TSH</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>751600</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H70" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>1.387</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0.0241</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>736600</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H71" t="n">
+        <v>90.23</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>2.262</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>1.799</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>731500</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H72" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>5.772</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>5.767</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>-0.0163</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>727800</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H73" t="n">
+        <v>53.83</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>7.811</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>7.737</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>713200</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H74" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>2.484</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>2.139</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>692200</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H75" t="n">
+        <v>59.77</v>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>2.286</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>-0.0086</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>689500</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H76" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>1.162</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>683400</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H77" t="n">
+        <v>40.38</v>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>1.329</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>678400</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H78" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>673000</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H79" t="n">
+        <v>54.06</v>
+      </c>
+      <c r="I79" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>650000</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H80" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>632200</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H81" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>2.073</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>622900</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H82" t="n">
+        <v>46.13</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>610900</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H83" t="n">
+        <v>65.67</v>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>9.573</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>9.106999999999999</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>-0.0221</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>568300</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H84" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>2.108</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>-0.0171</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>551800</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H85" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>3.599</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>3.699</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>548800</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H86" t="n">
+        <v>72.55</v>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>531400</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H87" t="n">
+        <v>78.31999999999999</v>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>3.607</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>2.415</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>529700</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H88" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>13.185</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>519000</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H89" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>1.181</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>512300</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H90" t="n">
+        <v>39.66</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="7" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>511800</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H91" t="n">
+        <v>84.76000000000001</v>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M54"/>
+  <autoFilter ref="A1:M91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-29/bursa-report-2026-09-29.xlsx
+++ b/docs/downloads/2026-09-29/bursa-report-2026-09-29.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-29" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-29'!$A$1:$M$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-29'!$A$1:$M$117</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="000CA30C"/>
+      <color rgb="00898781"/>
     </font>
   </fonts>
   <fills count="3">
@@ -83,7 +83,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>-0.1053</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>202029000</v>
+        <v>229662500</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.36</v>
+        <v>0.41</v>
       </c>
       <c r="H2" t="n">
         <v>20.85</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.185</v>
+        <v>0.19</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>37474600</v>
+        <v>50182100</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.82</v>
+        <v>1.09</v>
       </c>
       <c r="H3" t="n">
-        <v>77.83</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.15</v>
+        <v>0.151</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.118</v>
@@ -648,10 +648,10 @@
         <v>-0.0128</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>9667100</v>
+        <v>13031600</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="H4" t="n">
         <v>76.03</v>
@@ -693,10 +693,10 @@
         <v>-0.0086</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>7867600</v>
+        <v>12414100</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.33</v>
+        <v>0.52</v>
       </c>
       <c r="H5" t="n">
         <v>66.09</v>
@@ -723,33 +723,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.255</v>
+        <v>1.28</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.0625</v>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>7141400</v>
+        <v>7626300</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.47</v>
+        <v>0.67</v>
+      </c>
+      <c r="H6" t="n">
+        <v>40.16</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="2" t="n"/>
+      <c r="J6" s="2" t="n">
+        <v>1.362</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1.292</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
     </row>
@@ -761,40 +768,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>7211200</v>
+      </c>
+      <c r="G7" s="5" t="n">
         <v>0.47</v>
       </c>
-      <c r="E7" s="10" t="n">
-        <v>0.0108</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>6076900</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H7" t="n">
-        <v>58.22</v>
-      </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>0.41</v>
-      </c>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
     </row>
@@ -806,39 +806,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>-0.0317</v>
+        <v>0.47</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5762700</v>
+        <v>6295500</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.36</v>
+        <v>0.67</v>
       </c>
       <c r="H8" t="n">
-        <v>58.44</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.22</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.286</v>
+        <v>0.45</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.278</v>
+        <v>0.41</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -851,28 +851,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0213</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MTAG</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0.0455</v>
+        <v>0.29</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5664300</v>
+        <v>6042600</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>12.19</v>
+        <v>2.71</v>
       </c>
       <c r="H9" t="n">
-        <v>66.94</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="K9" s="2" t="n">
         <v>0.21</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>0.216</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -896,40 +896,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0.0357</v>
+        <v>0.125</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-0.0385</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5625500</v>
+        <v>5959900</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="H10" t="n">
-        <v>85.54000000000001</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.21</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
     </row>
@@ -941,39 +934,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.235</v>
+        <v>0.305</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.0408</v>
+        <v>-0.0317</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5314900</v>
+        <v>5959700</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.83</v>
+        <v>0.37</v>
       </c>
       <c r="H11" t="n">
-        <v>39.67</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.44</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.258</v>
+        <v>0.286</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.251</v>
+        <v>0.278</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -986,39 +979,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0213</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>MTAG</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1.28</v>
+        <v>0.225</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>0</v>
+        <v>0.0227</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5138400</v>
+        <v>5847600</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.45</v>
+        <v>12.58</v>
       </c>
       <c r="H12" t="n">
-        <v>40.16</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.95</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.362</v>
+        <v>0.21</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1.292</v>
+        <v>0.216</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1031,39 +1024,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0.013</v>
+        <v>0.52</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5095600</v>
+        <v>5730500</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.52</v>
+        <v>0.15</v>
       </c>
       <c r="H13" t="n">
-        <v>67.53</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.16</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.375</v>
+        <v>0.623</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.371</v>
+        <v>0.839</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1076,39 +1069,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PTT</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1.4</v>
+        <v>0.39</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5000000</v>
+        <v>5663800</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>7.07</v>
+        <v>0.58</v>
       </c>
       <c r="H14" t="n">
-        <v>42.64</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.53</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.439</v>
+        <v>0.375</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.431</v>
+        <v>0.371</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1121,39 +1114,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.41</v>
+        <v>0.235</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-0.012</v>
+        <v>-0.0408</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4920100</v>
+        <v>5643400</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.45</v>
+        <v>1.95</v>
       </c>
       <c r="H15" t="n">
-        <v>51.13</v>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.67</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.409</v>
+        <v>0.258</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.411</v>
+        <v>0.251</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1166,28 +1159,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>0.009000000000000001</v>
+        <v>2.9</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0.0507</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>4607900</v>
+        <v>5548700</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="H16" t="n">
-        <v>65.19</v>
+        <v>64.62</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -1195,10 +1188,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.525</v>
+        <v>2.65</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.532</v>
+        <v>2.508</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1211,33 +1204,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.13</v>
+        <v>0.77</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>0</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4603500</v>
+        <v>5352400</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
+        <v>0.43</v>
+      </c>
+      <c r="H17" t="n">
+        <v>48.12</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.774</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
     </row>
@@ -1249,28 +1249,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.525</v>
+        <v>1.42</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>0</v>
+        <v>0.0143</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4306800</v>
+        <v>5043500</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.11</v>
+        <v>7.13</v>
       </c>
       <c r="H18" t="n">
-        <v>26.55</v>
+        <v>46.47</v>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.623</v>
+        <v>1.441</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.839</v>
+        <v>1.432</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1294,28 +1294,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0.018</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3759000</v>
+        <v>4940000</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.3</v>
+        <v>0.84</v>
       </c>
       <c r="H19" t="n">
-        <v>48.12</v>
+        <v>66.53</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.773</v>
+        <v>0.526</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.774</v>
+        <v>0.532</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1339,28 +1339,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>0</v>
+        <v>0.41</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3581500</v>
+        <v>4920200</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.13</v>
+        <v>0.45</v>
       </c>
       <c r="H20" t="n">
-        <v>31.98</v>
+        <v>51.13</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.273</v>
+        <v>0.409</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.325</v>
+        <v>0.411</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1384,28 +1384,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0.0083</v>
+        <v>4.37</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0.0505</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3258000</v>
+        <v>4031000</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.33</v>
+        <v>0.78</v>
       </c>
       <c r="H21" t="n">
-        <v>48.47</v>
+        <v>83.02</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.607</v>
+        <v>3.623</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.605</v>
+        <v>3.253</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1429,28 +1429,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0370</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>XPB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.225</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>0.04650000000000001</v>
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3198200</v>
+        <v>3913000</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.92</v>
+        <v>0.27</v>
       </c>
       <c r="H22" t="n">
-        <v>67.76000000000001</v>
+        <v>71.27</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.204</v>
+        <v>0.483</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.18</v>
+        <v>0.406</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1474,39 +1474,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OASIS</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.1</v>
+        <v>0.305</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>0.1111</v>
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3092800</v>
+        <v>3869300</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>14.12</v>
+        <v>0.21</v>
       </c>
       <c r="H23" t="n">
-        <v>52.34</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.01</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.095</v>
+        <v>0.304</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.104</v>
+        <v>0.291</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1519,28 +1519,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E24" s="8" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="E24" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3088300</v>
+        <v>3743900</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H24" t="n">
-        <v>71.25</v>
+        <v>31.98</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.204</v>
+        <v>0.273</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.185</v>
+        <v>0.325</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1564,28 +1564,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-0.0208</v>
+        <v>0.225</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2819700</v>
+        <v>3612600</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.16</v>
+        <v>1.04</v>
       </c>
       <c r="H25" t="n">
-        <v>52.63</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.232</v>
+        <v>0.204</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.233</v>
+        <v>0.18</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1609,28 +1609,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0.0255</v>
+        <v>1.79</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2740700</v>
+        <v>3594900</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="H26" t="n">
-        <v>65.14</v>
+        <v>58.11</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.719</v>
+        <v>1.74</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>1.538</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1654,39 +1654,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>-0.0185</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2639300</v>
+        <v>3540800</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="H27" t="n">
-        <v>67.45999999999999</v>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.19</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.009</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.852</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1699,39 +1699,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>0</v>
+        <v>0.0191</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2635200</v>
+        <v>3488100</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.06</v>
+        <v>0.34</v>
       </c>
       <c r="H28" t="n">
-        <v>51.13</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.61</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.736</v>
+        <v>0.719</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1744,39 +1744,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.39</v>
+        <v>0.605</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>0</v>
+        <v>0.0083</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2400900</v>
+        <v>3258000</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.11</v>
+        <v>0.33</v>
       </c>
       <c r="H29" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.47</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.382</v>
+        <v>0.607</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.322</v>
+        <v>0.605</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1789,28 +1789,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E30" s="8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E30" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2387300</v>
+        <v>3250700</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="H30" t="n">
-        <v>71.27</v>
+        <v>56.39</v>
       </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.483</v>
+        <v>0.233</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.406</v>
+        <v>0.233</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1834,39 +1834,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0.0156</v>
+        <v>0.365</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2326400</v>
+        <v>3201100</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.53</v>
       </c>
       <c r="H31" t="n">
-        <v>35.32</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.25</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.384</v>
+        <v>0.367</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.371</v>
+        <v>0.367</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1879,39 +1879,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0.0326</v>
+        <v>0.725</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2314500</v>
+        <v>3189400</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.31</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>62.84</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.04</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2.645</v>
+        <v>0.735</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>2.507</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1924,28 +1924,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E33" s="8" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2300200</v>
+        <v>3088300</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="H33" t="n">
-        <v>48.8</v>
+        <v>71.25</v>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.467</v>
+        <v>0.204</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.471</v>
+        <v>0.185</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1969,28 +1969,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.365</v>
+        <v>0.865</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>-0.0135</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2241000</v>
+        <v>2922500</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.37</v>
+        <v>0.16</v>
       </c>
       <c r="H34" t="n">
-        <v>48.25</v>
+        <v>47.09</v>
       </c>
       <c r="I34" s="9" t="inlineStr">
         <is>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.367</v>
+        <v>0.868</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.367</v>
+        <v>0.87</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2014,39 +2014,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>-0.0165</v>
+        <v>1.08</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2207800</v>
+        <v>2860900</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.45</v>
+        <v>0.24</v>
       </c>
       <c r="H35" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.13</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.633</v>
+        <v>1.011</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.657</v>
+        <v>0.853</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2070,14 +2070,14 @@
       <c r="D36" s="2" t="n">
         <v>2.08</v>
       </c>
-      <c r="E36" s="8" t="n">
+      <c r="E36" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1937600</v>
+        <v>2835700</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="H36" t="n">
         <v>45.92</v>
@@ -2104,28 +2104,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0.0385</v>
+        <v>0.3</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1880000</v>
+        <v>2825100</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="H37" t="n">
-        <v>82.38</v>
+        <v>68.55</v>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>3.618</v>
+        <v>0.277</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>3.252</v>
+        <v>0.27</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2149,39 +2149,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E38" s="8" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E38" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1872400</v>
+        <v>2726600</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="H38" t="n">
-        <v>59.05</v>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.3</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.741</v>
+        <v>0.382</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1.538</v>
+        <v>0.322</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2194,39 +2194,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1751800</v>
+        <v>2580300</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="H39" t="n">
-        <v>50.19</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.68</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.328</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.8080000000000001</v>
+        <v>1.438</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2239,28 +2239,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0.009000000000000001</v>
+        <v>2.84</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>-0.0241</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1681900</v>
+        <v>2553100</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="H40" t="n">
-        <v>61.06</v>
+        <v>59.71</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.527</v>
+        <v>2.773</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.48</v>
+        <v>2.636</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2284,28 +2284,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.25</v>
+        <v>0.47</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>0</v>
+        <v>0.0108</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1678300</v>
+        <v>2415600</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="H41" t="n">
-        <v>36.09</v>
+        <v>50.83</v>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.27</v>
+        <v>0.468</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.313</v>
+        <v>0.471</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2329,28 +2329,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>0.0467</v>
+        <v>0.325</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1667600</v>
+        <v>2333800</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.29</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>62.4</v>
+        <v>35.32</v>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.766</v>
+        <v>0.384</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.753</v>
+        <v>0.371</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2374,28 +2374,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>SUNSURIA</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>0.0109</v>
+        <v>0.28</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1648000</v>
+        <v>2331300</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.48</v>
+        <v>34.41</v>
       </c>
       <c r="H43" t="n">
-        <v>47.5</v>
+        <v>51.15</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.928</v>
+        <v>0.278</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.969</v>
+        <v>0.282</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2419,28 +2419,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>-0.0053</v>
+        <v>-0.0059</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1608100</v>
+        <v>2330100</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="H44" t="n">
-        <v>70.83</v>
+        <v>42.66</v>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.888</v>
+        <v>10.168</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.852</v>
+        <v>10.309</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2464,28 +2464,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>2.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E45" s="8" t="n">
-        <v>0</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1607900</v>
+        <v>2273600</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.27</v>
+        <v>0.16</v>
       </c>
       <c r="H45" t="n">
-        <v>48.43</v>
+        <v>61.06</v>
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
@@ -2493,10 +2493,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.567</v>
+        <v>0.527</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2.54</v>
+        <v>0.48</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2509,28 +2509,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.28</v>
+        <v>0.595</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>-0.0508</v>
+        <v>-0.0165</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1588800</v>
+        <v>2252100</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.18</v>
+        <v>0.45</v>
       </c>
       <c r="H46" t="n">
-        <v>60.65</v>
+        <v>34.5</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.265</v>
+        <v>0.633</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.222</v>
+        <v>0.657</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2554,39 +2554,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>0</v>
+        <v>2.52</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1528600</v>
+        <v>2181700</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="H47" t="n">
-        <v>60.57</v>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.27</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.464</v>
+        <v>2.581</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.462</v>
+        <v>2.447</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2599,39 +2599,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0191</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CABNET</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0.0851</v>
+        <v>0.275</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>-0.0678</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1522600</v>
+        <v>2166000</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>9.449999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="H48" t="n">
-        <v>68.41</v>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.4</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.221</v>
+        <v>0.265</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.216</v>
+        <v>0.222</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2644,33 +2644,40 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>0</v>
+        <v>0.21</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1465800</v>
+        <v>2164700</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.39</v>
+      </c>
+      <c r="H49" t="n">
+        <v>47.8</v>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J49" s="2" t="n"/>
-      <c r="K49" s="2" t="n"/>
+      <c r="J49" s="2" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0.212</v>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
     </row>
@@ -2682,28 +2689,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>-0.0039</v>
+        <v>0.785</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>0.0467</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1419100</v>
+        <v>2152700</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="H50" t="n">
-        <v>48.66</v>
+        <v>62.4</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2711,10 +2718,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.583</v>
+        <v>0.766</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2.448</v>
+        <v>0.753</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2727,28 +2734,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SUNSURIA</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>0.0351</v>
+        <v>0.925</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0.0054</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1408200</v>
+        <v>2136900</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>20.78</v>
+        <v>0.62</v>
       </c>
       <c r="H51" t="n">
-        <v>61.9</v>
+        <v>45.73</v>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
@@ -2756,10 +2763,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.279</v>
+        <v>0.927</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.282</v>
+        <v>0.969</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2772,39 +2779,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>0.0278</v>
+        <v>4.76</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-0.0063</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1397900</v>
+        <v>2061300</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.42</v>
+        <v>0.12</v>
       </c>
       <c r="H52" t="n">
-        <v>63.48</v>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.67</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.711</v>
+        <v>4.837</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.713</v>
+        <v>4.953</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2817,28 +2824,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.425</v>
+        <v>7.83</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>-0.0116</v>
+        <v>-0.02</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1388400</v>
+        <v>2000800</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>1.31</v>
+        <v>0.16</v>
       </c>
       <c r="H53" t="n">
-        <v>41.37</v>
+        <v>52.27</v>
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
@@ -2846,10 +2853,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.431</v>
+        <v>7.808</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.452</v>
+        <v>7.736</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2862,39 +2869,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>0</v>
+        <v>2.32</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1348400</v>
+        <v>1843300</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>1.73</v>
+        <v>0.11</v>
       </c>
       <c r="H54" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.09</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.261</v>
+        <v>2.345</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.266</v>
+        <v>2.245</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2907,28 +2914,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.25</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1325200</v>
+        <v>1821300</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="H55" t="n">
-        <v>47.09</v>
+        <v>36.09</v>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
@@ -2936,10 +2943,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.868</v>
+        <v>0.27</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.87</v>
+        <v>0.313</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2952,40 +2959,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>BPROP</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>-0.0039</v>
+        <v>0.245</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1306100</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H56" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="K56" s="2" t="n">
-        <v>10.309</v>
-      </c>
+        <v>1809500</v>
+      </c>
+      <c r="G56" s="5" t="n"/>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
     </row>
@@ -2997,39 +2995,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>2.86</v>
+        <v>4.84</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>-0.0172</v>
+        <v>-0.0143</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1303100</v>
+        <v>1804900</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H57" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.69</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2.775</v>
+        <v>4.754</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2.637</v>
+        <v>4.524</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3042,39 +3040,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E58" s="8" t="n">
-        <v>0</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1273400</v>
+        <v>1739800</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="H58" t="n">
-        <v>54.01</v>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.83</v>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.304</v>
+        <v>0.888</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.291</v>
+        <v>0.852</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3096,19 +3094,19 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>-0.0233</v>
+        <v>0.215</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1178800</v>
+        <v>1726700</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>27.87</v>
+        <v>29.99</v>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
@@ -3132,39 +3130,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>4.77</v>
+        <v>2.45</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>-0.0042</v>
+        <v>-0.0239</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1106600</v>
+        <v>1677700</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="H60" t="n">
-        <v>37.64</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.43</v>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>4.838</v>
+        <v>2.441</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>4.954</v>
+        <v>2.285</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3177,28 +3175,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0191</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>CABNET</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>0.0208</v>
+        <v>0.26</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0.1064</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1068100</v>
+        <v>1661000</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.18</v>
+        <v>10.31</v>
       </c>
       <c r="H61" t="n">
-        <v>62.85</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
@@ -3206,10 +3204,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.221</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.616</v>
+        <v>0.216</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3222,39 +3220,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E62" s="8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E62" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1060900</v>
+        <v>1649500</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>1.05</v>
+        <v>0.28</v>
       </c>
       <c r="H62" t="n">
-        <v>37.51</v>
-      </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.43</v>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.205</v>
+        <v>2.567</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.214</v>
+        <v>2.54</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3267,39 +3265,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>-0.0122</v>
+        <v>1.32</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>984300</v>
+        <v>1585400</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.05</v>
+        <v>0.27</v>
       </c>
       <c r="H63" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>95.65000000000001</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>4.755</v>
+        <v>0.921</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>4.524</v>
+        <v>0.746</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3312,28 +3310,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E64" s="8" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E64" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>979300</v>
+        <v>1557800</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.06</v>
+        <v>0.57</v>
       </c>
       <c r="H64" t="n">
-        <v>50.6</v>
+        <v>60.57</v>
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
@@ -3341,10 +3339,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2.346</v>
+        <v>0.464</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2.245</v>
+        <v>0.462</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3357,28 +3355,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0.0234</v>
+        <v>0.425</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>-0.0116</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>906500</v>
+        <v>1546300</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.15</v>
+        <v>1.46</v>
       </c>
       <c r="H65" t="n">
-        <v>95.56999999999999</v>
+        <v>41.37</v>
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
@@ -3386,10 +3384,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.92</v>
+        <v>0.431</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.746</v>
+        <v>0.452</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3402,28 +3400,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>0</v>
+        <v>1.54</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>896000</v>
+        <v>1535800</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.23</v>
+        <v>0.52</v>
       </c>
       <c r="H66" t="n">
-        <v>39.59</v>
+        <v>38.15</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3431,10 +3429,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.586</v>
+        <v>1.579</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.587</v>
+        <v>1.644</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3447,40 +3445,33 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="E67" s="8" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E67" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>855100</v>
+        <v>1475800</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H67" t="n">
-        <v>45.43</v>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="K67" s="2" t="n">
-        <v>1.972</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n"/>
+      <c r="K67" s="2" t="n"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
     </row>
@@ -3492,28 +3483,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>0.0105</v>
+        <v>1.17</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>785900</v>
+        <v>1452800</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
       <c r="H68" t="n">
-        <v>89.68000000000001</v>
+        <v>49.11</v>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
@@ -3521,10 +3512,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.312</v>
+        <v>1.18</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1.973</v>
+        <v>1.145</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3537,39 +3528,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.655</v>
+        <v>0.2</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>0.0155</v>
+        <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>764500</v>
+        <v>1447400</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.08</v>
+        <v>1.43</v>
       </c>
       <c r="H69" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.51</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.634</v>
+        <v>0.205</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.577</v>
+        <v>0.214</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3582,39 +3573,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0.016</v>
+        <v>0.74</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>751600</v>
+        <v>1405700</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.28</v>
+        <v>0.42</v>
       </c>
       <c r="H70" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.48</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.387</v>
+        <v>0.711</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1.317</v>
+        <v>0.713</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3627,28 +3618,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>0.0241</v>
+        <v>0.405</v>
+      </c>
+      <c r="E71" s="8" t="n">
+        <v>0.0253</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>736600</v>
+        <v>1398000</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.28</v>
+        <v>0.83</v>
       </c>
       <c r="H71" t="n">
-        <v>90.23</v>
+        <v>67.7</v>
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
@@ -3656,10 +3647,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>2.262</v>
+        <v>0.374</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1.799</v>
+        <v>0.342</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3672,28 +3663,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>-0.0071</v>
+        <v>0.26</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>731500</v>
+        <v>1348400</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.24</v>
+        <v>1.73</v>
       </c>
       <c r="H72" t="n">
-        <v>44.28</v>
+        <v>45.51</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -3701,10 +3692,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>5.772</v>
+        <v>0.261</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>5.767</v>
+        <v>0.266</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3717,28 +3708,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>7.86</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>-0.0163</v>
+        <v>0.35</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>727800</v>
+        <v>1305900</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
       </c>
       <c r="H73" t="n">
-        <v>53.83</v>
+        <v>59.75</v>
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
@@ -3746,10 +3737,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>7.811</v>
+        <v>0.339</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>7.737</v>
+        <v>0.333</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3762,39 +3753,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0.0074</v>
+        <v>2.94</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>0.028</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>713200</v>
+        <v>1203800</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.15</v>
+        <v>0.53</v>
       </c>
       <c r="H74" t="n">
-        <v>81.56</v>
-      </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>90.22</v>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>2.484</v>
+        <v>2.317</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>2.139</v>
+        <v>1.974</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3807,39 +3798,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>2.49</v>
+        <v>0.35</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>-0.008</v>
+        <v>-0.0278</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>692200</v>
+        <v>1165200</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.05</v>
+        <v>0.67</v>
       </c>
       <c r="H75" t="n">
-        <v>59.77</v>
-      </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.48</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2.445</v>
+        <v>0.353</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>2.286</v>
+        <v>0.321</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3852,39 +3843,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>-0.0086</v>
+        <v>1.95</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>689500</v>
+        <v>1151800</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="H76" t="n">
-        <v>50.03</v>
-      </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.43</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.162</v>
+        <v>1.98</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1.102</v>
+        <v>1.972</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3897,28 +3888,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>-0.0076</v>
+        <v>0.735</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>683400</v>
+        <v>1141600</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.06</v>
+        <v>0.2</v>
       </c>
       <c r="H77" t="n">
-        <v>40.38</v>
+        <v>62.85</v>
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
@@ -3926,10 +3917,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.329</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1.438</v>
+        <v>0.616</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3942,28 +3933,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.265</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>678400</v>
+        <v>1112700</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.19</v>
+        <v>0.91</v>
       </c>
       <c r="H78" t="n">
-        <v>46.45</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
@@ -3971,10 +3962,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.217</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.594</v>
+        <v>0.2</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3987,39 +3978,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>-0.0071</v>
+        <v>0.765</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>673000</v>
+        <v>1093500</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H79" t="n">
-        <v>54.06</v>
-      </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.772</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.664</v>
+        <v>0.773</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4032,39 +4023,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E80" s="8" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E80" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>650000</v>
+        <v>1088000</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.67</v>
+        <v>0.16</v>
       </c>
       <c r="H80" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.08</v>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.631</v>
+        <v>0.297</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.637</v>
+        <v>0.311</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4077,28 +4068,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1.88</v>
+        <v>0.41</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>-0.0105</v>
+        <v>-0.012</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>632200</v>
+        <v>1087000</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="H81" t="n">
-        <v>35.9</v>
+        <v>53.12</v>
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
@@ -4106,10 +4097,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.95</v>
+        <v>0.402</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2.073</v>
+        <v>0.402</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4122,28 +4113,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E82" s="8" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>-0.0426</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>622900</v>
+        <v>1070300</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.1</v>
+        <v>0.65</v>
       </c>
       <c r="H82" t="n">
-        <v>46.13</v>
+        <v>38.48</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4151,10 +4142,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.772</v>
+        <v>0.239</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.773</v>
+        <v>0.243</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4167,39 +4158,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0.0091</v>
+        <v>1.23</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>-0.0184</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>610900</v>
+        <v>1040100</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="H83" t="n">
-        <v>65.67</v>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.37</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>9.573</v>
+        <v>1.269</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>9.106999999999999</v>
+        <v>1.302</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4212,28 +4203,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>-0.0221</v>
+        <v>1.28</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>0.024</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>568300</v>
+        <v>1028400</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.08</v>
+        <v>0.38</v>
       </c>
       <c r="H84" t="n">
-        <v>50.6</v>
+        <v>37.76</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4241,10 +4232,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>2.225</v>
+        <v>1.388</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>2.108</v>
+        <v>1.317</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4257,39 +4248,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>3.44</v>
+        <v>0.355</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>-0.0171</v>
+        <v>-0.0139</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>551800</v>
+        <v>1022700</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="H85" t="n">
-        <v>34.15</v>
-      </c>
-      <c r="I85" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.3</v>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>3.599</v>
+        <v>0.338</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>3.699</v>
+        <v>0.32</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4302,28 +4293,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.62</v>
+        <v>0.705</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>0.008100000000000001</v>
+        <v>0</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>548800</v>
+        <v>1015200</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.37</v>
+        <v>0.13</v>
       </c>
       <c r="H86" t="n">
-        <v>72.55</v>
+        <v>55.12</v>
       </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
@@ -4331,10 +4322,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.495</v>
+        <v>0.664</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4347,39 +4338,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>4.39</v>
+        <v>3.43</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>-0.0068</v>
+        <v>-0.02</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>531400</v>
+        <v>990600</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="H87" t="n">
-        <v>78.31999999999999</v>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.62</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>3.607</v>
+        <v>3.598</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2.415</v>
+        <v>3.698</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4392,28 +4383,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>12.94</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0.0023</v>
+        <v>3</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>529700</v>
+        <v>975300</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="H88" t="n">
-        <v>32.93</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
@@ -4421,10 +4412,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>13.185</v>
+        <v>2.265</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>13.77</v>
+        <v>1.8</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4437,28 +4428,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E89" s="8" t="n">
-        <v>0</v>
+        <v>5.73</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>519000</v>
+        <v>969200</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H89" t="n">
-        <v>50.53</v>
+        <v>55.79</v>
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
@@ -4466,10 +4457,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.181</v>
+        <v>5.688</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1.145</v>
+        <v>5.16</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4482,28 +4473,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>0.0132</v>
+        <v>5.56</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>-0.0089</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>512300</v>
+        <v>960700</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="H90" t="n">
-        <v>39.66</v>
+        <v>44.04</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4511,10 +4502,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.793</v>
+        <v>5.771</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.845</v>
+        <v>5.767</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4527,45 +4518,1213 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>1.28</v>
+        <v>0.575</v>
       </c>
       <c r="E91" s="10" t="n">
-        <v>0.0159</v>
+        <v>0</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>511800</v>
+        <v>945600</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="H91" t="n">
-        <v>84.76000000000001</v>
-      </c>
-      <c r="I91" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.59</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.068</v>
+        <v>0.586</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.9</v>
+        <v>0.587</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>909900</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H92" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>2.484</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>2.139</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E93" s="8" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>896400</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H93" t="n">
+        <v>85.14</v>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>1.068</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>-0.0092</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>884000</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H94" t="n">
+        <v>74.19</v>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>883700</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H95" t="n">
+        <v>34.06</v>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>13.186</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>850600</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H96" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>807500</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H97" t="n">
+        <v>59.94</v>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>798900</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H98" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>753000</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H99" t="n">
+        <v>56.43</v>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>2.872</v>
+      </c>
+      <c r="K99" s="2" t="n"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>737400</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H100" t="n">
+        <v>36.97</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>1.149</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="7" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="E101" s="8" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>704400</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H101" t="n">
+        <v>73.97</v>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>2.549</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>-0.0172</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>700200</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H102" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>1.161</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>1.102</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="7" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>-0.0105</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>690700</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H103" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>2.073</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>687000</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H104" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>674600</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H105" t="n">
+        <v>76.79000000000001</v>
+      </c>
+      <c r="I105" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>3.603</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>2.414</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="7" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="E106" s="8" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>673600</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H106" t="n">
+        <v>65.47</v>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>9.571999999999999</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>9.106999999999999</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>669400</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H107" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>-0.0221</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>656300</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H108" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>2.108</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="7" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>650000</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H109" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="7" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>623200</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H110" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>1.554</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>1.668</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>559200</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H111" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>1.074</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="7" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>MFLOUR</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>559100</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H112" t="n">
+        <v>42.46</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>4243</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>WTK</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="E113" s="8" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>553900</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H113" t="n">
+        <v>36.83</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>1.035</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>1.017</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>532800</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H114" t="n">
+        <v>52.65</v>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>526700</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H115" t="n">
+        <v>33.84</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>7.956</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>8.252000000000001</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="7" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>-0.0169</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>519000</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H116" t="n">
+        <v>45.54</v>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>1.769</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>1.803</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>508200</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H117" t="n">
+        <v>53.54</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M91"/>
+  <autoFilter ref="A1:M117"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-29/bursa-report-2026-09-29.xlsx
+++ b/docs/downloads/2026-09-29/bursa-report-2026-09-29.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-29" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-29'!$A$1:$M$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-29'!$A$1:$M$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M139"/>
+  <dimension ref="A1:M171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.395</v>
+        <v>0.4</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.026</v>
+        <v>0.039</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>8924500</v>
+        <v>11116900</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.91</v>
+        <v>1.13</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>70.45</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.371</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>EMA与SAR、Supertrend均呈多头排列，现价高于50日均线，但RSI 70.45已入超买区，信号偏强但需留意高位风险。</t>
+          <t>现价0.40高于50日均线0.371，EMA与SAR、Supertrend均偏多；但RSI达72.9已入超买区，信号可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>-0.1053</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>256426400</v>
+        <v>268848900</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="H3" t="n">
         <v>20.85</v>
@@ -670,10 +670,10 @@
         <v>0.027</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>60297900</v>
+        <v>63960000</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="H4" t="n">
         <v>79.09999999999999</v>
@@ -715,10 +715,10 @@
         <v>-0.0128</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>13966600</v>
+        <v>18558200</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H5" t="n">
         <v>76.03</v>
@@ -760,10 +760,10 @@
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>13014600</v>
+        <v>13418000</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="H6" t="n">
         <v>68.72</v>
@@ -799,19 +799,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0.0616</v>
+        <v>0.0507</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>8517500</v>
+        <v>11896900</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.13</v>
+        <v>1.58</v>
       </c>
       <c r="H7" t="n">
-        <v>65.61</v>
+        <v>64.62</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2.653</v>
+        <v>2.65</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>2.509</v>
+        <v>2.508</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,39 +835,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>1.29</v>
+        <v>0.77</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>8197400</v>
+        <v>10678800</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.72</v>
+        <v>0.85</v>
       </c>
       <c r="H8" t="n">
-        <v>41.69</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.12</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1.363</v>
+        <v>0.773</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>1.292</v>
+        <v>0.774</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,28 +880,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FSBM</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.1</v>
+        <v>1.32</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>0.0526</v>
+        <v>0.0313</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>8171000</v>
+        <v>10561200</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.32</v>
+        <v>0.92</v>
       </c>
       <c r="H9" t="n">
-        <v>35.37</v>
+        <v>45.87</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.13</v>
+        <v>1.366</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.161</v>
+        <v>1.293</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,33 +925,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>FSBM</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>0.0625</v>
+        <v>0.095</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>7803100</v>
+        <v>10268200</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.51</v>
+        <v>0.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>33</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
+      <c r="J10" s="9" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.16</v>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
     </row>
@@ -963,39 +970,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>0.0357</v>
+        <v>0.51</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>7139000</v>
+        <v>10147700</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>3.21</v>
+        <v>0.27</v>
       </c>
       <c r="H11" t="n">
-        <v>85.54000000000001</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.4</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.231</v>
+        <v>0.622</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.21</v>
+        <v>0.839</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1008,33 +1015,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>-0.0385</v>
+        <v>0.305</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>6679500</v>
+        <v>9499800</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.09</v>
+        <v>0.51</v>
+      </c>
+      <c r="H12" t="n">
+        <v>54.01</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
+      <c r="J12" s="9" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.291</v>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
     </row>
@@ -1046,39 +1060,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>6565500</v>
+        <v>9435800</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.52</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>48.12</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.19</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.773</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.774</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1091,39 +1105,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.515</v>
+        <v>0.865</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>-0.019</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>6514100</v>
+        <v>9142000</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.17</v>
+        <v>0.51</v>
       </c>
       <c r="H14" t="n">
-        <v>25.78</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.09</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.622</v>
+        <v>0.868</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.839</v>
+        <v>0.87</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1136,40 +1150,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E15" s="17" t="n">
-        <v>0</v>
+        <v>0.12</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>6348300</v>
+        <v>8787400</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="H15" t="n">
-        <v>57.06</v>
+        <v>0.12</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J15" s="9" t="n">
-        <v>0.449</v>
-      </c>
-      <c r="K15" s="9" t="n">
-        <v>0.41</v>
-      </c>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="9" t="n"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
     </row>
@@ -1181,39 +1188,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0</v>
+        <v>0.29</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>6312800</v>
+        <v>8022000</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.46</v>
+        <v>3.6</v>
       </c>
       <c r="H16" t="n">
-        <v>50.19</v>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.54000000000001</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.231</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1226,40 +1233,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6153800</v>
+        <v>7896200</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H17" t="n">
-        <v>54.01</v>
+        <v>0.52</v>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J17" s="9" t="n">
-        <v>0.304</v>
-      </c>
-      <c r="K17" s="9" t="n">
-        <v>0.291</v>
-      </c>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9" t="n"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
     </row>
@@ -1271,28 +1271,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>-0.0476</v>
+        <v>4.43</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0.0649</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>6060300</v>
+        <v>7291400</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.38</v>
+        <v>1.42</v>
       </c>
       <c r="H18" t="n">
-        <v>56.45</v>
+        <v>83.73</v>
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.286</v>
+        <v>3.629</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.277</v>
+        <v>3.254</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1316,28 +1316,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>-0.0408</v>
+        <v>0.47</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5995500</v>
+        <v>6658100</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>2.07</v>
+        <v>0.71</v>
       </c>
       <c r="H19" t="n">
-        <v>39.67</v>
+        <v>58.22</v>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.258</v>
+        <v>0.45</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.251</v>
+        <v>0.41</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1361,40 +1361,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0213</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MTAG</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0.0227</v>
+        <v>0.005</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>5903400</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="H20" t="n">
-        <v>63.95</v>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="K20" s="9" t="n">
-        <v>0.216</v>
-      </c>
+        <v>6526500</v>
+      </c>
+      <c r="G20" s="12" t="n"/>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="9" t="n"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
     </row>
@@ -1406,28 +1397,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>0.05769999999999999</v>
+        <v>0.555</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>5676500</v>
+        <v>6285700</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="H21" t="n">
-        <v>83.38</v>
+        <v>63.74</v>
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
@@ -1435,10 +1426,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>3.626</v>
+        <v>0.525</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>3.254</v>
+        <v>0.532</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1451,39 +1442,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.235</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>-0.0408</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5470300</v>
+        <v>6262300</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.93</v>
+        <v>2.16</v>
       </c>
       <c r="H22" t="n">
-        <v>65.19</v>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.67</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.525</v>
+        <v>0.258</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.532</v>
+        <v>0.251</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1496,31 +1487,40 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
+        <v>2.51</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>-0.0157</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>5466400</v>
-      </c>
-      <c r="G23" s="12" t="n"/>
+        <v>6256300</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H23" t="n">
+        <v>46.6</v>
+      </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>2.447</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
     </row>
@@ -1532,39 +1532,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PTT</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>0.0071</v>
+        <v>0.305</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>-0.0317</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>5044100</v>
+        <v>6221800</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>7.13</v>
+        <v>0.39</v>
       </c>
       <c r="H24" t="n">
-        <v>44.62</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.44</v>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1.44</v>
+        <v>0.286</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1.431</v>
+        <v>0.278</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1586,19 +1586,19 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.805</v>
+        <v>0.79</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0.0255</v>
+        <v>0.0064</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>4968900</v>
+        <v>6069700</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.48</v>
+        <v>0.59</v>
       </c>
       <c r="H25" t="n">
-        <v>65.14</v>
+        <v>63.5</v>
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0.6889999999999999</v>
@@ -1622,28 +1622,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0213</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>MTAG</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>-0.012</v>
+        <v>0.22</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>4961900</v>
+        <v>6045500</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.46</v>
+        <v>13.01</v>
       </c>
       <c r="H26" t="n">
-        <v>51.13</v>
+        <v>60.36</v>
       </c>
       <c r="I26" s="16" t="inlineStr">
         <is>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.409</v>
+        <v>0.209</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.411</v>
+        <v>0.216</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1667,28 +1667,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.865</v>
+        <v>2.3</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0171</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>4748800</v>
+        <v>5954400</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="H27" t="n">
-        <v>47.09</v>
+        <v>47.67</v>
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.868</v>
+        <v>2.343</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.87</v>
+        <v>2.245</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1712,28 +1712,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>-0.0089</v>
+        <v>0.605</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>4161600</v>
+        <v>5794300</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.28</v>
+        <v>0.59</v>
       </c>
       <c r="H28" t="n">
-        <v>69.81</v>
+        <v>48.47</v>
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.482</v>
+        <v>0.607</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.406</v>
+        <v>0.605</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1757,28 +1757,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>0</v>
+        <v>7.81</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>-0.0225</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>4136800</v>
+        <v>5469000</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="H29" t="n">
-        <v>45.5</v>
+        <v>51.27</v>
       </c>
       <c r="I29" s="16" t="inlineStr">
         <is>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.607</v>
+        <v>7.806</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.605</v>
+        <v>7.736</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1802,39 +1802,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>1.78</v>
+        <v>4.75</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>-0.0111</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>3992000</v>
+        <v>5238000</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="H30" t="n">
-        <v>57.19</v>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.75</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>1.739</v>
+        <v>4.836</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1.537</v>
+        <v>4.953</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         <v>0.04650000000000001</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3895600</v>
+        <v>5086900</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="H31" t="n">
         <v>67.76000000000001</v>
@@ -1892,39 +1892,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E32" s="17" t="n">
-        <v>0</v>
+        <v>1.41</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3842700</v>
+        <v>5066500</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.13</v>
+        <v>7.17</v>
       </c>
       <c r="H32" t="n">
-        <v>31.98</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.62</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.273</v>
+        <v>1.44</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.325</v>
+        <v>1.431</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1937,39 +1937,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>4.75</v>
+        <v>0.41</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.012</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>3832600</v>
+        <v>4996500</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.22</v>
+        <v>0.46</v>
       </c>
       <c r="H33" t="n">
-        <v>35.75</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.13</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>4.836</v>
+        <v>0.409</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>4.953</v>
+        <v>0.411</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1982,39 +1982,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>7.82</v>
+        <v>0.21</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>-0.0213</v>
+        <v>-0.0233</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>3805600</v>
+        <v>4818700</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="H34" t="n">
-        <v>51.76</v>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.87</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>7.807</v>
+        <v>0.236</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>7.736</v>
+        <v>0.248</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2027,28 +2027,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>0</v>
+        <v>10.08</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>3791000</v>
+        <v>4678000</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H35" t="n">
-        <v>66.27</v>
+        <v>41.49</v>
       </c>
       <c r="I35" s="16" t="inlineStr">
         <is>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.277</v>
+        <v>10.166</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.27</v>
+        <v>10.308</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2072,28 +2072,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.215</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>3713000</v>
+        <v>4597700</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.31</v>
+        <v>0.21</v>
       </c>
       <c r="H36" t="n">
-        <v>74.22</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="I36" s="16" t="inlineStr">
         <is>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>1.012</v>
+        <v>0.204</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.853</v>
+        <v>0.185</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2117,39 +2117,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3628800</v>
+        <v>4469800</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="H37" t="n">
-        <v>45.92</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>30.69</v>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>2.122</v>
+        <v>0.273</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>2.064</v>
+        <v>0.325</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2162,39 +2162,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>2.31</v>
+        <v>0.385</v>
       </c>
       <c r="E38" s="10" t="n">
         <v>-0.0128</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3448800</v>
+        <v>4467600</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="H38" t="n">
-        <v>48.37</v>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.94</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>2.344</v>
+        <v>0.382</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>2.245</v>
+        <v>0.322</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2207,28 +2207,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>0</v>
+        <v>0.555</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>-0.0089</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>3398500</v>
+        <v>4439600</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="H39" t="n">
-        <v>56.39</v>
+        <v>69.81</v>
       </c>
       <c r="I39" s="16" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.233</v>
+        <v>0.482</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.233</v>
+        <v>0.406</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2252,28 +2252,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>0</v>
+        <v>2.86</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3389900</v>
+        <v>4358800</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="H40" t="n">
-        <v>60.08</v>
+        <v>62.01</v>
       </c>
       <c r="I40" s="16" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.527</v>
+        <v>2.775</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.48</v>
+        <v>2.637</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2297,39 +2297,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>-0.0135</v>
+        <v>2.08</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3371100</v>
+        <v>4334100</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="H41" t="n">
-        <v>48.25</v>
-      </c>
-      <c r="I41" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.92</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.367</v>
+        <v>2.122</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.367</v>
+        <v>2.064</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2342,39 +2342,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>0</v>
+        <v>1.79</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3348400</v>
+        <v>4333800</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="H42" t="n">
-        <v>51.13</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.11</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.736</v>
+        <v>1.74</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.6840000000000001</v>
+        <v>1.538</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2387,39 +2387,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>0.0467</v>
+        <v>2.49</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3346200</v>
+        <v>4230900</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.57</v>
+        <v>0.28</v>
       </c>
       <c r="H43" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.77</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.766</v>
+        <v>2.445</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.753</v>
+        <v>2.286</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2432,39 +2432,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>-0.0157</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3299600</v>
+        <v>4206600</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="H44" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.06</v>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>2.58</v>
+        <v>0.527</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>2.447</v>
+        <v>0.48</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2477,39 +2477,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>0</v>
+        <v>0.785</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0.0467</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3102000</v>
+        <v>3982900</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.14</v>
+        <v>0.68</v>
       </c>
       <c r="H45" t="n">
-        <v>71.25</v>
-      </c>
-      <c r="I45" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.4</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.204</v>
+        <v>0.766</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.185</v>
+        <v>0.753</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2522,39 +2522,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>-0.0241</v>
+        <v>0.73</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2995400</v>
+        <v>3967100</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.21</v>
+        <v>0.09</v>
       </c>
       <c r="H46" t="n">
-        <v>59.71</v>
-      </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.13</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>2.773</v>
+        <v>0.736</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.636</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2567,28 +2567,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>10.1</v>
+        <v>0.235</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>-0.0059</v>
+        <v>-0.0208</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2869800</v>
+        <v>3939300</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="H47" t="n">
-        <v>42.66</v>
+        <v>52.63</v>
       </c>
       <c r="I47" s="16" t="inlineStr">
         <is>
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>10.168</v>
+        <v>0.232</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>10.309</v>
+        <v>0.233</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,28 +2612,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>-0.0152</v>
+        <v>0.355</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>0.0441</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2780600</v>
+        <v>3925000</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.24</v>
+        <v>0.9</v>
       </c>
       <c r="H48" t="n">
-        <v>38.68</v>
+        <v>62.57</v>
       </c>
       <c r="I48" s="16" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>1.328</v>
+        <v>0.34</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>1.438</v>
+        <v>0.333</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>-0.0128</v>
+        <v>1.09</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2755700</v>
+        <v>3863500</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="H49" t="n">
-        <v>53.94</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.22</v>
+      </c>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.382</v>
+        <v>1.012</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.322</v>
+        <v>0.853</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2702,28 +2702,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SUNSURIA</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>-0.0526</v>
+        <v>0.175</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2751300</v>
+        <v>3854100</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>40.61</v>
+        <v>0.76</v>
       </c>
       <c r="H50" t="n">
-        <v>44.26</v>
+        <v>59.06</v>
       </c>
       <c r="I50" s="16" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.277</v>
+        <v>0.164</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.281</v>
+        <v>0.165</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2747,39 +2747,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E51" s="15" t="n">
-        <v>0.0156</v>
+        <v>0.29</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2702700</v>
+        <v>3811000</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.8</v>
+        <v>0.61</v>
       </c>
       <c r="H51" t="n">
-        <v>35.32</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.78</v>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.384</v>
+        <v>0.276</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.371</v>
+        <v>0.27</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,39 +2792,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>SUNSURIA</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>2651200</v>
+        <v>3716900</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.11</v>
+        <v>54.86</v>
       </c>
       <c r="H52" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.15</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.236</v>
+        <v>0.278</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.248</v>
+        <v>0.282</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2837,39 +2837,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>-0.0199</v>
+        <v>4.73</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2599700</v>
+        <v>3635900</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="H53" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.78</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>2.442</v>
+        <v>4.739</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2.286</v>
+        <v>4.591</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2882,28 +2882,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>0</v>
+        <v>0.365</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2563500</v>
+        <v>3457100</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.11</v>
+        <v>0.57</v>
       </c>
       <c r="H54" t="n">
-        <v>48.8</v>
+        <v>48.25</v>
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.467</v>
+        <v>0.367</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.471</v>
+        <v>0.367</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2936,19 +2936,19 @@
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>4.84</v>
+        <v>4.87</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>-0.0143</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2504400</v>
+        <v>3413100</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="H55" t="n">
-        <v>59.69</v>
+        <v>62.17</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>4.754</v>
+        <v>4.757</v>
       </c>
       <c r="K55" s="9" t="n">
         <v>4.524</v>
@@ -2972,28 +2972,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>-0.0248</v>
+        <v>0.765</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2435800</v>
+        <v>3318900</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.49</v>
+        <v>0.55</v>
       </c>
       <c r="H56" t="n">
-        <v>33.4</v>
+        <v>46.13</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.633</v>
+        <v>0.772</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.657</v>
+        <v>0.773</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3017,39 +3017,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>0.0109</v>
+        <v>0.595</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2314900</v>
+        <v>3255400</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="H57" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="I57" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.5</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.928</v>
+        <v>0.633</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.969</v>
+        <v>0.657</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3062,28 +3062,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E58" s="15" t="n">
-        <v>0.0294</v>
+        <v>1.14</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>-0.0339</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2259200</v>
+        <v>3156900</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="H58" t="n">
-        <v>59.75</v>
+        <v>45.29</v>
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.339</v>
+        <v>1.178</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.333</v>
+        <v>1.145</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3107,28 +3107,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>0</v>
+        <v>5.76</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>-0.0035</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2207700</v>
+        <v>3127100</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="H59" t="n">
-        <v>51</v>
+        <v>57.15</v>
       </c>
       <c r="I59" s="16" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.214</v>
+        <v>5.691</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.212</v>
+        <v>5.161</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3152,39 +3152,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.275</v>
+        <v>1.3</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>-0.0678</v>
+        <v>-0.0152</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2166000</v>
+        <v>3097200</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="H60" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.68</v>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.265</v>
+        <v>1.328</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.222</v>
+        <v>1.438</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3197,28 +3197,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1.32</v>
+        <v>12.94</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>0.0313</v>
+        <v>0.0023</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2104200</v>
+        <v>3026400</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="H61" t="n">
-        <v>95.65000000000001</v>
+        <v>32.93</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.921</v>
+        <v>13.185</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.746</v>
+        <v>13.77</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3257,10 +3257,10 @@
         <v>0.0278</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2057900</v>
+        <v>2943600</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="H62" t="n">
         <v>63.5</v>
@@ -3287,39 +3287,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>12.96</v>
-      </c>
-      <c r="E63" s="15" t="n">
-        <v>0.0039</v>
+        <v>7.68</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1999400</v>
+        <v>2934500</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="H63" t="n">
-        <v>34.06</v>
-      </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.95</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>13.186</v>
+        <v>7.948</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>13.77</v>
+        <v>8.25</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3332,31 +3332,40 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BPROP</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E64" s="17" t="n">
-        <v>0</v>
+        <v>0.325</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1911500</v>
-      </c>
-      <c r="G64" s="12" t="n"/>
+        <v>2854100</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H64" t="n">
+        <v>35.32</v>
+      </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J64" s="9" t="n"/>
-      <c r="K64" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>0.371</v>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
     </row>
@@ -3368,28 +3377,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>-0.0106</v>
+        <v>1.3</v>
+      </c>
+      <c r="E65" s="15" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1905600</v>
+        <v>2778500</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.7</v>
+        <v>0.47</v>
       </c>
       <c r="H65" t="n">
-        <v>52.58</v>
+        <v>95.48</v>
       </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
@@ -3397,10 +3406,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.464</v>
+        <v>0.919</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.462</v>
+        <v>0.746</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3413,28 +3422,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.25</v>
+        <v>0.465</v>
       </c>
       <c r="E66" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1880800</v>
+        <v>2730200</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="H66" t="n">
-        <v>36.09</v>
+        <v>48.8</v>
       </c>
       <c r="I66" s="16" t="inlineStr">
         <is>
@@ -3442,10 +3451,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.27</v>
+        <v>0.467</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.313</v>
+        <v>0.471</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3458,39 +3467,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>0</v>
+        <v>0.93</v>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1872000</v>
+        <v>2693300</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.31</v>
+        <v>0.78</v>
       </c>
       <c r="H67" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.5</v>
+      </c>
+      <c r="I67" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.772</v>
+        <v>0.928</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.773</v>
+        <v>0.969</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3512,19 +3521,19 @@
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>-0.0104</v>
+        <v>-0.0263</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1801200</v>
+        <v>2596200</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.36</v>
+        <v>0.52</v>
       </c>
       <c r="H68" t="n">
-        <v>39.33</v>
+        <v>35.59</v>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
@@ -3532,10 +3541,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>1.27</v>
+        <v>1.268</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>1.303</v>
+        <v>1.302</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3548,39 +3557,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.9350000000000001</v>
+        <v>3.44</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>-0.0053</v>
+        <v>-0.0171</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1775200</v>
+        <v>2537400</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.38</v>
+        <v>0.52</v>
       </c>
       <c r="H69" t="n">
-        <v>70.83</v>
-      </c>
-      <c r="I69" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.15</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.888</v>
+        <v>3.599</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.852</v>
+        <v>3.699</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3593,39 +3602,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>0</v>
+        <v>7.45</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1740800</v>
+        <v>2529500</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="H70" t="n">
-        <v>48.43</v>
-      </c>
-      <c r="I70" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.74</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>2.567</v>
+        <v>7.667</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>2.54</v>
+        <v>7.835</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3638,28 +3647,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0191</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CABNET</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E71" s="15" t="n">
-        <v>0.1064</v>
+        <v>0.215</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1732000</v>
+        <v>2525700</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>10.75</v>
+        <v>0.46</v>
       </c>
       <c r="H71" t="n">
-        <v>69.84999999999999</v>
+        <v>51</v>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
@@ -3667,10 +3676,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.221</v>
+        <v>0.214</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.216</v>
+        <v>0.212</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3683,28 +3692,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>7.42</v>
+        <v>1.94</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>-0.0133</v>
+        <v>-0.0051</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1680800</v>
+        <v>2522700</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="H72" t="n">
-        <v>36.79</v>
+        <v>44.13</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3712,10 +3721,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>7.664</v>
+        <v>1.979</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>7.835</v>
+        <v>1.972</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3728,39 +3737,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E73" s="15" t="n">
-        <v>0.0192</v>
+        <v>0.27</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>-0.08470000000000001</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1632700</v>
+        <v>2369100</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>1.34</v>
+        <v>0.27</v>
       </c>
       <c r="H73" t="n">
-        <v>74.73999999999999</v>
-      </c>
-      <c r="I73" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.32</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.217</v>
+        <v>0.264</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.2</v>
+        <v>0.222</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3773,39 +3782,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>-0.0116</v>
+        <v>1.28</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>0.024</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1610000</v>
+        <v>2360300</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>1.52</v>
+        <v>0.88</v>
       </c>
       <c r="H74" t="n">
-        <v>41.37</v>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.76</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.431</v>
+        <v>1.388</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.452</v>
+        <v>1.317</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3818,39 +3827,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E75" s="15" t="n">
-        <v>0.038</v>
+        <v>1.94</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1604600</v>
+        <v>2346900</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.95</v>
+        <v>0.76</v>
       </c>
       <c r="H75" t="n">
-        <v>69</v>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.51</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.374</v>
+        <v>1.986</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.342</v>
+        <v>2.103</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3863,39 +3872,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <v>0.0064</v>
+        <v>0.93</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1602700</v>
+        <v>2278000</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.19</v>
+        <v>0.49</v>
       </c>
       <c r="H76" t="n">
-        <v>51.78</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.43000000000001</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>4.739</v>
+        <v>0.888</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>4.591</v>
+        <v>0.852</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3908,28 +3917,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>-0.006500000000000001</v>
+        <v>0.78</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1587300</v>
+        <v>2149300</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="H77" t="n">
-        <v>38.15</v>
+        <v>42.8</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3937,10 +3946,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>1.579</v>
+        <v>0.794</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>1.644</v>
+        <v>0.846</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3953,28 +3962,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>-0.008500000000000001</v>
+        <v>2.91</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>0.0175</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1556100</v>
+        <v>2072000</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.23</v>
+        <v>0.92</v>
       </c>
       <c r="H78" t="n">
-        <v>49.11</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I78" s="16" t="inlineStr">
         <is>
@@ -3982,10 +3991,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.18</v>
+        <v>2.314</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.145</v>
+        <v>1.974</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -3998,39 +4007,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E79" s="15" t="n">
-        <v>0.032</v>
+        <v>2.55</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1553200</v>
+        <v>2021000</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.58</v>
+        <v>0.34</v>
       </c>
       <c r="H79" t="n">
-        <v>39.15</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.43</v>
+      </c>
+      <c r="I79" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>1.389</v>
+        <v>2.567</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>1.317</v>
+        <v>2.54</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4043,28 +4052,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>0.0245</v>
+        <v>0.25</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1543200</v>
+        <v>2020800</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.68</v>
+        <v>0.18</v>
       </c>
       <c r="H80" t="n">
-        <v>90.11</v>
+        <v>36.09</v>
       </c>
       <c r="I80" s="16" t="inlineStr">
         <is>
@@ -4072,10 +4081,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>2.316</v>
+        <v>0.27</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>1.974</v>
+        <v>0.313</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4088,40 +4097,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>BPROP</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="E81" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1487400</v>
-      </c>
-      <c r="G81" s="12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="H81" t="n">
-        <v>37.51</v>
-      </c>
+        <v>1939500</v>
+      </c>
+      <c r="G81" s="12" t="n"/>
       <c r="I81" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J81" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="K81" s="9" t="n">
-        <v>0.214</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="n"/>
+      <c r="K81" s="9" t="n"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
     </row>
@@ -4133,33 +4133,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>0191</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>CABNET</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>-0.0104</v>
+        <v>0.26</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>0.1064</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1485900</v>
+        <v>1918600</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.08</v>
+        <v>11.91</v>
+      </c>
+      <c r="H82" t="n">
+        <v>69.84999999999999</v>
       </c>
       <c r="I82" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J82" s="9" t="n"/>
-      <c r="K82" s="9" t="n"/>
+      <c r="J82" s="9" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>0.216</v>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
     </row>
@@ -4171,39 +4178,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="E83" s="15" t="n">
-        <v>0.0051</v>
+        <v>0.465</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1484900</v>
+        <v>1905600</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.21</v>
+        <v>0.7</v>
       </c>
       <c r="H83" t="n">
-        <v>47</v>
-      </c>
-      <c r="I83" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.58</v>
+      </c>
+      <c r="I83" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.98</v>
+        <v>0.464</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.973</v>
+        <v>0.462</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4216,28 +4223,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.745</v>
+        <v>0.265</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>0.0347</v>
+        <v>0.0192</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1411200</v>
+        <v>1885700</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.42</v>
+        <v>1.54</v>
       </c>
       <c r="H84" t="n">
-        <v>65</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="I84" s="16" t="inlineStr">
         <is>
@@ -4245,10 +4252,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.712</v>
+        <v>0.217</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.713</v>
+        <v>0.2</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4261,28 +4268,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.23</v>
+        <v>1.54</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>-0.0213</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1405600</v>
+        <v>1858300</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.86</v>
+        <v>0.63</v>
       </c>
       <c r="H85" t="n">
-        <v>41.61</v>
+        <v>38.15</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -4290,10 +4297,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.24</v>
+        <v>1.579</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.244</v>
+        <v>1.644</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4306,28 +4313,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>5.8</v>
+        <v>3</v>
       </c>
       <c r="E86" s="15" t="n">
-        <v>0.0035</v>
+        <v>0.0345</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1403500</v>
+        <v>1853800</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.1</v>
+        <v>0.71</v>
       </c>
       <c r="H86" t="n">
-        <v>58.77</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="I86" s="16" t="inlineStr">
         <is>
@@ -4335,10 +4342,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>5.695</v>
+        <v>2.265</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>5.162</v>
+        <v>1.8</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4351,40 +4358,38 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E87" s="17" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1348400</v>
+        <v>1826500</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>1.73</v>
+        <v>0.53</v>
       </c>
       <c r="H87" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.26</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.261</v>
-      </c>
-      <c r="K87" s="9" t="n">
-        <v>0.266</v>
-      </c>
+        <v>2.874</v>
+      </c>
+      <c r="K87" s="9" t="n"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
     </row>
@@ -4411,10 +4416,10 @@
         <v>-0.0139</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1347100</v>
+        <v>1824100</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="H88" t="n">
         <v>62.3</v>
@@ -4441,39 +4446,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>-0.005</v>
+        <v>0.41</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>0.038</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1310100</v>
+        <v>1820800</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.3</v>
+        <v>1.08</v>
       </c>
       <c r="H89" t="n">
-        <v>32.98</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>1.043</v>
+        <v>0.374</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1.074</v>
+        <v>0.342</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4486,39 +4491,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>1.95</v>
+        <v>0.735</v>
       </c>
       <c r="E90" s="15" t="n">
-        <v>0.0052</v>
+        <v>0.0208</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1296600</v>
+        <v>1743800</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.42</v>
+        <v>0.3</v>
       </c>
       <c r="H90" t="n">
-        <v>39.56</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.98</v>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>1.987</v>
+        <v>0.677</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>2.103</v>
+        <v>0.619</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4531,39 +4536,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="E91" s="15" t="n">
-        <v>0.0414</v>
+        <v>1.63</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>-0.0181</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1290300</v>
+        <v>1678200</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.49</v>
+        <v>0.27</v>
       </c>
       <c r="H91" t="n">
-        <v>90.65000000000001</v>
-      </c>
-      <c r="I91" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.99</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>2.267</v>
+        <v>1.723</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.8</v>
+        <v>1.839</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4576,39 +4581,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>-0.0278</v>
+        <v>0.57</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1206100</v>
+        <v>1630500</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.45</v>
       </c>
       <c r="H92" t="n">
-        <v>52.48</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.26</v>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.353</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.321</v>
+        <v>0.594</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4621,28 +4626,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.405</v>
+        <v>0.425</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>-0.0241</v>
+        <v>-0.0116</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1182100</v>
+        <v>1625400</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.21</v>
+        <v>1.53</v>
       </c>
       <c r="H93" t="n">
-        <v>51.65</v>
+        <v>41.37</v>
       </c>
       <c r="I93" s="16" t="inlineStr">
         <is>
@@ -4650,10 +4655,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.402</v>
+        <v>0.431</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.401</v>
+        <v>0.452</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4666,28 +4671,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>SENDAI</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>0.0159</v>
+        <v>0.275</v>
+      </c>
+      <c r="E94" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1181200</v>
+        <v>1533400</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.45</v>
+        <v>0.9</v>
       </c>
       <c r="H94" t="n">
-        <v>84.76000000000001</v>
+        <v>59.56</v>
       </c>
       <c r="I94" s="16" t="inlineStr">
         <is>
@@ -4695,10 +4700,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.068</v>
+        <v>0.259</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.9</v>
+        <v>0.268</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4711,39 +4716,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.7</v>
+        <v>0.985</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>-0.0071</v>
+        <v>-0.0101</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1163900</v>
+        <v>1515400</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="H95" t="n">
-        <v>54.06</v>
-      </c>
-      <c r="I95" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.17</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>1.043</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.664</v>
+        <v>1.074</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4756,39 +4761,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.615</v>
+        <v>0.695</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>-0.008100000000000001</v>
+        <v>-0.0142</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1108700</v>
+        <v>1492500</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.46</v>
+        <v>0.2</v>
       </c>
       <c r="H96" t="n">
-        <v>40.73</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.05</v>
+      </c>
+      <c r="I96" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.635</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.634</v>
+        <v>0.664</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4801,40 +4806,33 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>-0.0172</v>
+        <v>0.48</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1101600</v>
+        <v>1491800</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H97" t="n">
-        <v>35.65</v>
+        <v>0.08</v>
       </c>
       <c r="I97" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J97" s="9" t="n">
-        <v>0.297</v>
-      </c>
-      <c r="K97" s="9" t="n">
-        <v>0.311</v>
-      </c>
+      <c r="J97" s="9" t="n"/>
+      <c r="K97" s="9" t="n"/>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
     </row>
@@ -4855,19 +4853,19 @@
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>5.56</v>
+        <v>5.55</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>-0.0089</v>
+        <v>-0.0107</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1099200</v>
+        <v>1479200</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
       <c r="H98" t="n">
-        <v>44.04</v>
+        <v>43.8</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -4875,7 +4873,7 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>5.771</v>
+        <v>5.77</v>
       </c>
       <c r="K98" s="9" t="n">
         <v>5.767</v>
@@ -4891,39 +4889,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>-0.0229</v>
+        <v>0.745</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>0.0347</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1098200</v>
+        <v>1429300</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.23</v>
+        <v>0.42</v>
       </c>
       <c r="H99" t="n">
-        <v>33.11</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65</v>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>3.597</v>
+        <v>0.712</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>3.698</v>
+        <v>0.713</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4936,39 +4934,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v>0.0155</v>
+        <v>0.23</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1091400</v>
+        <v>1405800</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.12</v>
+        <v>0.86</v>
       </c>
       <c r="H100" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="I100" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.61</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.634</v>
+        <v>0.24</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.577</v>
+        <v>0.244</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4981,39 +4979,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>-0.0181</v>
+        <v>0.87</v>
+      </c>
+      <c r="E101" s="15" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1040100</v>
+        <v>1405500</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.09</v>
+        <v>0.46</v>
       </c>
       <c r="H101" t="n">
-        <v>76.42</v>
-      </c>
-      <c r="I101" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.83</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>3.602</v>
+        <v>0.86</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>2.414</v>
+        <v>0.856</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5026,38 +5024,40 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="E102" s="15" t="n">
-        <v>0.0241</v>
+        <v>1.88</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1013400</v>
+        <v>1391800</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="H102" t="n">
-        <v>56</v>
-      </c>
-      <c r="I102" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.9</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>2.871</v>
-      </c>
-      <c r="K102" s="9" t="n"/>
+        <v>1.95</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>2.073</v>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
     </row>
@@ -5069,28 +5069,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0259</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>993100</v>
+        <v>1360600</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="H103" t="n">
-        <v>46.45</v>
+        <v>47.24</v>
       </c>
       <c r="I103" s="16" t="inlineStr">
         <is>
@@ -5098,10 +5098,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.5639999999999999</v>
+        <v>1.16</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.594</v>
+        <v>1.102</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5114,28 +5114,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>0</v>
+        <v>4.38</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>960200</v>
+        <v>1358200</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="H104" t="n">
-        <v>76.75</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
@@ -5143,10 +5143,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.984</v>
+        <v>3.606</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.8110000000000001</v>
+        <v>2.415</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5159,39 +5159,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>3.32</v>
+      </c>
+      <c r="E105" s="15" t="n">
+        <v>0.0408</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>954600</v>
+        <v>1351700</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.25</v>
+        <v>0.55</v>
       </c>
       <c r="H105" t="n">
-        <v>36.42</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.5</v>
+      </c>
+      <c r="I105" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.585</v>
+        <v>2.97</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.587</v>
+        <v>2.548</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5204,28 +5204,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>7.76</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>-0.0102</v>
+        <v>0.26</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>951500</v>
+        <v>1348400</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.09</v>
+        <v>1.73</v>
       </c>
       <c r="H106" t="n">
-        <v>33.84</v>
+        <v>45.51</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5233,10 +5233,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>7.956</v>
+        <v>0.261</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>8.252000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5249,39 +5249,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.775</v>
+        <v>1.27</v>
       </c>
       <c r="E107" s="15" t="n">
-        <v>0.0197</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>933600</v>
+        <v>1344800</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.23</v>
+        <v>0.51</v>
       </c>
       <c r="H107" t="n">
-        <v>41.27</v>
-      </c>
-      <c r="I107" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.36</v>
+      </c>
+      <c r="I107" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.794</v>
+        <v>1.067</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.846</v>
+        <v>0.9</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5294,39 +5294,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E108" s="17" t="n">
-        <v>0</v>
+        <v>1.73</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>-0.0226</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>926200</v>
+        <v>1331700</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="H108" t="n">
-        <v>33.09</v>
-      </c>
-      <c r="I108" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.47</v>
+      </c>
+      <c r="I108" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>1.111</v>
+        <v>1.768</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>1.149</v>
+        <v>1.803</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5339,28 +5339,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <v>0</v>
+        <v>6.17</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>0.0049</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>922900</v>
+        <v>1310000</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.62</v>
+        <v>0.08</v>
       </c>
       <c r="H109" t="n">
-        <v>71.7</v>
+        <v>39.02</v>
       </c>
       <c r="I109" s="16" t="inlineStr">
         <is>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>6.289</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.495</v>
+        <v>6.483</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5384,28 +5384,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v>0.0112</v>
+        <v>0.35</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>910600</v>
+        <v>1296100</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.19</v>
+        <v>0.75</v>
       </c>
       <c r="H110" t="n">
-        <v>81.91</v>
+        <v>52.48</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>2.485</v>
+        <v>0.353</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>2.139</v>
+        <v>0.321</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5429,28 +5429,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="E111" s="15" t="n">
-        <v>0.0564</v>
+        <v>0.285</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>880600</v>
+        <v>1281100</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.36</v>
+        <v>0.19</v>
       </c>
       <c r="H111" t="n">
-        <v>73.73</v>
+        <v>35.65</v>
       </c>
       <c r="I111" s="16" t="inlineStr">
         <is>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>2.975</v>
+        <v>0.297</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>2.549</v>
+        <v>0.311</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5474,39 +5474,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E112" s="17" t="n">
-        <v>0</v>
+        <v>0.405</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>-0.0241</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>870400</v>
+        <v>1276200</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.37</v>
+        <v>0.22</v>
       </c>
       <c r="H112" t="n">
-        <v>31.36</v>
-      </c>
-      <c r="I112" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.65</v>
+      </c>
+      <c r="I112" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>1.082</v>
+        <v>0.402</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>1.26</v>
+        <v>0.401</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5519,28 +5519,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>9.9</v>
+        <v>0.655</v>
       </c>
       <c r="E113" s="15" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.0155</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>817600</v>
+        <v>1228600</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="H113" t="n">
-        <v>64.64</v>
+        <v>57.9</v>
       </c>
       <c r="I113" s="16" t="inlineStr">
         <is>
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>9.568</v>
+        <v>0.634</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>9.106</v>
+        <v>0.577</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5564,28 +5564,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E114" s="10" t="n">
-        <v>-0.0183</v>
+        <v>0.63</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>811000</v>
+        <v>1196500</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.43</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>59.94</v>
+        <v>74.09</v>
       </c>
       <c r="I114" s="16" t="inlineStr">
         <is>
@@ -5593,10 +5593,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.501</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.407</v>
+        <v>0.495</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5609,39 +5609,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E115" s="15" t="n">
-        <v>0.0097</v>
+        <v>0.615</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>802300</v>
+        <v>1188800</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.1</v>
+        <v>0.49</v>
       </c>
       <c r="H115" t="n">
-        <v>76.08</v>
-      </c>
-      <c r="I115" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.73</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.906</v>
+        <v>0.635</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.767</v>
+        <v>0.634</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5654,28 +5654,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>-0.0172</v>
+        <v>9.890000000000001</v>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>0.003</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>747400</v>
+        <v>1152100</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.08</v>
+        <v>0.36</v>
       </c>
       <c r="H116" t="n">
-        <v>48.59</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="I116" s="16" t="inlineStr">
         <is>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>1.161</v>
+        <v>9.567</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>1.102</v>
+        <v>9.106</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5699,28 +5699,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.735</v>
+        <v>1.04</v>
       </c>
       <c r="E117" s="15" t="n">
-        <v>0.0208</v>
+        <v>0.0097</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>744700</v>
+        <v>1149500</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H117" t="n">
-        <v>69.98</v>
+        <v>76.08</v>
       </c>
       <c r="I117" s="16" t="inlineStr">
         <is>
@@ -5728,10 +5728,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.677</v>
+        <v>0.906</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.619</v>
+        <v>0.767</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5744,28 +5744,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1.88</v>
+        <v>0.42</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>-0.0105</v>
+        <v>-0.0118</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>725000</v>
+        <v>1144100</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.16</v>
+        <v>0.53</v>
       </c>
       <c r="H118" t="n">
-        <v>35.9</v>
+        <v>65.7</v>
       </c>
       <c r="I118" s="16" t="inlineStr">
         <is>
@@ -5773,10 +5773,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>1.95</v>
+        <v>0.396</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>2.073</v>
+        <v>0.381</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5789,28 +5789,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E119" s="10" t="n">
-        <v>-0.0221</v>
+        <v>2.71</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>0.0074</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>721200</v>
+        <v>1139500</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.1</v>
+        <v>0.24</v>
       </c>
       <c r="H119" t="n">
-        <v>50.6</v>
+        <v>81.56</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5818,10 +5818,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>2.225</v>
+        <v>2.484</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>2.108</v>
+        <v>2.139</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5834,39 +5834,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1.49</v>
+        <v>0.37</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>-0.0132</v>
+        <v>-0.039</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>690900</v>
+        <v>1123400</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.3</v>
+        <v>0.95</v>
       </c>
       <c r="H120" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="I120" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.08</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>1.554</v>
+        <v>0.386</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>1.668</v>
+        <v>0.393</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5879,39 +5879,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0342</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>RTECH</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>-0.019</v>
+        <v>0.25</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>680100</v>
+        <v>1116900</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.06</v>
+        <v>1.37</v>
       </c>
       <c r="H121" t="n">
-        <v>44.58</v>
-      </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67</v>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.076</v>
+        <v>0.231</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1.024</v>
+        <v>0.215</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5924,28 +5924,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E122" s="17" t="n">
-        <v>0</v>
+        <v>0.57</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>657500</v>
+        <v>1078900</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="H122" t="n">
-        <v>59.03</v>
+        <v>36.42</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.86</v>
+        <v>0.585</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.856</v>
+        <v>0.587</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5969,28 +5969,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E123" s="17" t="n">
-        <v>0</v>
+        <v>2.23</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>650000</v>
+        <v>1053900</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.67</v>
+        <v>0.14</v>
       </c>
       <c r="H123" t="n">
-        <v>48.02</v>
+        <v>52.06</v>
       </c>
       <c r="I123" s="13" t="inlineStr">
         <is>
@@ -5998,10 +5998,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.631</v>
+        <v>2.227</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.637</v>
+        <v>2.108</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6014,39 +6014,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.635</v>
+        <v>1.04</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0095</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>617800</v>
+        <v>1048500</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.47</v>
+        <v>0.1</v>
       </c>
       <c r="H124" t="n">
-        <v>52.65</v>
-      </c>
-      <c r="I124" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.87</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.634</v>
+        <v>1.077</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.629</v>
+        <v>1.025</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6059,28 +6059,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.835</v>
+        <v>1.09</v>
       </c>
       <c r="E125" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>602100</v>
+        <v>1046600</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="H125" t="n">
-        <v>62.68</v>
+        <v>76.75</v>
       </c>
       <c r="I125" s="16" t="inlineStr">
         <is>
@@ -6088,10 +6088,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.804</v>
+        <v>0.984</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.725</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6104,39 +6104,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E126" s="10" t="n">
-        <v>-0.012</v>
+        <v>2.04</v>
+      </c>
+      <c r="E126" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>599200</v>
+        <v>1023900</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="H126" t="n">
-        <v>33.89</v>
-      </c>
-      <c r="I126" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.8</v>
+      </c>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>1.724</v>
+        <v>2.061</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>1.839</v>
+        <v>2.104</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6149,28 +6149,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E127" s="15" t="n">
-        <v>0.0317</v>
+        <v>4.31</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>-0.0401</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>595600</v>
+        <v>983700</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="H127" t="n">
-        <v>50.75</v>
+        <v>47.02</v>
       </c>
       <c r="I127" s="16" t="inlineStr">
         <is>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>1.282</v>
+        <v>4.4</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>1.341</v>
+        <v>4.426</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6194,28 +6194,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.68</v>
+        <v>1.06</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>-0.0175</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>595600</v>
+        <v>981200</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
       <c r="H128" t="n">
-        <v>37.8</v>
+        <v>31.18</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.854</v>
+        <v>1.148</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6239,39 +6239,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E129" s="15" t="n">
-        <v>0.0106</v>
+        <v>0.63</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>590100</v>
+        <v>933100</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.25</v>
+        <v>0.71</v>
       </c>
       <c r="H129" t="n">
-        <v>35.85</v>
-      </c>
-      <c r="I129" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.62</v>
+      </c>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>1.034</v>
+        <v>0.634</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>1.017</v>
+        <v>0.629</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6284,28 +6284,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>1.14</v>
+        <v>1.49</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>-0.0256</v>
+        <v>-0.0132</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>585200</v>
+        <v>910200</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="H130" t="n">
-        <v>58.55</v>
+        <v>30.4</v>
       </c>
       <c r="I130" s="16" t="inlineStr">
         <is>
@@ -6313,10 +6313,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>1.11</v>
+        <v>1.554</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>1.014</v>
+        <v>1.668</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6329,28 +6329,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E131" s="15" t="n">
-        <v>0.0166</v>
+        <v>0.765</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>-0.0129</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>584800</v>
+        <v>905900</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.33</v>
+        <v>0.63</v>
       </c>
       <c r="H131" t="n">
-        <v>55.71</v>
+        <v>50.64</v>
       </c>
       <c r="I131" s="16" t="inlineStr">
         <is>
@@ -6358,10 +6358,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.907</v>
+        <v>0.765</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.789</v>
+        <v>0.755</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6374,39 +6374,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>-0.0226</v>
+        <v>-0.0234</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>582100</v>
+        <v>898400</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.11</v>
+        <v>0.57</v>
       </c>
       <c r="H132" t="n">
-        <v>44.47</v>
-      </c>
-      <c r="I132" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.85</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>1.768</v>
+        <v>1.749</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1.803</v>
+        <v>1.853</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6419,28 +6419,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>PADINI</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E133" s="10" t="n">
-        <v>-0.0069</v>
+        <v>1.02</v>
+      </c>
+      <c r="E133" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>576200</v>
+        <v>892800</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="H133" t="n">
-        <v>38.97</v>
+        <v>31.36</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6448,10 +6448,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.734</v>
+        <v>1.082</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.752</v>
+        <v>1.26</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6464,39 +6464,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E134" s="17" t="n">
-        <v>0</v>
+        <v>1.28</v>
+      </c>
+      <c r="E134" s="15" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>569400</v>
+        <v>881800</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.19</v>
+        <v>0.58</v>
       </c>
       <c r="H134" t="n">
-        <v>42.77</v>
-      </c>
-      <c r="I134" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.78</v>
+      </c>
+      <c r="I134" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>2.998</v>
+        <v>1.28</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>3.04</v>
+        <v>1.34</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6509,28 +6509,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>1.46</v>
+        <v>0.63</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>-0.0135</v>
+        <v>-0.0156</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>561900</v>
+        <v>879400</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H135" t="n">
-        <v>44.31</v>
+        <v>54.69</v>
       </c>
       <c r="I135" s="16" t="inlineStr">
         <is>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>1.476</v>
+        <v>0.62</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>1.526</v>
+        <v>0.583</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6554,28 +6554,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E136" s="15" t="n">
-        <v>0.0179</v>
+        <v>0.54</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>-0.0092</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>553200</v>
+        <v>843900</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>1.02</v>
+        <v>0.45</v>
       </c>
       <c r="H136" t="n">
-        <v>77.31999999999999</v>
+        <v>61.03</v>
       </c>
       <c r="I136" s="16" t="inlineStr">
         <is>
@@ -6583,10 +6583,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.515</v>
+        <v>0.502</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.496</v>
+        <v>0.407</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6599,39 +6599,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>4.45</v>
+        <v>7.9</v>
       </c>
       <c r="E137" s="10" t="n">
-        <v>-0.0089</v>
+        <v>-0.0063</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>549400</v>
+        <v>824000</v>
       </c>
       <c r="G137" s="12" t="n">
         <v>0.23</v>
       </c>
       <c r="H137" t="n">
-        <v>51.79</v>
-      </c>
-      <c r="I137" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.9</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>4.413</v>
+        <v>7.875</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>4.429</v>
+        <v>7.803</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6644,39 +6644,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.63</v>
+        <v>0.755</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>-0.0156</v>
+        <v>-0.0066</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>510200</v>
+        <v>806100</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="H138" t="n">
-        <v>53.54</v>
-      </c>
-      <c r="I138" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.62</v>
+      </c>
+      <c r="I138" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.633</v>
+        <v>0.755</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.593</v>
+        <v>0.74</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6689,45 +6689,1485 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>-0.0186</v>
+        <v>0.91</v>
+      </c>
+      <c r="E139" s="15" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>505300</v>
+        <v>800400</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.87</v>
+        <v>0.45</v>
       </c>
       <c r="H139" t="n">
-        <v>52.33</v>
-      </c>
-      <c r="I139" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.33</v>
+      </c>
+      <c r="I139" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>1.584</v>
+        <v>0.906</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>1.504</v>
+        <v>0.789</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>-0.0171</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>800200</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H140" t="n">
+        <v>60.43</v>
+      </c>
+      <c r="I140" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>1.111</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="E141" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>772100</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H141" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="n">
+        <v>2.998</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E142" s="15" t="n">
+        <v>0.0281</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>751200</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H142" t="n">
+        <v>41.13</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>1.893</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>1.962</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="E143" s="15" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>710300</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H143" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="I143" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>6.599</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>6.517</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>706600</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H144" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="I144" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>7084</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>QL</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>698300</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H145" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="I145" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>3.944</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>4243</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>WTK</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E146" s="15" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>695900</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H146" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>1.017</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>KERJAYA</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="E147" s="15" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>686000</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H147" t="n">
+        <v>76.48999999999999</v>
+      </c>
+      <c r="I147" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="n">
+        <v>3.346</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>679100</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H148" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="I148" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>1.477</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>1.527</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>677600</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H149" t="n">
+        <v>49.04</v>
+      </c>
+      <c r="I149" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>IHH</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="E150" s="15" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>666900</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H150" t="n">
+        <v>51.89</v>
+      </c>
+      <c r="I150" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>7.902</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>8.086</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E151" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>663400</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H151" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="I151" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>2.059</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>1.997</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>-0.009000000000000001</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>657300</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H152" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>4.564</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>4.532</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>0271</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>WELLS</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E153" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>650000</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H153" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>7179</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>LAGENDA</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>-0.0186</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>635800</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H154" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>BIMB</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>625300</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H155" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="I155" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>2.109</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>0372</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>CHEEDING</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E156" s="15" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>605700</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H156" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="I156" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E157" s="15" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>605700</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H157" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="I157" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="K157" s="9" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="14" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>595300</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H158" t="n">
+        <v>33.53</v>
+      </c>
+      <c r="I158" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="n">
+        <v>4.703</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>4.978</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>TAKAFUL</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>589400</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H159" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="n">
+        <v>3.061</v>
+      </c>
+      <c r="K159" s="9" t="n">
+        <v>3.147</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E160" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>586200</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H160" t="n">
+        <v>40.79</v>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="K160" s="9" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>581600</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H161" t="n">
+        <v>46.18</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="n">
+        <v>5.266</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>-0.0121</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>568900</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H162" t="n">
+        <v>31.06</v>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="n">
+        <v>6.709</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>6.877</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>5185</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>AFFIN</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>568100</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H163" t="n">
+        <v>38.31</v>
+      </c>
+      <c r="I163" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="n">
+        <v>2.042</v>
+      </c>
+      <c r="K163" s="9" t="n">
+        <v>2.117</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E164" s="15" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>567000</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H164" t="n">
+        <v>70.84</v>
+      </c>
+      <c r="I164" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n">
+        <v>1.359</v>
+      </c>
+      <c r="K164" s="9" t="n">
+        <v>1.326</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>5348</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ORKIM</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>-0.0125</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>561100</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H165" t="n">
+        <v>36.88</v>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="K165" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="E166" s="15" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>549100</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H166" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="I166" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K166" s="9" t="n">
+        <v>2.862</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>0388</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>SEMICO</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E167" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>549000</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H167" t="n">
+        <v>65.06</v>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="K167" s="9" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>537700</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H168" t="n">
+        <v>53.54</v>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>-0.0194</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>525200</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H169" t="n">
+        <v>50.72</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="K169" s="9" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>5053</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>OSK</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>-0.005500000000000001</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>511900</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H170" t="n">
+        <v>33.96</v>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K170" s="9" t="n">
+        <v>1.959</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E171" s="15" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>500900</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H171" t="n">
+        <v>50.78</v>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J171" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K171" s="9" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M139"/>
+  <autoFilter ref="A1:M171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-29/bursa-report-2026-09-29.xlsx
+++ b/docs/downloads/2026-09-29/bursa-report-2026-09-29.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-29" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-29'!$A$1:$M$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-29'!$A$1:$M$189</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M171"/>
+  <dimension ref="A1:M189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.039</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>11116900</v>
+        <v>11339400</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>72.90000000000001</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.40高于50日均线0.371，EMA与SAR、Supertrend均偏多；但RSI达72.9已入超买区，信号可靠性需谨慎看待。</t>
+          <t>现价0.40高于50日均线0.371，EMA与SAR、Supertrend均偏多；但RSI达72.9已入超买区，信号偏热，可靠性需谨慎看待。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.17</v>
+        <v>0.165</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>-0.1053</v>
+        <v>-0.1316</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>268848900</v>
+        <v>274458600</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="H3" t="n">
-        <v>20.85</v>
+        <v>20.46</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -670,10 +670,10 @@
         <v>0.027</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>63960000</v>
+        <v>65293500</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="H4" t="n">
         <v>79.09999999999999</v>
@@ -715,10 +715,10 @@
         <v>-0.0128</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>18558200</v>
+        <v>19878200</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="H5" t="n">
         <v>76.03</v>
@@ -745,39 +745,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.58</v>
+        <v>0.155</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>13418000</v>
+        <v>14721700</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="H6" t="n">
-        <v>68.72</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.73</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.55</v>
+        <v>0.156</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.494</v>
+        <v>0.159</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -790,28 +790,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2.9</v>
+        <v>0.58</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0.0507</v>
+        <v>0.045</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>11896900</v>
+        <v>14103800</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="H7" t="n">
-        <v>64.62</v>
+        <v>64.52</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2.65</v>
+        <v>0.529</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>2.508</v>
+        <v>0.481</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,39 +835,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.58</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>10678800</v>
+        <v>13585800</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.85</v>
+        <v>0.57</v>
       </c>
       <c r="H8" t="n">
-        <v>48.12</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>68.72</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.773</v>
+        <v>0.55</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.774</v>
+        <v>0.494</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,39 +880,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1.32</v>
+        <v>2.9</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>0.0313</v>
+        <v>0.0507</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>10561200</v>
+        <v>13570700</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.92</v>
+        <v>1.81</v>
       </c>
       <c r="H9" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.62</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1.366</v>
+        <v>2.65</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>1.293</v>
+        <v>2.508</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,39 +925,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FSBM</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>10268200</v>
+        <v>12659500</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H10" t="n">
-        <v>33</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.09</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.129</v>
+        <v>0.868</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.16</v>
+        <v>0.87</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -979,19 +979,19 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.51</v>
+        <v>0.505</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>-0.0286</v>
+        <v>-0.0381</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>10147700</v>
+        <v>12184400</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="H11" t="n">
-        <v>25.4</v>
+        <v>25.04</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.622</v>
+        <v>0.621</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0.839</v>
@@ -1015,39 +1015,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0</v>
+        <v>0.77</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>9499800</v>
+        <v>12104300</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.51</v>
+        <v>0.97</v>
       </c>
       <c r="H12" t="n">
-        <v>54.01</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.12</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.304</v>
+        <v>0.773</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.291</v>
+        <v>0.774</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,28 +1060,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.305</v>
       </c>
       <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>9435800</v>
+        <v>11276600</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="H13" t="n">
-        <v>50.19</v>
+        <v>54.01</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.304</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.291</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,39 +1105,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>1.32</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>9142000</v>
+        <v>11066300</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.51</v>
+        <v>0.97</v>
       </c>
       <c r="H14" t="n">
-        <v>47.09</v>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.87</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.868</v>
+        <v>1.366</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.87</v>
+        <v>1.293</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1150,33 +1150,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0473</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Evocom Berhad</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>-0.07690000000000001</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>8787400</v>
+        <v>10697800</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.12</v>
+        <v>0.79</v>
+      </c>
+      <c r="H15" t="n">
+        <v>50.19</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="9" t="n"/>
+      <c r="J15" s="9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>0.8080000000000001</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
     </row>
@@ -1188,39 +1195,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>FSBM</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.29</v>
+        <v>0.1</v>
       </c>
       <c r="E16" s="15" t="n">
-        <v>0.0357</v>
+        <v>0.0526</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>8022000</v>
+        <v>10313300</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>3.6</v>
+        <v>0.4</v>
       </c>
       <c r="H16" t="n">
-        <v>85.54000000000001</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.37</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.231</v>
+        <v>0.13</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.21</v>
+        <v>0.161</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1233,25 +1240,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0473</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>Evocom Berhad</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>0.0417</v>
+        <v>0.125</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>-0.0385</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>7896200</v>
+        <v>8922200</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.52</v>
+        <v>0.12</v>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
@@ -1271,28 +1278,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>4.43</v>
+        <v>0.29</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>0.0649</v>
+        <v>0.0357</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>7291400</v>
+        <v>8057500</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1.42</v>
+        <v>3.62</v>
       </c>
       <c r="H18" t="n">
-        <v>83.73</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
@@ -1300,10 +1307,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>3.629</v>
+        <v>0.231</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>3.254</v>
+        <v>0.21</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1316,40 +1323,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.47</v>
+        <v>0.255</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.0108</v>
+        <v>0.0625</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>6658100</v>
+        <v>7906400</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H19" t="n">
-        <v>58.22</v>
+        <v>0.52</v>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J19" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K19" s="9" t="n">
-        <v>0.41</v>
-      </c>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
     </row>
@@ -1361,31 +1361,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>0</v>
+        <v>4.44</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0.0673</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>6526500</v>
-      </c>
-      <c r="G20" s="12" t="n"/>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="9" t="n"/>
+        <v>7834400</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H20" t="n">
+        <v>83.84</v>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>3.255</v>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
     </row>
@@ -1397,28 +1406,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>0</v>
+        <v>0.605</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>6285700</v>
+        <v>7527600</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>1.07</v>
+        <v>0.76</v>
       </c>
       <c r="H21" t="n">
-        <v>63.74</v>
+        <v>48.47</v>
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
@@ -1426,10 +1435,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.525</v>
+        <v>0.607</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.532</v>
+        <v>0.605</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1442,40 +1451,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>-0.0408</v>
+        <v>0.005</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>6262300</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="H22" t="n">
-        <v>39.67</v>
-      </c>
+        <v>7526500</v>
+      </c>
+      <c r="G22" s="12" t="n"/>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>0.258</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>0.251</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>-0.0157</v>
+        <v>-0.0118</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>6256300</v>
+        <v>7200900</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="H23" t="n">
-        <v>46.6</v>
+        <v>47.27</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>2.58</v>
+        <v>2.581</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>2.447</v>
@@ -1532,28 +1532,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.305</v>
+        <v>2.46</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>-0.0317</v>
+        <v>-0.0199</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>6221800</v>
+        <v>7112100</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="H24" t="n">
-        <v>58.44</v>
+        <v>55.67</v>
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.286</v>
+        <v>2.442</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.278</v>
+        <v>2.286</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1577,28 +1577,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.79</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0.0064</v>
+        <v>0.018</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>6069700</v>
+        <v>6897300</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.59</v>
+        <v>1.17</v>
       </c>
       <c r="H25" t="n">
-        <v>63.5</v>
+        <v>66.53</v>
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.718</v>
+        <v>0.526</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.532</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1622,39 +1622,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0213</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MTAG</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.22</v>
+        <v>0.73</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>6045500</v>
+        <v>6814600</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>13.01</v>
+        <v>0.15</v>
       </c>
       <c r="H26" t="n">
-        <v>60.36</v>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.13</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.209</v>
+        <v>0.736</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.216</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1667,39 +1667,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>-0.0171</v>
+        <v>0.47</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>5954400</v>
+        <v>6685700</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.37</v>
+        <v>0.71</v>
       </c>
       <c r="H27" t="n">
-        <v>47.67</v>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.22</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>2.343</v>
+        <v>0.45</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>2.245</v>
+        <v>0.41</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1712,28 +1712,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>0.0083</v>
+        <v>0.785</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>5794300</v>
+        <v>6484200</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.59</v>
+        <v>0.63</v>
       </c>
       <c r="H28" t="n">
-        <v>48.47</v>
+        <v>62.92</v>
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.607</v>
+        <v>0.717</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.605</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1757,28 +1757,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>7.81</v>
+        <v>0.3</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>-0.0225</v>
+        <v>-0.0476</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>5469000</v>
+        <v>6428200</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="H29" t="n">
-        <v>51.27</v>
+        <v>56.45</v>
       </c>
       <c r="I29" s="16" t="inlineStr">
         <is>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>7.806</v>
+        <v>0.286</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>7.736</v>
+        <v>0.277</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1802,28 +1802,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>4.75</v>
+        <v>0.24</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0204</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5238000</v>
+        <v>6280500</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.3</v>
+        <v>2.17</v>
       </c>
       <c r="H30" t="n">
-        <v>35.75</v>
+        <v>41.53</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>4.836</v>
+        <v>0.258</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>4.953</v>
+        <v>0.251</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1847,28 +1847,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0370</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>XPB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>0.04650000000000001</v>
+        <v>2.3</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>-0.0171</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>5086900</v>
+        <v>6241500</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.47</v>
+        <v>0.38</v>
       </c>
       <c r="H31" t="n">
-        <v>67.76000000000001</v>
+        <v>47.67</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.204</v>
+        <v>2.343</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.18</v>
+        <v>2.245</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1892,39 +1892,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PTT</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>0.0071</v>
+        <v>7.81</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>-0.0225</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>5066500</v>
+        <v>6089200</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>7.17</v>
+        <v>0.49</v>
       </c>
       <c r="H32" t="n">
-        <v>44.62</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.27</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>1.44</v>
+        <v>7.806</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>1.431</v>
+        <v>7.736</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1937,28 +1937,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0213</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>MTAG</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.41</v>
+        <v>0.215</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>-0.012</v>
+        <v>-0.0227</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>4996500</v>
+        <v>6071800</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.46</v>
+        <v>13.07</v>
       </c>
       <c r="H33" t="n">
-        <v>51.13</v>
+        <v>54.9</v>
       </c>
       <c r="I33" s="16" t="inlineStr">
         <is>
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.409</v>
+        <v>0.209</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.411</v>
+        <v>0.216</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1982,28 +1982,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.21</v>
+        <v>4.75</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>-0.0233</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4818700</v>
+        <v>5769600</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="H34" t="n">
-        <v>27.87</v>
+        <v>35.75</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.236</v>
+        <v>4.836</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.248</v>
+        <v>4.953</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2027,39 +2027,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>10.08</v>
+        <v>0.21</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0233</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>4678000</v>
+        <v>5764500</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="H35" t="n">
-        <v>41.49</v>
-      </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.87</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>10.166</v>
+        <v>0.236</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>10.308</v>
+        <v>0.248</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2072,39 +2072,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>COMPUGT</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>-0.0227</v>
+        <v>0.015</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4597700</v>
+        <v>5696900</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.21</v>
+        <v>5.36</v>
       </c>
       <c r="H36" t="n">
-        <v>64.98999999999999</v>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.63</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.204</v>
+        <v>0.016</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.185</v>
+        <v>0.016</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2117,28 +2117,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.24</v>
+        <v>0.215</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>-0.0204</v>
+        <v>-0.0227</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4469800</v>
+        <v>5311500</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="H37" t="n">
-        <v>30.69</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="I37" s="16" t="inlineStr">
         <is>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.273</v>
+        <v>0.204</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.325</v>
+        <v>0.185</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2162,39 +2162,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>-0.0128</v>
+        <v>0.225</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>4467600</v>
+        <v>5223900</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.2</v>
+        <v>1.51</v>
       </c>
       <c r="H38" t="n">
-        <v>53.94</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.76000000000001</v>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.382</v>
+        <v>0.204</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.322</v>
+        <v>0.18</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2207,28 +2207,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.555</v>
+        <v>2.85</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>-0.0089</v>
+        <v>-0.0206</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>4439600</v>
+        <v>5105400</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="H39" t="n">
-        <v>69.81</v>
+        <v>60.84</v>
       </c>
       <c r="I39" s="16" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.482</v>
+        <v>2.774</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.406</v>
+        <v>2.637</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2252,39 +2252,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>-0.0172</v>
+        <v>1.41</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4358800</v>
+        <v>5066500</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.31</v>
+        <v>7.17</v>
       </c>
       <c r="H40" t="n">
-        <v>62.01</v>
-      </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.62</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>2.775</v>
+        <v>1.44</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>2.637</v>
+        <v>1.431</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2297,28 +2297,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>JADI</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>0</v>
+        <v>0.03</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>0.2</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4334100</v>
+        <v>5027500</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.26</v>
+        <v>8.06</v>
       </c>
       <c r="H41" t="n">
-        <v>45.92</v>
+        <v>49.31</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>2.122</v>
+        <v>0.03</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>2.064</v>
+        <v>0.033</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2342,28 +2342,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>1.79</v>
+        <v>10.08</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4333800</v>
+        <v>5026100</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.18</v>
+        <v>0.43</v>
       </c>
       <c r="H42" t="n">
-        <v>58.11</v>
+        <v>41.49</v>
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>1.74</v>
+        <v>10.166</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>1.538</v>
+        <v>10.308</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2387,28 +2387,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>2.49</v>
+        <v>0.41</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>-0.008</v>
+        <v>-0.012</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4230900</v>
+        <v>4996500</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.28</v>
+        <v>0.46</v>
       </c>
       <c r="H43" t="n">
-        <v>59.77</v>
+        <v>51.13</v>
       </c>
       <c r="I43" s="16" t="inlineStr">
         <is>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2.445</v>
+        <v>0.409</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>2.286</v>
+        <v>0.411</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2432,28 +2432,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.0588</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4206600</v>
+        <v>4940800</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.3</v>
+        <v>1.13</v>
       </c>
       <c r="H44" t="n">
-        <v>61.06</v>
+        <v>65.03</v>
       </c>
       <c r="I44" s="16" t="inlineStr">
         <is>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.527</v>
+        <v>0.34</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.48</v>
+        <v>0.333</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2477,39 +2477,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>0.0467</v>
+        <v>0.24</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3982900</v>
+        <v>4905800</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.68</v>
+        <v>0.17</v>
       </c>
       <c r="H45" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>30.69</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.766</v>
+        <v>0.273</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.753</v>
+        <v>0.325</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2522,39 +2522,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>0</v>
+        <v>0.555</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>-0.0089</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3967100</v>
+        <v>4837000</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.09</v>
+        <v>0.33</v>
       </c>
       <c r="H46" t="n">
-        <v>51.13</v>
-      </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.81</v>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.736</v>
+        <v>0.482</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.406</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2567,39 +2567,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.235</v>
+        <v>0.385</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>-0.0208</v>
+        <v>-0.0128</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3939300</v>
+        <v>4792000</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0.22</v>
       </c>
       <c r="H47" t="n">
-        <v>52.63</v>
-      </c>
-      <c r="I47" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.94</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.232</v>
+        <v>0.382</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.233</v>
+        <v>0.322</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,39 +2612,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>0.0441</v>
+        <v>3.45</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>-0.0143</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3925000</v>
+        <v>4663000</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="H48" t="n">
-        <v>62.57</v>
-      </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.69</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.34</v>
+        <v>3.6</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.333</v>
+        <v>3.699</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2657,28 +2657,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.235</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3863500</v>
+        <v>4643200</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="H49" t="n">
-        <v>74.22</v>
+        <v>52.63</v>
       </c>
       <c r="I49" s="16" t="inlineStr">
         <is>
@@ -2686,10 +2686,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>1.012</v>
+        <v>0.232</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.853</v>
+        <v>0.233</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2702,39 +2702,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.175</v>
+        <v>2.08</v>
       </c>
       <c r="E50" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3854100</v>
+        <v>4578200</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.76</v>
+        <v>0.28</v>
       </c>
       <c r="H50" t="n">
-        <v>59.06</v>
-      </c>
-      <c r="I50" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.92</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.164</v>
+        <v>2.122</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.165</v>
+        <v>2.064</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2747,28 +2747,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.29</v>
+        <v>1.79</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>-0.0169</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3811000</v>
+        <v>4557400</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.61</v>
+        <v>0.19</v>
       </c>
       <c r="H51" t="n">
-        <v>61.78</v>
+        <v>58.11</v>
       </c>
       <c r="I51" s="16" t="inlineStr">
         <is>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.276</v>
+        <v>1.74</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.27</v>
+        <v>1.538</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,39 +2792,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SUNSURIA</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>-0.0175</v>
+        <v>4.74</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3716900</v>
+        <v>4427100</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>54.86</v>
+        <v>0.52</v>
       </c>
       <c r="H52" t="n">
-        <v>51.15</v>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.6</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.278</v>
+        <v>4.74</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.282</v>
+        <v>4.592</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2837,39 +2837,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>4.73</v>
+        <v>0.475</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>0.0064</v>
+        <v>0.0215</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3635900</v>
+        <v>4377800</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.43</v>
+        <v>0.19</v>
       </c>
       <c r="H53" t="n">
-        <v>51.78</v>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.69</v>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>4.739</v>
+        <v>0.468</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>4.591</v>
+        <v>0.471</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2882,28 +2882,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SUNSURIA</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.365</v>
+        <v>0.27</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>-0.0135</v>
+        <v>-0.0526</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>3457100</v>
+        <v>4218900</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.57</v>
+        <v>62.27</v>
       </c>
       <c r="H54" t="n">
-        <v>48.25</v>
+        <v>44.26</v>
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.367</v>
+        <v>0.277</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.367</v>
+        <v>0.281</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2927,39 +2927,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>-0.008100000000000001</v>
+        <v>1.1</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>0.0185</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3413100</v>
+        <v>4125000</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="H55" t="n">
-        <v>62.17</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.22</v>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>4.757</v>
+        <v>1.013</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>4.524</v>
+        <v>0.853</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2972,39 +2972,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E56" s="17" t="n">
-        <v>0</v>
+        <v>0.785</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0.0467</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3318900</v>
+        <v>4073700</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="H56" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.4</v>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.772</v>
+        <v>0.766</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.773</v>
+        <v>0.753</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3017,28 +3017,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>-0.0165</v>
+        <v>0.765</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3255400</v>
+        <v>3878500</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="H57" t="n">
-        <v>34.5</v>
+        <v>46.13</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.633</v>
+        <v>0.772</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.657</v>
+        <v>0.773</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3062,28 +3062,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>-0.0339</v>
+        <v>0.175</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3156900</v>
+        <v>3861600</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.47</v>
+        <v>0.76</v>
       </c>
       <c r="H58" t="n">
-        <v>45.29</v>
+        <v>59.06</v>
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>1.178</v>
+        <v>0.164</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1.145</v>
+        <v>0.165</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3107,28 +3107,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>5.76</v>
+        <v>0.29</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>-0.0035</v>
+        <v>-0.0169</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3127100</v>
+        <v>3851000</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.22</v>
+        <v>0.61</v>
       </c>
       <c r="H59" t="n">
-        <v>57.15</v>
+        <v>61.78</v>
       </c>
       <c r="I59" s="16" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>5.691</v>
+        <v>0.276</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>5.161</v>
+        <v>0.27</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3152,28 +3152,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>1.3</v>
+        <v>5.77</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>-0.0152</v>
+        <v>-0.0017</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3097200</v>
+        <v>3736800</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H60" t="n">
-        <v>38.68</v>
+        <v>57.61</v>
       </c>
       <c r="I60" s="16" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>1.328</v>
+        <v>5.692</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>1.438</v>
+        <v>5.161</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3197,28 +3197,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>12.94</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>0.0023</v>
+        <v>0.145</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3026400</v>
+        <v>3733200</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.38</v>
+        <v>0.09</v>
       </c>
       <c r="H61" t="n">
-        <v>32.93</v>
+        <v>45.61</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>13.185</v>
+        <v>0.157</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>13.77</v>
+        <v>0.148</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3242,39 +3242,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v>0.0278</v>
+        <v>4.89</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2943600</v>
+        <v>3625800</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H62" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="I62" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.94</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>4.759</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.616</v>
+        <v>4.525</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3287,39 +3287,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>7.68</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>-0.0204</v>
+        <v>12.94</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>0.0023</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2934500</v>
+        <v>3525200</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.27</v>
+        <v>0.45</v>
       </c>
       <c r="H63" t="n">
-        <v>30.95</v>
-      </c>
-      <c r="I63" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>32.93</v>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>7.948</v>
+        <v>13.185</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>8.25</v>
+        <v>13.77</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3332,28 +3332,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E64" s="15" t="n">
-        <v>0.0156</v>
+        <v>7.68</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2854100</v>
+        <v>3463100</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.85</v>
+        <v>0.32</v>
       </c>
       <c r="H64" t="n">
-        <v>35.32</v>
+        <v>30.95</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.384</v>
+        <v>7.948</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.371</v>
+        <v>8.25</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3377,28 +3377,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E65" s="15" t="n">
-        <v>0.0156</v>
+        <v>0.365</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2778500</v>
+        <v>3457100</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="H65" t="n">
-        <v>95.48</v>
+        <v>48.25</v>
       </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.919</v>
+        <v>0.367</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.746</v>
+        <v>0.367</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3422,39 +3422,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E66" s="17" t="n">
-        <v>0</v>
+        <v>0.595</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2730200</v>
+        <v>3402900</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.12</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.5</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.467</v>
+        <v>0.633</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.471</v>
+        <v>0.657</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3467,28 +3467,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E67" s="15" t="n">
-        <v>0.0109</v>
+        <v>1.15</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>-0.0254</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2693300</v>
+        <v>3400300</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.78</v>
+        <v>0.51</v>
       </c>
       <c r="H67" t="n">
-        <v>47.5</v>
+        <v>46.5</v>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.928</v>
+        <v>1.178</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.969</v>
+        <v>1.145</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3512,39 +3512,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>-0.0263</v>
+        <v>0.745</v>
+      </c>
+      <c r="E68" s="15" t="n">
+        <v>0.0347</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2596200</v>
+        <v>3308500</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="H68" t="n">
-        <v>35.59</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.13</v>
+      </c>
+      <c r="I68" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>1.268</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>1.302</v>
+        <v>0.616</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3557,39 +3557,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>3.44</v>
+        <v>1.31</v>
       </c>
       <c r="E69" s="10" t="n">
-        <v>-0.0171</v>
+        <v>-0.0076</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2537400</v>
+        <v>3202000</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.52</v>
+        <v>0.28</v>
       </c>
       <c r="H69" t="n">
-        <v>34.15</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.38</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>3.599</v>
+        <v>1.329</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>3.699</v>
+        <v>1.438</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3602,39 +3602,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.74</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2529500</v>
+        <v>3158900</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.37</v>
+        <v>0.54</v>
       </c>
       <c r="H70" t="n">
-        <v>37.74</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.73999999999999</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>7.667</v>
+        <v>0.678</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>7.835</v>
+        <v>0.619</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3647,39 +3647,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>0</v>
+        <v>0.325</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2525700</v>
+        <v>2964100</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.46</v>
+        <v>0.88</v>
       </c>
       <c r="H71" t="n">
-        <v>51</v>
-      </c>
-      <c r="I71" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.32</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.214</v>
+        <v>0.384</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.212</v>
+        <v>0.371</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3701,19 +3701,19 @@
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>-0.0051</v>
+        <v>1.95</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2522700</v>
+        <v>2863600</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H72" t="n">
-        <v>44.13</v>
+        <v>45.43</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>1.979</v>
+        <v>1.98</v>
       </c>
       <c r="K72" s="9" t="n">
         <v>1.972</v>
@@ -3737,39 +3737,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>-0.08470000000000001</v>
+        <v>-0.0233</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2369100</v>
+        <v>2850700</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.27</v>
+        <v>0.51</v>
       </c>
       <c r="H73" t="n">
-        <v>56.32</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.8</v>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.264</v>
+        <v>0.214</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.222</v>
+        <v>0.212</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3782,39 +3782,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="E74" s="15" t="n">
-        <v>0.024</v>
+        <v>0.0156</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2360300</v>
+        <v>2830000</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.88</v>
+        <v>0.48</v>
       </c>
       <c r="H74" t="n">
-        <v>37.76</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>95.48</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.388</v>
+        <v>0.919</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1.317</v>
+        <v>0.746</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3827,39 +3827,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>0</v>
+        <v>0.93</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2346900</v>
+        <v>2792400</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H75" t="n">
-        <v>37.51</v>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.5</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>1.986</v>
+        <v>0.928</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.103</v>
+        <v>0.969</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3872,28 +3872,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>-0.0106</v>
+        <v>0.415</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>0.0506</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2278000</v>
+        <v>2791000</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.49</v>
+        <v>1.65</v>
       </c>
       <c r="H76" t="n">
-        <v>68.43000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="I76" s="16" t="inlineStr">
         <is>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.888</v>
+        <v>0.375</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.852</v>
+        <v>0.342</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3917,28 +3917,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <v>0.0263</v>
+        <v>1.23</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>-0.0184</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2149300</v>
+        <v>2744800</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.52</v>
+        <v>0.55</v>
       </c>
       <c r="H77" t="n">
-        <v>42.8</v>
+        <v>37.37</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.794</v>
+        <v>1.269</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.846</v>
+        <v>1.302</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3962,39 +3962,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>0.0175</v>
+        <v>7.45</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2072000</v>
+        <v>2657700</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.92</v>
+        <v>0.39</v>
       </c>
       <c r="H78" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="I78" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.74</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>2.314</v>
+        <v>7.667</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.974</v>
+        <v>7.835</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4007,28 +4007,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>0</v>
+        <v>0.93</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2021000</v>
+        <v>2619800</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.34</v>
+        <v>0.57</v>
       </c>
       <c r="H79" t="n">
-        <v>48.43</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="I79" s="16" t="inlineStr">
         <is>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>2.567</v>
+        <v>0.888</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>2.54</v>
+        <v>0.852</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4052,39 +4052,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E80" s="17" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>0.0197</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2020800</v>
+        <v>2530100</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.18</v>
+        <v>0.62</v>
       </c>
       <c r="H80" t="n">
-        <v>36.09</v>
-      </c>
-      <c r="I80" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.27</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.27</v>
+        <v>0.794</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.313</v>
+        <v>0.846</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4097,31 +4097,40 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BPROP</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E81" s="17" t="n">
-        <v>0</v>
+        <v>1.28</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0.024</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1939500</v>
-      </c>
-      <c r="G81" s="12" t="n"/>
+        <v>2483800</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H81" t="n">
+        <v>37.76</v>
+      </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J81" s="9" t="n"/>
-      <c r="K81" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>1.388</v>
+      </c>
+      <c r="K81" s="9" t="n">
+        <v>1.317</v>
+      </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
     </row>
@@ -4133,39 +4142,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0191</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CABNET</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E82" s="15" t="n">
-        <v>0.1064</v>
+        <v>0.275</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>-0.0678</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1918600</v>
+        <v>2473100</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>11.91</v>
+        <v>0.28</v>
       </c>
       <c r="H82" t="n">
-        <v>69.84999999999999</v>
-      </c>
-      <c r="I82" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.4</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.221</v>
+        <v>0.265</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.216</v>
+        <v>0.222</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4178,28 +4187,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.465</v>
+        <v>0.7</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>-0.0106</v>
+        <v>-0.0071</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1905600</v>
+        <v>2439200</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.7</v>
+        <v>0.32</v>
       </c>
       <c r="H83" t="n">
-        <v>52.58</v>
+        <v>54.06</v>
       </c>
       <c r="I83" s="16" t="inlineStr">
         <is>
@@ -4207,10 +4216,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.464</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.462</v>
+        <v>0.664</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4223,39 +4232,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.265</v>
+        <v>1.95</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>0.0192</v>
+        <v>0.0052</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1885700</v>
+        <v>2385500</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>1.54</v>
+        <v>0.78</v>
       </c>
       <c r="H84" t="n">
-        <v>74.73999999999999</v>
-      </c>
-      <c r="I84" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.56</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.217</v>
+        <v>1.987</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.2</v>
+        <v>2.103</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4268,39 +4277,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>-0.006500000000000001</v>
+        <v>2.93</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>0.0245</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1858300</v>
+        <v>2292100</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.63</v>
+        <v>1.01</v>
       </c>
       <c r="H85" t="n">
-        <v>38.15</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>90.11</v>
+      </c>
+      <c r="I85" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>1.579</v>
+        <v>2.316</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1.644</v>
+        <v>1.974</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4313,28 +4322,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>3</v>
+        <v>0.665</v>
       </c>
       <c r="E86" s="15" t="n">
-        <v>0.0345</v>
+        <v>0.031</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1853800</v>
+        <v>2118400</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.71</v>
+        <v>0.22</v>
       </c>
       <c r="H86" t="n">
-        <v>90.48999999999999</v>
+        <v>59.67</v>
       </c>
       <c r="I86" s="16" t="inlineStr">
         <is>
@@ -4342,10 +4351,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>2.265</v>
+        <v>0.635</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1.8</v>
+        <v>0.577</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4358,28 +4367,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="E87" s="15" t="n">
-        <v>0.0345</v>
+        <v>0.0276</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1826500</v>
+        <v>2093000</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.53</v>
+        <v>0.8</v>
       </c>
       <c r="H87" t="n">
-        <v>57.26</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="I87" s="16" t="inlineStr">
         <is>
@@ -4387,9 +4396,11 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>2.874</v>
-      </c>
-      <c r="K87" s="9" t="n"/>
+        <v>2.263</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>1.8</v>
+      </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
     </row>
@@ -4401,28 +4412,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>-0.0139</v>
+        <v>2.56</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1824100</v>
+        <v>2084100</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="H88" t="n">
-        <v>62.3</v>
+        <v>49.47</v>
       </c>
       <c r="I88" s="16" t="inlineStr">
         <is>
@@ -4430,10 +4441,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.338</v>
+        <v>2.568</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.32</v>
+        <v>2.54</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4446,28 +4457,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.41</v>
+        <v>0.255</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>0.038</v>
+        <v>0.02</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1820800</v>
+        <v>2071300</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>1.08</v>
+        <v>0.18</v>
       </c>
       <c r="H89" t="n">
-        <v>69</v>
+        <v>38.96</v>
       </c>
       <c r="I89" s="16" t="inlineStr">
         <is>
@@ -4475,10 +4486,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.374</v>
+        <v>0.27</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.342</v>
+        <v>0.313</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4491,39 +4502,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E90" s="15" t="n">
-        <v>0.0208</v>
+        <v>0.615</v>
+      </c>
+      <c r="E90" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1743800</v>
+        <v>1999000</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.3</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H90" t="n">
-        <v>69.98</v>
-      </c>
-      <c r="I90" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.06</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.677</v>
+        <v>0.609</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.619</v>
+        <v>0.59</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4536,39 +4547,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>-0.0181</v>
+        <v>0.265</v>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1678200</v>
+        <v>1967700</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.27</v>
+        <v>1.61</v>
       </c>
       <c r="H91" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>74.73999999999999</v>
+      </c>
+      <c r="I91" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>1.723</v>
+        <v>0.217</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.839</v>
+        <v>0.2</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4581,28 +4592,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" s="15" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>1957400</v>
+      </c>
+      <c r="G92" s="12" t="n">
         <v>0.57</v>
       </c>
-      <c r="E92" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="11" t="n">
-        <v>1630500</v>
-      </c>
-      <c r="G92" s="12" t="n">
-        <v>0.45</v>
-      </c>
       <c r="H92" t="n">
-        <v>49.26</v>
+        <v>57.26</v>
       </c>
       <c r="I92" s="16" t="inlineStr">
         <is>
@@ -4610,11 +4621,9 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="K92" s="9" t="n">
-        <v>0.594</v>
-      </c>
+        <v>2.874</v>
+      </c>
+      <c r="K92" s="9" t="n"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
     </row>
@@ -4626,40 +4635,31 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>BPROP</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>-0.0116</v>
+        <v>0.245</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1625400</v>
-      </c>
-      <c r="G93" s="12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H93" t="n">
-        <v>41.37</v>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J93" s="9" t="n">
-        <v>0.431</v>
-      </c>
-      <c r="K93" s="9" t="n">
-        <v>0.452</v>
-      </c>
+        <v>1940500</v>
+      </c>
+      <c r="G93" s="12" t="n"/>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n"/>
+      <c r="K93" s="9" t="n"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
     </row>
@@ -4671,39 +4671,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SENDAI</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.275</v>
+        <v>1.55</v>
       </c>
       <c r="E94" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1533400</v>
+        <v>1924100</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.9</v>
+        <v>0.65</v>
       </c>
       <c r="H94" t="n">
-        <v>59.56</v>
-      </c>
-      <c r="I94" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.82</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.259</v>
+        <v>1.58</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.268</v>
+        <v>1.645</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4716,39 +4716,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0191</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>CABNET</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>-0.0101</v>
+        <v>0.26</v>
+      </c>
+      <c r="E95" s="15" t="n">
+        <v>0.1064</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1515400</v>
+        <v>1923800</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.35</v>
+        <v>11.94</v>
       </c>
       <c r="H95" t="n">
-        <v>32.17</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.84999999999999</v>
+      </c>
+      <c r="I95" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.043</v>
+        <v>0.221</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1.074</v>
+        <v>0.216</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4761,28 +4761,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.695</v>
+        <v>0.465</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>-0.0142</v>
+        <v>-0.0106</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1492500</v>
+        <v>1905600</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="H96" t="n">
-        <v>53.05</v>
+        <v>52.58</v>
       </c>
       <c r="I96" s="16" t="inlineStr">
         <is>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.464</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.664</v>
+        <v>0.462</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4806,33 +4806,40 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E97" s="17" t="n">
-        <v>0</v>
+        <v>1.64</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1491800</v>
+        <v>1897800</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I97" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J97" s="9" t="n"/>
-      <c r="K97" s="9" t="n"/>
+        <v>0.3</v>
+      </c>
+      <c r="H97" t="n">
+        <v>33.89</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>1.724</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>1.839</v>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
     </row>
@@ -4844,39 +4851,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>5.55</v>
+        <v>0.355</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>-0.0107</v>
+        <v>-0.0139</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1479200</v>
+        <v>1859700</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.49</v>
+        <v>0.27</v>
       </c>
       <c r="H98" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.3</v>
+      </c>
+      <c r="I98" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>5.77</v>
+        <v>0.338</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>5.767</v>
+        <v>0.32</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4889,39 +4896,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E99" s="15" t="n">
-        <v>0.0347</v>
+        <v>0.345</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>-0.0417</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1429300</v>
+        <v>1744500</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.42</v>
+        <v>1</v>
       </c>
       <c r="H99" t="n">
-        <v>65</v>
-      </c>
-      <c r="I99" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.4</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.712</v>
+        <v>0.353</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.713</v>
+        <v>0.32</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4934,39 +4941,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>-0.0213</v>
+        <v>0.755</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>0.0486</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1405800</v>
+        <v>1744300</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.86</v>
+        <v>0.52</v>
       </c>
       <c r="H100" t="n">
-        <v>41.61</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.68000000000001</v>
+      </c>
+      <c r="I100" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.24</v>
+        <v>0.712</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.244</v>
+        <v>0.713</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4979,39 +4986,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.87</v>
+        <v>6.19</v>
       </c>
       <c r="E101" s="15" t="n">
-        <v>0.0058</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1405500</v>
+        <v>1728700</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="H101" t="n">
-        <v>63.83</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.64</v>
+      </c>
+      <c r="I101" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.86</v>
+        <v>6.29</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.856</v>
+        <v>6.483</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5033,19 +5040,19 @@
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>-0.0105</v>
+        <v>-0.0158</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1391800</v>
+        <v>1670400</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="H102" t="n">
-        <v>35.9</v>
+        <v>34.96</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -5053,10 +5060,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>1.95</v>
+        <v>1.949</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>2.073</v>
+        <v>2.072</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5084,10 +5091,10 @@
         <v>-0.0259</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1360600</v>
+        <v>1650400</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="H103" t="n">
         <v>47.24</v>
@@ -5114,28 +5121,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>4.38</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>-0.009000000000000001</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1358200</v>
+        <v>1634300</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.11</v>
+        <v>0.45</v>
       </c>
       <c r="H104" t="n">
-        <v>77.93000000000001</v>
+        <v>46.45</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
@@ -5143,10 +5150,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>3.606</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>2.415</v>
+        <v>0.594</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5159,28 +5166,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>SENDAI</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="E105" s="15" t="n">
-        <v>0.0408</v>
+        <v>0.275</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1351700</v>
+        <v>1626500</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.55</v>
+        <v>0.95</v>
       </c>
       <c r="H105" t="n">
-        <v>72.5</v>
+        <v>59.56</v>
       </c>
       <c r="I105" s="16" t="inlineStr">
         <is>
@@ -5188,10 +5195,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>2.97</v>
+        <v>0.259</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>2.548</v>
+        <v>0.268</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5204,39 +5211,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>0</v>
+        <v>0.425</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>-0.0116</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1348400</v>
+        <v>1625400</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="H106" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.37</v>
+      </c>
+      <c r="I106" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.261</v>
+        <v>0.431</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.266</v>
+        <v>0.452</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5249,39 +5256,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E107" s="15" t="n">
-        <v>0.007900000000000001</v>
+        <v>5.55</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>-0.0107</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1344800</v>
+        <v>1610500</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="H107" t="n">
-        <v>84.36</v>
-      </c>
-      <c r="I107" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.8</v>
+      </c>
+      <c r="I107" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>1.067</v>
+        <v>5.77</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.9</v>
+        <v>5.767</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5294,28 +5301,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>1.73</v>
+        <v>4.4</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>-0.0226</v>
+        <v>-0.004500000000000001</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1331700</v>
+        <v>1601500</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="H108" t="n">
-        <v>44.47</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="I108" s="16" t="inlineStr">
         <is>
@@ -5323,10 +5330,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>1.768</v>
+        <v>3.608</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>1.803</v>
+        <v>2.415</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5339,28 +5346,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="E109" s="15" t="n">
-        <v>0.0049</v>
+        <v>0.29</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1310000</v>
+        <v>1571200</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="H109" t="n">
-        <v>39.02</v>
+        <v>39.08</v>
       </c>
       <c r="I109" s="16" t="inlineStr">
         <is>
@@ -5368,10 +5375,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>6.289</v>
+        <v>0.297</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>6.483</v>
+        <v>0.311</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5384,28 +5391,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.35</v>
+        <v>0.61</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>-0.0278</v>
+        <v>-0.0161</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1296100</v>
+        <v>1569800</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H110" t="n">
-        <v>52.48</v>
+        <v>39.14</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -5413,10 +5420,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.353</v>
+        <v>0.635</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.321</v>
+        <v>0.634</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5429,39 +5436,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.285</v>
+        <v>0.985</v>
       </c>
       <c r="E111" s="10" t="n">
-        <v>-0.0172</v>
+        <v>-0.0101</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1281100</v>
+        <v>1554000</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="H111" t="n">
-        <v>35.65</v>
-      </c>
-      <c r="I111" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.17</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.297</v>
+        <v>1.043</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.311</v>
+        <v>1.074</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5474,28 +5481,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>AXREIT</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>-0.0241</v>
+        <v>1.8</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1276200</v>
+        <v>1516500</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.22</v>
+        <v>1.12</v>
       </c>
       <c r="H112" t="n">
-        <v>51.65</v>
+        <v>46.97</v>
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
@@ -5503,10 +5510,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.402</v>
+        <v>1.811</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.401</v>
+        <v>1.845</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5519,28 +5526,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E113" s="15" t="n">
-        <v>0.0155</v>
+        <v>1.73</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>-0.0226</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1228600</v>
+        <v>1508100</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
       </c>
       <c r="H113" t="n">
-        <v>57.9</v>
+        <v>44.47</v>
       </c>
       <c r="I113" s="16" t="inlineStr">
         <is>
@@ -5548,10 +5555,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.634</v>
+        <v>1.768</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.577</v>
+        <v>1.803</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5564,40 +5571,33 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E114" s="15" t="n">
-        <v>0.0244</v>
+        <v>0.48</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1196500</v>
+        <v>1491800</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="H114" t="n">
-        <v>74.09</v>
+        <v>0.08</v>
       </c>
       <c r="I114" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J114" s="9" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="K114" s="9" t="n">
-        <v>0.495</v>
-      </c>
+      <c r="J114" s="9" t="n"/>
+      <c r="K114" s="9" t="n"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
     </row>
@@ -5609,28 +5609,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E115" s="10" t="n">
-        <v>-0.008100000000000001</v>
+        <v>0.2</v>
+      </c>
+      <c r="E115" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1188800</v>
+        <v>1487700</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.49</v>
+        <v>1.47</v>
       </c>
       <c r="H115" t="n">
-        <v>40.73</v>
+        <v>37.51</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.635</v>
+        <v>0.205</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.634</v>
+        <v>0.214</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5654,28 +5654,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>9.890000000000001</v>
+        <v>3.34</v>
       </c>
       <c r="E116" s="15" t="n">
-        <v>0.003</v>
+        <v>0.047</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1152100</v>
+        <v>1468800</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.36</v>
+        <v>0.59</v>
       </c>
       <c r="H116" t="n">
-        <v>64.43000000000001</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="I116" s="16" t="inlineStr">
         <is>
@@ -5683,10 +5683,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>9.567</v>
+        <v>2.972</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>9.106</v>
+        <v>2.548</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5699,39 +5699,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="E117" s="15" t="n">
-        <v>0.0097</v>
+        <v>0.23</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1149500</v>
+        <v>1442300</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.14</v>
+        <v>0.88</v>
       </c>
       <c r="H117" t="n">
-        <v>76.08</v>
-      </c>
-      <c r="I117" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.61</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.906</v>
+        <v>0.24</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.767</v>
+        <v>0.244</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5744,39 +5744,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>-0.0118</v>
+        <v>0.87</v>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1144100</v>
+        <v>1405500</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="H118" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="I118" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.83</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.396</v>
+        <v>0.86</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.381</v>
+        <v>0.856</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5789,39 +5789,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>2.71</v>
+        <v>1.27</v>
       </c>
       <c r="E119" s="15" t="n">
-        <v>0.0074</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1139500</v>
+        <v>1397300</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.24</v>
+        <v>0.53</v>
       </c>
       <c r="H119" t="n">
-        <v>81.56</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.36</v>
+      </c>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>2.484</v>
+        <v>1.067</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>2.139</v>
+        <v>0.9</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5834,39 +5834,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>-0.039</v>
+        <v>9.94</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1123400</v>
+        <v>1378600</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.95</v>
+        <v>0.43</v>
       </c>
       <c r="H120" t="n">
-        <v>41.08</v>
-      </c>
-      <c r="I120" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.47</v>
+      </c>
+      <c r="I120" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.386</v>
+        <v>9.571999999999999</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.393</v>
+        <v>9.106999999999999</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5879,28 +5879,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0342</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>RTECH</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.25</v>
+        <v>0.64</v>
       </c>
       <c r="E121" s="15" t="n">
-        <v>0.0417</v>
+        <v>0.0407</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1116900</v>
+        <v>1353500</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>1.37</v>
+        <v>0.91</v>
       </c>
       <c r="H121" t="n">
-        <v>67</v>
+        <v>75.47</v>
       </c>
       <c r="I121" s="16" t="inlineStr">
         <is>
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.231</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.215</v>
+        <v>0.496</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5924,28 +5924,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.26</v>
+      </c>
+      <c r="E122" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1078900</v>
+        <v>1348400</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.28</v>
+        <v>1.73</v>
       </c>
       <c r="H122" t="n">
-        <v>36.42</v>
+        <v>45.51</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.585</v>
+        <v>0.261</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.587</v>
+        <v>0.266</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5969,39 +5969,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>-0.0133</v>
+        <v>1.05</v>
+      </c>
+      <c r="E123" s="15" t="n">
+        <v>0.0194</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1053900</v>
+        <v>1294600</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="H123" t="n">
-        <v>52.06</v>
-      </c>
-      <c r="I123" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.75</v>
+      </c>
+      <c r="I123" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>2.227</v>
+        <v>0.907</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>2.108</v>
+        <v>0.767</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6014,39 +6014,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>1.04</v>
+        <v>0.405</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>-0.0095</v>
+        <v>-0.0241</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1048500</v>
+        <v>1286200</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.1</v>
+        <v>0.23</v>
       </c>
       <c r="H124" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.65</v>
+      </c>
+      <c r="I124" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>1.077</v>
+        <v>0.402</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>1.025</v>
+        <v>0.401</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6059,28 +6059,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1.09</v>
+        <v>0.42</v>
       </c>
       <c r="E125" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1046600</v>
+        <v>1270200</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="H125" t="n">
-        <v>76.75</v>
+        <v>43.62</v>
       </c>
       <c r="I125" s="16" t="inlineStr">
         <is>
@@ -6088,10 +6088,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.984</v>
+        <v>0.437</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.434</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6104,39 +6104,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E126" s="17" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1023900</v>
+        <v>1260200</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.4</v>
+        <v>1.07</v>
       </c>
       <c r="H126" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="I126" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.52</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>2.061</v>
+        <v>0.386</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>2.104</v>
+        <v>0.393</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6149,28 +6149,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>4.31</v>
+        <v>0.42</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>-0.0401</v>
+        <v>-0.0118</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>983700</v>
+        <v>1181100</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="H127" t="n">
-        <v>47.02</v>
+        <v>65.7</v>
       </c>
       <c r="I127" s="16" t="inlineStr">
         <is>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>4.4</v>
+        <v>0.396</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>4.426</v>
+        <v>0.381</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6194,28 +6194,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>-0.009300000000000001</v>
+        <v>-0.019</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>981200</v>
+        <v>1178100</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="H128" t="n">
-        <v>31.18</v>
+        <v>44.58</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.11</v>
+        <v>1.076</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.148</v>
+        <v>1.024</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6239,39 +6239,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>-0.0156</v>
+        <v>2.73</v>
+      </c>
+      <c r="E129" s="15" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>933100</v>
+        <v>1166600</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.71</v>
+        <v>0.25</v>
       </c>
       <c r="H129" t="n">
-        <v>46.62</v>
-      </c>
-      <c r="I129" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>82.23999999999999</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.634</v>
+        <v>2.486</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.629</v>
+        <v>2.14</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6284,28 +6284,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>1.49</v>
+        <v>4.33</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>-0.0132</v>
+        <v>-0.0356</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>910200</v>
+        <v>1147500</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
       <c r="H130" t="n">
-        <v>30.4</v>
+        <v>47.65</v>
       </c>
       <c r="I130" s="16" t="inlineStr">
         <is>
@@ -6313,10 +6313,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>1.554</v>
+        <v>4.402</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>1.668</v>
+        <v>4.427</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6329,28 +6329,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>-0.0129</v>
+        <v>1.1</v>
+      </c>
+      <c r="E131" s="15" t="n">
+        <v>0.0092</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>905900</v>
+        <v>1145500</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.63</v>
+        <v>0.24</v>
       </c>
       <c r="H131" t="n">
-        <v>50.64</v>
+        <v>77.52</v>
       </c>
       <c r="I131" s="16" t="inlineStr">
         <is>
@@ -6358,10 +6358,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.765</v>
+        <v>0.985</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.755</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6374,39 +6374,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="E132" s="10" t="n">
-        <v>-0.0234</v>
+        <v>3.64</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>898400</v>
+        <v>1145400</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="H132" t="n">
-        <v>36.85</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.63</v>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>1.749</v>
+        <v>3.343</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1.853</v>
+        <v>2.91</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6419,28 +6419,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E133" s="17" t="n">
-        <v>0</v>
+        <v>0.57</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>892800</v>
+        <v>1143600</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="H133" t="n">
-        <v>31.36</v>
+        <v>36.42</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6448,10 +6448,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>1.082</v>
+        <v>0.585</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>1.26</v>
+        <v>0.587</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6464,28 +6464,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>0342</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>RTECH</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>1.28</v>
+        <v>0.25</v>
       </c>
       <c r="E134" s="15" t="n">
-        <v>0.0159</v>
+        <v>0.0417</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>881800</v>
+        <v>1136900</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.58</v>
+        <v>1.39</v>
       </c>
       <c r="H134" t="n">
-        <v>47.78</v>
+        <v>67</v>
       </c>
       <c r="I134" s="16" t="inlineStr">
         <is>
@@ -6493,10 +6493,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>1.28</v>
+        <v>0.231</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>1.34</v>
+        <v>0.215</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6509,28 +6509,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.63</v>
+        <v>0.255</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>-0.0156</v>
+        <v>-0.0192</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>879400</v>
+        <v>1126300</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="H135" t="n">
-        <v>54.69</v>
+        <v>48.39</v>
       </c>
       <c r="I135" s="16" t="inlineStr">
         <is>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.62</v>
+        <v>0.254</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.583</v>
+        <v>0.27</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6554,39 +6554,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.54</v>
+        <v>2.23</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>-0.0092</v>
+        <v>-0.0133</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>843900</v>
+        <v>1105600</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="H136" t="n">
-        <v>61.03</v>
-      </c>
-      <c r="I136" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.06</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.502</v>
+        <v>2.227</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.407</v>
+        <v>2.108</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6599,39 +6599,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="E137" s="10" t="n">
-        <v>-0.0063</v>
+        <v>2.04</v>
+      </c>
+      <c r="E137" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>824000</v>
+        <v>1086000</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.23</v>
+        <v>0.42</v>
       </c>
       <c r="H137" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="I137" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.8</v>
+      </c>
+      <c r="I137" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>7.875</v>
+        <v>2.061</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>7.803</v>
+        <v>2.104</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6644,28 +6644,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.755</v>
+        <v>1.5</v>
       </c>
       <c r="E138" s="10" t="n">
         <v>-0.0066</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>806100</v>
+        <v>1070300</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="H138" t="n">
-        <v>50.62</v>
+        <v>31.69</v>
       </c>
       <c r="I138" s="16" t="inlineStr">
         <is>
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.755</v>
+        <v>1.555</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.74</v>
+        <v>1.669</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6689,39 +6689,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E139" s="15" t="n">
-        <v>0.005500000000000001</v>
+        <v>7.89</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>-0.0075</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>800400</v>
+        <v>1051500</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.45</v>
+        <v>0.29</v>
       </c>
       <c r="H139" t="n">
-        <v>54.33</v>
-      </c>
-      <c r="I139" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.26</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.906</v>
+        <v>7.874</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.789</v>
+        <v>7.803</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6734,39 +6734,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>1.15</v>
+        <v>0.27</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>-0.0171</v>
+        <v>-0.0182</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>800200</v>
+        <v>1049700</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.22</v>
+        <v>1.18</v>
       </c>
       <c r="H140" t="n">
-        <v>60.43</v>
-      </c>
-      <c r="I140" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.39</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>1.111</v>
+        <v>0.278</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>1.014</v>
+        <v>0.275</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6779,28 +6779,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E141" s="17" t="n">
-        <v>0</v>
+        <v>1.06</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>772100</v>
+        <v>989800</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.26</v>
+        <v>0.46</v>
       </c>
       <c r="H141" t="n">
-        <v>42.77</v>
+        <v>31.18</v>
       </c>
       <c r="I141" s="13" t="inlineStr">
         <is>
@@ -6808,10 +6808,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>2.998</v>
+        <v>1.11</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>3.04</v>
+        <v>1.148</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6824,28 +6824,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="E142" s="15" t="n">
-        <v>0.0281</v>
+        <v>1.67</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>-0.0234</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>751200</v>
+        <v>971400</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="H142" t="n">
-        <v>41.13</v>
+        <v>36.85</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>1.893</v>
+        <v>1.749</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>1.962</v>
+        <v>1.853</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6869,28 +6869,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>6.81</v>
-      </c>
-      <c r="E143" s="15" t="n">
-        <v>0.0074</v>
+        <v>0.63</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>-0.0156</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>710300</v>
+        <v>950400</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="H143" t="n">
-        <v>56.25</v>
+        <v>54.69</v>
       </c>
       <c r="I143" s="16" t="inlineStr">
         <is>
@@ -6898,10 +6898,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>6.599</v>
+        <v>0.62</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>6.517</v>
+        <v>0.583</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6914,28 +6914,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.83</v>
+        <v>0.63</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>-0.006</v>
+        <v>-0.0156</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>706600</v>
+        <v>933100</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.24</v>
+        <v>0.71</v>
       </c>
       <c r="H144" t="n">
-        <v>61.2</v>
+        <v>46.62</v>
       </c>
       <c r="I144" s="16" t="inlineStr">
         <is>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>0.804</v>
+        <v>0.634</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>0.725</v>
+        <v>0.629</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6959,39 +6959,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>QL</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>-0.005</v>
+        <v>1.82</v>
+      </c>
+      <c r="E145" s="15" t="n">
+        <v>0.0225</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>698300</v>
+        <v>930600</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.4</v>
+        <v>0.13</v>
       </c>
       <c r="H145" t="n">
-        <v>56.56</v>
-      </c>
-      <c r="I145" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.82</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>3.944</v>
+        <v>1.892</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>3.933</v>
+        <v>1.962</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7004,28 +7004,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>PADINI</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E146" s="15" t="n">
-        <v>0.0106</v>
+        <v>1.02</v>
+      </c>
+      <c r="E146" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>695900</v>
+        <v>924800</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="H146" t="n">
-        <v>35.85</v>
+        <v>31.36</v>
       </c>
       <c r="I146" s="13" t="inlineStr">
         <is>
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>1.034</v>
+        <v>1.082</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.017</v>
+        <v>1.26</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7049,28 +7049,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>3.67</v>
+        <v>0.765</v>
       </c>
       <c r="E147" s="15" t="n">
-        <v>0.0166</v>
+        <v>0.0066</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>686000</v>
+        <v>916400</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="H147" t="n">
-        <v>76.48999999999999</v>
+        <v>53.02</v>
       </c>
       <c r="I147" s="16" t="inlineStr">
         <is>
@@ -7078,10 +7078,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>3.346</v>
+        <v>0.756</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>2.91</v>
+        <v>0.74</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7094,28 +7094,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>QL</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>1.47</v>
+        <v>4.01</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>-0.0068</v>
+        <v>-0.0074</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>679100</v>
+        <v>909500</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.27</v>
+        <v>0.51</v>
       </c>
       <c r="H148" t="n">
-        <v>46.25</v>
+        <v>55.78</v>
       </c>
       <c r="I148" s="16" t="inlineStr">
         <is>
@@ -7123,10 +7123,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>1.477</v>
+        <v>3.943</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>1.527</v>
+        <v>3.933</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7139,28 +7139,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="E149" s="10" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0194</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>677600</v>
+        <v>908900</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.23</v>
+        <v>0.63</v>
       </c>
       <c r="H149" t="n">
-        <v>49.04</v>
+        <v>49.12</v>
       </c>
       <c r="I149" s="16" t="inlineStr">
         <is>
@@ -7168,10 +7168,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.765</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.575</v>
+        <v>0.755</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7184,28 +7184,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>7.97</v>
+        <v>1.28</v>
       </c>
       <c r="E150" s="15" t="n">
-        <v>0.0019</v>
+        <v>0.0159</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>666900</v>
+        <v>881800</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.18</v>
+        <v>0.58</v>
       </c>
       <c r="H150" t="n">
-        <v>51.89</v>
+        <v>47.78</v>
       </c>
       <c r="I150" s="16" t="inlineStr">
         <is>
@@ -7213,10 +7213,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>7.902</v>
+        <v>1.28</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>8.086</v>
+        <v>1.34</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7229,28 +7229,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E151" s="17" t="n">
-        <v>0</v>
+        <v>6.79</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>0.0044</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>663400</v>
+        <v>880500</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="H151" t="n">
-        <v>57.6</v>
+        <v>55.81</v>
       </c>
       <c r="I151" s="16" t="inlineStr">
         <is>
@@ -7258,10 +7258,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>2.059</v>
+        <v>6.597</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>1.997</v>
+        <v>6.516</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7274,39 +7274,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="E152" s="10" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.915</v>
+      </c>
+      <c r="E152" s="15" t="n">
+        <v>0.011</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>657300</v>
+        <v>858800</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.08</v>
+        <v>0.48</v>
       </c>
       <c r="H152" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="I152" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.03</v>
+      </c>
+      <c r="I152" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>4.564</v>
+        <v>0.907</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>4.532</v>
+        <v>0.789</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7319,39 +7319,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E153" s="17" t="n">
-        <v>0</v>
+        <v>1.15</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>-0.0171</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>650000</v>
+        <v>855700</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.67</v>
+        <v>0.24</v>
       </c>
       <c r="H153" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="I153" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.43</v>
+      </c>
+      <c r="I153" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>0.631</v>
+        <v>1.111</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>0.637</v>
+        <v>1.014</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7364,39 +7364,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>1.58</v>
+        <v>0.54</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>-0.0186</v>
+        <v>-0.0092</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>635800</v>
+        <v>854700</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>1.1</v>
+        <v>0.46</v>
       </c>
       <c r="H154" t="n">
-        <v>52.33</v>
-      </c>
-      <c r="I154" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.03</v>
+      </c>
+      <c r="I154" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>1.584</v>
+        <v>0.502</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>1.504</v>
+        <v>0.407</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7409,28 +7409,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E155" s="10" t="n">
-        <v>-0.0048</v>
+        <v>2.67</v>
+      </c>
+      <c r="E155" s="15" t="n">
+        <v>0.023</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>625300</v>
+        <v>816400</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.57</v>
+        <v>0.1</v>
       </c>
       <c r="H155" t="n">
-        <v>39.91</v>
+        <v>46.42</v>
       </c>
       <c r="I155" s="16" t="inlineStr">
         <is>
@@ -7438,10 +7438,10 @@
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>2.08</v>
+        <v>2.672</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>2.109</v>
+        <v>2.862</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7454,39 +7454,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>0.6</v>
+        <v>0.95</v>
       </c>
       <c r="E156" s="15" t="n">
-        <v>0.0169</v>
+        <v>0.0106</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>605700</v>
+        <v>811800</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="H156" t="n">
-        <v>50.92</v>
-      </c>
-      <c r="I156" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.85</v>
+      </c>
+      <c r="I156" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>0.594</v>
+        <v>1.034</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>0.609</v>
+        <v>1.017</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7499,39 +7499,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>0.57</v>
+        <v>2.94</v>
       </c>
       <c r="E157" s="15" t="n">
-        <v>0.0179</v>
+        <v>0.0034</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>605700</v>
+        <v>811400</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>1.12</v>
+        <v>0.27</v>
       </c>
       <c r="H157" t="n">
-        <v>77.31999999999999</v>
-      </c>
-      <c r="I157" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.79</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>0.515</v>
+        <v>2.999</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>0.496</v>
+        <v>3.04</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7544,39 +7544,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="E158" s="10" t="n">
-        <v>-0.0022</v>
+        <v>0.63</v>
+      </c>
+      <c r="E158" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>595300</v>
+        <v>800000</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.13</v>
+        <v>0.83</v>
       </c>
       <c r="H158" t="n">
-        <v>33.53</v>
-      </c>
-      <c r="I158" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.02</v>
+      </c>
+      <c r="I158" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>4.703</v>
+        <v>0.631</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>4.978</v>
+        <v>0.637</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7589,39 +7589,39 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="E159" s="10" t="n">
-        <v>-0.01</v>
+        <v>1.4</v>
+      </c>
+      <c r="E159" s="15" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>589400</v>
+        <v>787100</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.51</v>
+        <v>0.42</v>
       </c>
       <c r="H159" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="I159" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.84</v>
+      </c>
+      <c r="I159" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>3.061</v>
+        <v>1.359</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>3.147</v>
+        <v>1.326</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7634,39 +7634,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E160" s="17" t="n">
-        <v>0</v>
+        <v>7.99</v>
+      </c>
+      <c r="E160" s="15" t="n">
+        <v>0.0044</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>586200</v>
+        <v>781000</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.37</v>
+        <v>0.21</v>
       </c>
       <c r="H160" t="n">
-        <v>40.79</v>
-      </c>
-      <c r="I160" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.87</v>
+      </c>
+      <c r="I160" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>0.734</v>
+        <v>7.904</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>0.752</v>
+        <v>8.087</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7679,39 +7679,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>5.15</v>
+        <v>0.83</v>
       </c>
       <c r="E161" s="10" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.006</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>581600</v>
+        <v>758000</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="H161" t="n">
-        <v>46.18</v>
-      </c>
-      <c r="I161" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.2</v>
+      </c>
+      <c r="I161" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>5.266</v>
+        <v>0.804</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>5.28</v>
+        <v>0.725</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7724,39 +7724,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>6.52</v>
+        <v>4.52</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>-0.0121</v>
+        <v>-0.0044</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>568900</v>
+        <v>738300</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="H162" t="n">
-        <v>31.06</v>
-      </c>
-      <c r="I162" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.09</v>
+      </c>
+      <c r="I162" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>6.709</v>
+        <v>4.702</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>6.877</v>
+        <v>4.978</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7769,39 +7769,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>AFFIN</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>2.02</v>
+        <v>4.39</v>
       </c>
       <c r="E163" s="10" t="n">
-        <v>-0.0098</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>568100</v>
+        <v>724700</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="H163" t="n">
-        <v>38.31</v>
-      </c>
-      <c r="I163" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.1</v>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>2.042</v>
+        <v>4.564</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>2.117</v>
+        <v>4.532</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7814,28 +7814,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>AFFIN</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E164" s="15" t="n">
-        <v>0.0072</v>
+        <v>2.02</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>-0.0098</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>567000</v>
+        <v>707300</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.3</v>
+        <v>1.07</v>
       </c>
       <c r="H164" t="n">
-        <v>70.84</v>
+        <v>38.31</v>
       </c>
       <c r="I164" s="16" t="inlineStr">
         <is>
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>1.359</v>
+        <v>2.042</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>1.326</v>
+        <v>2.117</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7859,39 +7859,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>ORKIM</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>0.79</v>
+        <v>1.46</v>
       </c>
       <c r="E165" s="10" t="n">
-        <v>-0.0125</v>
+        <v>-0.0135</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>561100</v>
+        <v>705200</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>2.82</v>
+        <v>0.28</v>
       </c>
       <c r="H165" t="n">
-        <v>36.88</v>
-      </c>
-      <c r="I165" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.31</v>
+      </c>
+      <c r="I165" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>0.802</v>
+        <v>1.476</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>0.84</v>
+        <v>1.526</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7904,39 +7904,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E166" s="15" t="n">
-        <v>0.0153</v>
+        <v>6.55</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>549100</v>
+        <v>697900</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="H166" t="n">
-        <v>44.44</v>
-      </c>
-      <c r="I166" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.59</v>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>2.67</v>
+        <v>6.712</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>2.862</v>
+        <v>6.877</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7949,39 +7949,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>0.615</v>
+        <v>2.11</v>
       </c>
       <c r="E167" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>549000</v>
+        <v>695400</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="H167" t="n">
-        <v>65.06</v>
-      </c>
-      <c r="I167" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.6</v>
+      </c>
+      <c r="I167" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>0.609</v>
+        <v>2.059</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>0.59</v>
+        <v>1.997</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -7994,28 +7994,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>0.63</v>
+        <v>0.505</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>-0.0156</v>
+        <v>-0.0194</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>537700</v>
+        <v>681400</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="H168" t="n">
-        <v>53.54</v>
+        <v>50.72</v>
       </c>
       <c r="I168" s="13" t="inlineStr">
         <is>
@@ -8023,10 +8023,10 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>0.633</v>
+        <v>0.511</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>0.593</v>
+        <v>0.467</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8039,39 +8039,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>0.505</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E169" s="10" t="n">
-        <v>-0.0194</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>525200</v>
+        <v>680900</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="H169" t="n">
-        <v>50.72</v>
-      </c>
-      <c r="I169" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.04</v>
+      </c>
+      <c r="I169" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>0.511</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>0.467</v>
+        <v>0.575</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8084,39 +8084,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E170" s="10" t="n">
-        <v>-0.005500000000000001</v>
+        <v>3.99</v>
+      </c>
+      <c r="E170" s="15" t="n">
+        <v>0.0076</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>511900</v>
+        <v>677800</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.43</v>
+        <v>0.21</v>
       </c>
       <c r="H170" t="n">
-        <v>33.96</v>
-      </c>
-      <c r="I170" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.3</v>
+      </c>
+      <c r="I170" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>1.9</v>
+        <v>3.77</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>1.959</v>
+        <v>3.419</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8129,45 +8129,855 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>1.03</v>
+        <v>0.6</v>
       </c>
       <c r="E171" s="15" t="n">
-        <v>0.0098</v>
+        <v>0.0169</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>500900</v>
+        <v>669000</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="H171" t="n">
-        <v>50.78</v>
-      </c>
-      <c r="I171" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.92</v>
+      </c>
+      <c r="I171" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>1.03</v>
+        <v>0.594</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>1.008</v>
+        <v>0.609</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
     </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>TAKAFUL</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>659700</v>
+      </c>
+      <c r="G172" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H172" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="n">
+        <v>3.061</v>
+      </c>
+      <c r="K172" s="9" t="n">
+        <v>3.147</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E173" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>641200</v>
+      </c>
+      <c r="G173" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H173" t="n">
+        <v>47.73</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J173" s="9" t="n">
+        <v>5.271</v>
+      </c>
+      <c r="K173" s="9" t="n">
+        <v>5.281</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>7179</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>LAGENDA</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>-0.0186</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>635800</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H174" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="n">
+        <v>1.584</v>
+      </c>
+      <c r="K174" s="9" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E175" s="15" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>633700</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H175" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="I175" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="K175" s="9" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>633400</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H176" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="n">
+        <v>6.775</v>
+      </c>
+      <c r="K176" s="9" t="n">
+        <v>6.818</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>5258</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>BIMB</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E177" s="10" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>627800</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H177" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="I177" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="K177" s="9" t="n">
+        <v>2.109</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>5248</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>BAUTO</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>621000</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H178" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="n">
+        <v>0.931</v>
+      </c>
+      <c r="K178" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E179" s="15" t="n">
+        <v>0.008100000000000001</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>615500</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H179" t="n">
+        <v>51.17</v>
+      </c>
+      <c r="I179" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="K179" s="9" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>5348</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ORKIM</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>-0.0125</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>606700</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H180" t="n">
+        <v>36.88</v>
+      </c>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="K180" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>6633</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>LHI</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E181" s="10" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>591800</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H181" t="n">
+        <v>38.97</v>
+      </c>
+      <c r="I181" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="K181" s="9" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="14" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E182" s="10" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>575700</v>
+      </c>
+      <c r="G182" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H182" t="n">
+        <v>57.11</v>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K182" s="9" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="14" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="E183" s="10" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>553200</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H183" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I183" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="n">
+        <v>3.288</v>
+      </c>
+      <c r="K183" s="9" t="n">
+        <v>3.477</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="14" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>7249</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SKYGATE</t>
+        </is>
+      </c>
+      <c r="D184" s="9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E184" s="10" t="n">
+        <v>-0.0508</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>540000</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H184" t="n">
+        <v>44.13</v>
+      </c>
+      <c r="I184" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K184" s="9" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="14" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>5053</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>OSK</t>
+        </is>
+      </c>
+      <c r="D185" s="9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E185" s="10" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>533700</v>
+      </c>
+      <c r="G185" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H185" t="n">
+        <v>32.92</v>
+      </c>
+      <c r="I185" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J185" s="9" t="n">
+        <v>1.899</v>
+      </c>
+      <c r="K185" s="9" t="n">
+        <v>1.959</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="14" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D186" s="9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E186" s="15" t="n">
+        <v>0.0221</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>529600</v>
+      </c>
+      <c r="G186" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H186" t="n">
+        <v>58.45</v>
+      </c>
+      <c r="I186" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J186" s="9" t="n">
+        <v>1.347</v>
+      </c>
+      <c r="K186" s="9" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="14" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D187" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E187" s="15" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>520900</v>
+      </c>
+      <c r="G187" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H187" t="n">
+        <v>50.78</v>
+      </c>
+      <c r="I187" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J187" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K187" s="9" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="14" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>UEMS</t>
+        </is>
+      </c>
+      <c r="D188" s="9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E188" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" s="11" t="n">
+        <v>510100</v>
+      </c>
+      <c r="G188" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H188" t="n">
+        <v>37.41</v>
+      </c>
+      <c r="I188" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J188" s="9" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="K188" s="9" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" s="14" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>TMK</t>
+        </is>
+      </c>
+      <c r="D189" s="9" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E189" s="10" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>507800</v>
+      </c>
+      <c r="G189" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H189" t="n">
+        <v>45.02</v>
+      </c>
+      <c r="I189" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J189" s="9" t="n">
+        <v>2.964</v>
+      </c>
+      <c r="K189" s="9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M171"/>
+  <autoFilter ref="A1:M189"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-09-29/bursa-report-2026-09-29.xlsx
+++ b/docs/downloads/2026-09-29/bursa-report-2026-09-29.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-09-29" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-29'!$A$1:$M$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-29'!$A$1:$M$193</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M189"/>
+  <dimension ref="A1:M193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.4</v>
+        <v>0.395</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.039</v>
+        <v>0.026</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>11339400</v>
+        <v>11386800</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>70.45</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.371</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>现价0.40高于50日均线0.371，EMA与SAR、Supertrend均偏多；但RSI达72.9已入超买区，信号偏热，可靠性需谨慎看待。</t>
+          <t>RSI 70.45 已入超买区，现价高于50日均线约6.5%，EMA与SAR、Supertrend均偏多，信号偏强但需留意超买。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.165</v>
+        <v>0.17</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>-0.1316</v>
+        <v>-0.1053</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>274458600</v>
+        <v>276682900</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="H3" t="n">
-        <v>20.46</v>
+        <v>20.85</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -670,10 +670,10 @@
         <v>0.027</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>65293500</v>
+        <v>66548200</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="H4" t="n">
         <v>79.09999999999999</v>
@@ -709,19 +709,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>-0.0128</v>
+        <v>0.39</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>19878200</v>
+        <v>21928200</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="H5" t="n">
-        <v>76.03</v>
+        <v>78.19</v>
       </c>
       <c r="I5" s="16" t="inlineStr">
         <is>
@@ -745,39 +745,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.155</v>
+        <v>0.58</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>14721700</v>
+        <v>15536900</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="H6" t="n">
-        <v>44.73</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>68.72</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.156</v>
+        <v>0.55</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.159</v>
+        <v>0.494</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -805,10 +805,10 @@
         <v>0.045</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>14103800</v>
+        <v>14975800</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="H7" t="n">
         <v>64.52</v>
@@ -835,39 +835,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.58</v>
+        <v>0.155</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>13585800</v>
+        <v>14721700</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="H8" t="n">
-        <v>68.72</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.73</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.55</v>
+        <v>0.156</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.494</v>
+        <v>0.159</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -889,19 +889,19 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>0.0507</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>13570700</v>
+        <v>14130200</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="H9" t="n">
-        <v>64.62</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="I9" s="16" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2.65</v>
+        <v>2.651</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>2.508</v>
@@ -940,10 +940,10 @@
         <v>-0.005699999999999999</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>12659500</v>
+        <v>12693100</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="H10" t="n">
         <v>47.09</v>
@@ -970,39 +970,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>-0.0381</v>
+        <v>0.77</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>12184400</v>
+        <v>12604400</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.32</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>25.04</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.12</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.621</v>
+        <v>0.773</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.839</v>
+        <v>0.774</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,39 +1015,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.505</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-0.0381</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>12104300</v>
+        <v>12293100</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.97</v>
+        <v>0.32</v>
       </c>
       <c r="H12" t="n">
-        <v>48.12</v>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.04</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.773</v>
+        <v>0.621</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.774</v>
+        <v>0.839</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,28 +1060,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>0</v>
+        <v>1.33</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>0.0391</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>11276600</v>
+        <v>11536000</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.61</v>
+        <v>1.01</v>
       </c>
       <c r="H13" t="n">
-        <v>54.01</v>
+        <v>47.13</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.304</v>
+        <v>1.367</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.291</v>
+        <v>1.293</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,28 +1105,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>0.0313</v>
+        <v>0.305</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>11066300</v>
+        <v>11276600</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.97</v>
+        <v>0.61</v>
       </c>
       <c r="H14" t="n">
-        <v>45.87</v>
+        <v>54.01</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1.366</v>
+        <v>0.304</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>1.293</v>
+        <v>0.291</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1210,7 +1210,7 @@
         <v>0.0526</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>10313300</v>
+        <v>10363900</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>0.4</v>
@@ -1249,16 +1249,16 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>-0.0385</v>
+        <v>-0.07690000000000001</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>8922200</v>
+        <v>9233800</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
@@ -1278,39 +1278,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0373</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VERDANT</t>
+          <t>COMPUGT</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>0.0357</v>
+        <v>0.015</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>8057500</v>
+        <v>8850000</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>3.62</v>
+        <v>8.33</v>
       </c>
       <c r="H18" t="n">
-        <v>85.54000000000001</v>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.63</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.231</v>
+        <v>0.016</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.21</v>
+        <v>0.016</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1323,33 +1323,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0468</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UNIPAC</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.255</v>
+        <v>4.46</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.0625</v>
+        <v>0.0721</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>7906400</v>
+        <v>8498500</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
+        <v>1.65</v>
+      </c>
+      <c r="H19" t="n">
+        <v>84.06</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>3.632</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>3.255</v>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
     </row>
@@ -1361,28 +1368,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0373</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>VERDANT</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>4.44</v>
+        <v>0.29</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>0.0673</v>
+        <v>0.0357</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>7834400</v>
+        <v>8066900</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.52</v>
+        <v>3.62</v>
       </c>
       <c r="H20" t="n">
-        <v>83.84</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
@@ -1390,10 +1397,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>3.63</v>
+        <v>0.231</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>3.255</v>
+        <v>0.21</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1406,40 +1413,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0468</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>UNIPAC</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.605</v>
+        <v>0.255</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>0.0083</v>
+        <v>0.0625</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>7527600</v>
+        <v>7989900</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="H21" t="n">
-        <v>48.47</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J21" s="9" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="K21" s="9" t="n">
-        <v>0.605</v>
-      </c>
+        <v>0.52</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n"/>
+      <c r="K21" s="9" t="n"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
     </row>
@@ -1451,31 +1451,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.005</v>
+        <v>0.6</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>7526500</v>
-      </c>
-      <c r="G22" s="12" t="n"/>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+        <v>7532900</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H22" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.605</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1487,40 +1496,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>-0.0118</v>
+        <v>0.005</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>7200900</v>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H23" t="n">
-        <v>47.27</v>
-      </c>
+        <v>7526800</v>
+      </c>
+      <c r="G23" s="12" t="n"/>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>2.581</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>2.447</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
     </row>
@@ -1532,39 +1532,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>-0.0199</v>
+        <v>-0.0118</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>7112100</v>
+        <v>7273000</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.47</v>
+        <v>0.38</v>
       </c>
       <c r="H24" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.27</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>2.442</v>
+        <v>2.581</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>2.286</v>
+        <v>2.447</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1577,28 +1577,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>0.018</v>
+        <v>2.48</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>6897300</v>
+        <v>7145700</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.17</v>
+        <v>0.47</v>
       </c>
       <c r="H25" t="n">
-        <v>66.53</v>
+        <v>58.34</v>
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.526</v>
+        <v>2.444</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.532</v>
+        <v>2.286</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1622,39 +1622,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>0.018</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>6814600</v>
+        <v>6905500</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.15</v>
+        <v>1.17</v>
       </c>
       <c r="H26" t="n">
-        <v>51.13</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.53</v>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.736</v>
+        <v>0.526</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.532</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1667,28 +1667,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0.0108</v>
+        <v>0.73</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>6685700</v>
+        <v>6827900</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.71</v>
+        <v>0.15</v>
       </c>
       <c r="H27" t="n">
-        <v>58.22</v>
+        <v>51.13</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.45</v>
+        <v>0.736</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.41</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1712,39 +1712,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E28" s="17" t="n">
-        <v>0</v>
+        <v>0.47</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6484200</v>
+        <v>6745800</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="H28" t="n">
-        <v>62.92</v>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.22</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.717</v>
+        <v>0.45</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1757,28 +1757,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NEXG</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>-0.0476</v>
+        <v>0.785</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6428200</v>
+        <v>6521100</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.4</v>
+        <v>0.63</v>
       </c>
       <c r="H29" t="n">
-        <v>56.45</v>
+        <v>62.92</v>
       </c>
       <c r="I29" s="16" t="inlineStr">
         <is>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.286</v>
+        <v>0.717</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.277</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1802,39 +1802,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0358</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ICTZONE</t>
+          <t>NEXG</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>-0.0204</v>
+        <v>-0.0476</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6280500</v>
+        <v>6437800</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>2.17</v>
+        <v>0.4</v>
       </c>
       <c r="H30" t="n">
-        <v>41.53</v>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.45</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.258</v>
+        <v>0.286</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.251</v>
+        <v>0.277</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1847,39 +1847,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0358</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>ICTZONE</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>2.3</v>
+        <v>0.235</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>-0.0171</v>
+        <v>-0.0408</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>6241500</v>
+        <v>6302500</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.38</v>
+        <v>2.17</v>
       </c>
       <c r="H31" t="n">
-        <v>47.67</v>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.67</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>2.343</v>
+        <v>0.258</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>2.245</v>
+        <v>0.251</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1892,28 +1892,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>7.81</v>
+        <v>2.3</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>-0.0225</v>
+        <v>-0.0171</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>6089200</v>
+        <v>6284800</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.49</v>
+        <v>0.39</v>
       </c>
       <c r="H32" t="n">
-        <v>51.27</v>
+        <v>47.67</v>
       </c>
       <c r="I32" s="16" t="inlineStr">
         <is>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>7.806</v>
+        <v>2.343</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>7.736</v>
+        <v>2.245</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1937,28 +1937,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0213</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MTAG</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.215</v>
+        <v>7.82</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>-0.0227</v>
+        <v>-0.0213</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>6071800</v>
+        <v>6102000</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>13.07</v>
+        <v>0.49</v>
       </c>
       <c r="H33" t="n">
-        <v>54.9</v>
+        <v>51.76</v>
       </c>
       <c r="I33" s="16" t="inlineStr">
         <is>
@@ -1966,10 +1966,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.209</v>
+        <v>7.807</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.216</v>
+        <v>7.736</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1982,39 +1982,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0213</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>MTAG</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>4.75</v>
+        <v>0.215</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0227</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5769600</v>
+        <v>6071800</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.33</v>
+        <v>13.07</v>
       </c>
       <c r="H34" t="n">
-        <v>35.75</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.9</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>4.836</v>
+        <v>0.209</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>4.953</v>
+        <v>0.216</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2027,28 +2027,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.21</v>
+        <v>4.75</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>-0.0233</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5764500</v>
+        <v>5880800</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="H35" t="n">
-        <v>27.87</v>
+        <v>35.75</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.236</v>
+        <v>4.836</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.248</v>
+        <v>4.953</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2072,28 +2072,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>COMPUGT</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>0</v>
+        <v>0.21</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5696900</v>
+        <v>5862000</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>5.36</v>
+        <v>0.25</v>
       </c>
       <c r="H36" t="n">
-        <v>46.63</v>
+        <v>27.87</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -2101,10 +2101,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.016</v>
+        <v>0.236</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.016</v>
+        <v>0.248</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2117,28 +2117,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.215</v>
+        <v>2.87</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>-0.0227</v>
+        <v>-0.0137</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5311500</v>
+        <v>5622400</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="H37" t="n">
-        <v>64.98999999999999</v>
+        <v>63.23</v>
       </c>
       <c r="I37" s="16" t="inlineStr">
         <is>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.204</v>
+        <v>2.776</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.185</v>
+        <v>2.637</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2162,39 +2162,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0370</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>XPB</t>
+          <t>JADI</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.225</v>
+        <v>0.03</v>
       </c>
       <c r="E38" s="15" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5223900</v>
+        <v>5474700</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1.51</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>67.76000000000001</v>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.31</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.204</v>
+        <v>0.03</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.18</v>
+        <v>0.033</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2207,28 +2207,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>2.85</v>
+        <v>0.215</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>-0.0206</v>
+        <v>-0.0227</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>5105400</v>
+        <v>5457700</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.36</v>
+        <v>0.25</v>
       </c>
       <c r="H39" t="n">
-        <v>60.84</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="I39" s="16" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>2.774</v>
+        <v>0.204</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>2.637</v>
+        <v>0.185</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2252,28 +2252,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PTT</t>
+          <t>PAVREIT</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <v>0.0071</v>
+        <v>1.55</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>5066500</v>
+        <v>5299000</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>7.17</v>
+        <v>1.79</v>
       </c>
       <c r="H40" t="n">
-        <v>44.62</v>
+        <v>39.82</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>1.431</v>
+        <v>1.645</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2297,39 +2297,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7223</t>
+          <t>0370</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JADI</t>
+          <t>XPB</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.03</v>
+        <v>0.225</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>0.2</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>5027500</v>
+        <v>5259400</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>8.06</v>
+        <v>1.52</v>
       </c>
       <c r="H41" t="n">
-        <v>49.31</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.76000000000001</v>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.03</v>
+        <v>0.204</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.033</v>
+        <v>0.18</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2351,19 +2351,19 @@
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>10.08</v>
+        <v>10.1</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0059</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>5026100</v>
+        <v>5236100</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="H42" t="n">
-        <v>41.49</v>
+        <v>42.66</v>
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>10.166</v>
+        <v>10.168</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>10.308</v>
+        <v>10.309</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2387,28 +2387,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>-0.012</v>
+        <v>0.36</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4996500</v>
+        <v>5143800</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.46</v>
+        <v>1.18</v>
       </c>
       <c r="H43" t="n">
-        <v>51.13</v>
+        <v>65.03</v>
       </c>
       <c r="I43" s="16" t="inlineStr">
         <is>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.409</v>
+        <v>0.34</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.411</v>
+        <v>0.333</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2432,39 +2432,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>PTT</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.36</v>
+        <v>1.41</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>0.0588</v>
+        <v>0.0071</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4940800</v>
+        <v>5066500</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1.13</v>
+        <v>7.17</v>
       </c>
       <c r="H44" t="n">
-        <v>65.03</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.62</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.34</v>
+        <v>1.44</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.333</v>
+        <v>1.431</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2477,28 +2477,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.24</v>
+        <v>0.405</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>-0.0204</v>
+        <v>-0.0241</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>4905800</v>
+        <v>5027300</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.17</v>
+        <v>0.46</v>
       </c>
       <c r="H45" t="n">
-        <v>30.69</v>
+        <v>46.7</v>
       </c>
       <c r="I45" s="16" t="inlineStr">
         <is>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.273</v>
+        <v>0.409</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.325</v>
+        <v>0.41</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         <v>-0.0089</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>4837000</v>
+        <v>5012500</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="H46" t="n">
         <v>69.81</v>
@@ -2567,39 +2567,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>-0.0128</v>
+        <v>0.245</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>4792000</v>
+        <v>4999000</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="H47" t="n">
-        <v>53.94</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>31.98</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.382</v>
+        <v>0.273</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.322</v>
+        <v>0.325</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,28 +2612,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>3.45</v>
+        <v>0.385</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>-0.0143</v>
+        <v>-0.0128</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>4663000</v>
+        <v>4825700</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.96</v>
+        <v>0.22</v>
       </c>
       <c r="H48" t="n">
-        <v>34.69</v>
+        <v>53.94</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>3.6</v>
+        <v>0.382</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>3.699</v>
+        <v>0.322</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.235</v>
+        <v>3.46</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>-0.0208</v>
+        <v>-0.0114</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4643200</v>
+        <v>4811500</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.26</v>
+        <v>0.99</v>
       </c>
       <c r="H49" t="n">
-        <v>52.63</v>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.25</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.232</v>
+        <v>3.601</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.233</v>
+        <v>3.699</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2702,39 +2702,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>2.08</v>
+        <v>0.24</v>
       </c>
       <c r="E50" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4578200</v>
+        <v>4665500</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="H50" t="n">
-        <v>45.92</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.39</v>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>2.122</v>
+        <v>0.233</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>2.064</v>
+        <v>0.233</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2747,39 +2747,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.79</v>
+        <v>2.07</v>
       </c>
       <c r="E51" s="10" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.0048</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4557400</v>
+        <v>4646900</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="H51" t="n">
-        <v>58.11</v>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.84</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.74</v>
+        <v>2.121</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>1.538</v>
+        <v>2.064</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,39 +2792,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="E52" s="15" t="n">
-        <v>0.008500000000000001</v>
+        <v>1.79</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4427100</v>
+        <v>4568400</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.52</v>
+        <v>0.19</v>
       </c>
       <c r="H52" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.11</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>4.74</v>
+        <v>1.74</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>4.592</v>
+        <v>1.538</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2837,39 +2837,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.475</v>
+        <v>4.74</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>0.0215</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4377800</v>
+        <v>4451500</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.19</v>
+        <v>0.52</v>
       </c>
       <c r="H53" t="n">
-        <v>52.69</v>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.6</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.468</v>
+        <v>4.74</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.471</v>
+        <v>4.592</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2882,28 +2882,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SUNSURIA</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>-0.0526</v>
+        <v>0.47</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>4218900</v>
+        <v>4381800</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>62.27</v>
+        <v>0.19</v>
       </c>
       <c r="H54" t="n">
-        <v>44.26</v>
+        <v>50.83</v>
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.277</v>
+        <v>0.468</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.281</v>
+        <v>0.471</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2927,28 +2927,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>3743</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SUNSURIA</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>0.0185</v>
+        <v>0.275</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.0351</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>4125000</v>
+        <v>4219000</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.35</v>
+        <v>62.27</v>
       </c>
       <c r="H55" t="n">
-        <v>75.22</v>
+        <v>47.46</v>
       </c>
       <c r="I55" s="16" t="inlineStr">
         <is>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>1.013</v>
+        <v>0.277</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.853</v>
+        <v>0.281</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2972,28 +2972,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.785</v>
+        <v>1.09</v>
       </c>
       <c r="E56" s="15" t="n">
-        <v>0.0467</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>4073700</v>
+        <v>4173100</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="H56" t="n">
-        <v>62.4</v>
+        <v>74.22</v>
       </c>
       <c r="I56" s="16" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.766</v>
+        <v>1.012</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.753</v>
+        <v>0.853</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3017,39 +3017,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>0</v>
+        <v>0.785</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>0.0467</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3878500</v>
+        <v>4074300</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="H57" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.4</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.772</v>
+        <v>0.766</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.773</v>
+        <v>0.753</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3062,28 +3062,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SYSTECH</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E58" s="17" t="n">
-        <v>0</v>
+        <v>0.145</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3861600</v>
+        <v>3902100</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.76</v>
+        <v>0.1</v>
       </c>
       <c r="H58" t="n">
-        <v>59.06</v>
+        <v>45.61</v>
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.164</v>
+        <v>0.157</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.165</v>
+        <v>0.148</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3107,39 +3107,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>-0.0169</v>
+        <v>0.765</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3851000</v>
+        <v>3878500</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="H59" t="n">
-        <v>61.78</v>
-      </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.276</v>
+        <v>0.772</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.27</v>
+        <v>0.773</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3152,28 +3152,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>5.77</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>-0.0017</v>
+        <v>0.295</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3736800</v>
+        <v>3864100</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.26</v>
+        <v>0.61</v>
       </c>
       <c r="H60" t="n">
-        <v>57.61</v>
+        <v>66.27</v>
       </c>
       <c r="I60" s="16" t="inlineStr">
         <is>
@@ -3181,10 +3181,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>5.692</v>
+        <v>0.277</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>5.161</v>
+        <v>0.27</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3197,28 +3197,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>SYSTECH</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.145</v>
+        <v>0.17</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>-0.0333</v>
+        <v>-0.0286</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3733200</v>
+        <v>3861700</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.09</v>
+        <v>0.76</v>
       </c>
       <c r="H61" t="n">
-        <v>45.61</v>
+        <v>54.99</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.157</v>
+        <v>0.163</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.148</v>
+        <v>0.165</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3242,39 +3242,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>4.89</v>
+        <v>5.76</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>-0.004099999999999999</v>
+        <v>-0.0035</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3625800</v>
+        <v>3828200</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="H62" t="n">
-        <v>63.94</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.15</v>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>4.759</v>
+        <v>5.691</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>4.525</v>
+        <v>5.161</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3287,39 +3287,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>12.94</v>
-      </c>
-      <c r="E63" s="15" t="n">
-        <v>0.0023</v>
+        <v>4.89</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3525200</v>
+        <v>3709500</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.45</v>
+        <v>0.21</v>
       </c>
       <c r="H63" t="n">
-        <v>32.93</v>
-      </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>63.94</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>13.185</v>
+        <v>4.759</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>13.77</v>
+        <v>4.525</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3332,28 +3332,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>7.68</v>
+        <v>0.595</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>-0.0204</v>
+        <v>-0.0165</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3463100</v>
+        <v>3567500</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.32</v>
+        <v>0.72</v>
       </c>
       <c r="H64" t="n">
-        <v>30.95</v>
+        <v>34.5</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>7.948</v>
+        <v>0.633</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>8.25</v>
+        <v>0.657</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3377,39 +3377,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.365</v>
+        <v>7.69</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>-0.0135</v>
+        <v>-0.0191</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3457100</v>
+        <v>3566500</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="H65" t="n">
-        <v>48.25</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.28</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.367</v>
+        <v>7.949</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.367</v>
+        <v>8.25</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3422,39 +3422,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>-0.0165</v>
+        <v>12.96</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>0.0039</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3402900</v>
+        <v>3553000</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.45</v>
       </c>
       <c r="H66" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.06</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.633</v>
+        <v>13.186</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.657</v>
+        <v>13.77</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3467,28 +3467,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>1.15</v>
+        <v>0.365</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>-0.0254</v>
+        <v>-0.0135</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3400300</v>
+        <v>3457100</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.51</v>
+        <v>0.57</v>
       </c>
       <c r="H67" t="n">
-        <v>46.5</v>
+        <v>48.25</v>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
@@ -3496,10 +3496,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>1.178</v>
+        <v>0.367</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>1.145</v>
+        <v>0.367</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3512,28 +3512,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v>0.0347</v>
+        <v>1.14</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>-0.0339</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3308500</v>
+        <v>3432200</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
       <c r="H68" t="n">
-        <v>64.13</v>
+        <v>45.29</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
@@ -3541,10 +3541,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>1.178</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.616</v>
+        <v>1.145</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3557,28 +3557,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>-0.0076</v>
+        <v>0.745</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0.0347</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3202000</v>
+        <v>3373900</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.28</v>
+        <v>0.58</v>
       </c>
       <c r="H69" t="n">
-        <v>40.38</v>
+        <v>64.13</v>
       </c>
       <c r="I69" s="16" t="inlineStr">
         <is>
@@ -3586,10 +3586,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.329</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.438</v>
+        <v>0.616</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3611,19 +3611,19 @@
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.74</v>
+        <v>0.745</v>
       </c>
       <c r="E70" s="15" t="n">
-        <v>0.0278</v>
+        <v>0.0347</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3158900</v>
+        <v>3297700</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H70" t="n">
-        <v>70.73999999999999</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="I70" s="16" t="inlineStr">
         <is>
@@ -3647,39 +3647,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0267</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E71" s="15" t="n">
-        <v>0.0156</v>
+        <v>1.29</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2964100</v>
+        <v>3254100</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.88</v>
+        <v>0.28</v>
       </c>
       <c r="H71" t="n">
-        <v>35.32</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.12</v>
+      </c>
+      <c r="I71" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.384</v>
+        <v>1.327</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.371</v>
+        <v>1.438</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="E72" s="17" t="n">
-        <v>0</v>
+        <v>0.42</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.0633</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2863600</v>
+        <v>2989800</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.4</v>
+        <v>1.77</v>
       </c>
       <c r="H72" t="n">
-        <v>45.43</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>71.31999999999999</v>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>1.98</v>
+        <v>0.375</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>1.972</v>
+        <v>0.342</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3737,39 +3737,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0267</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>-0.0233</v>
+        <v>0.32</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2850700</v>
+        <v>2989100</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.51</v>
+        <v>0.89</v>
       </c>
       <c r="H73" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="I73" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.76</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.214</v>
+        <v>0.383</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.212</v>
+        <v>0.371</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3782,39 +3782,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E74" s="15" t="n">
-        <v>0.0156</v>
+        <v>1.94</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>-0.0051</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2830000</v>
+        <v>2930900</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="H74" t="n">
-        <v>95.48</v>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.13</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.919</v>
+        <v>1.979</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.746</v>
+        <v>1.972</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3827,28 +3827,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.93</v>
+        <v>1.3</v>
       </c>
       <c r="E75" s="15" t="n">
-        <v>0.0109</v>
+        <v>0.0156</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2792400</v>
+        <v>2881300</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="H75" t="n">
-        <v>47.5</v>
+        <v>95.48</v>
       </c>
       <c r="I75" s="16" t="inlineStr">
         <is>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.928</v>
+        <v>0.919</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.969</v>
+        <v>0.746</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3872,28 +3872,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <v>0.0506</v>
+        <v>0.21</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2791000</v>
+        <v>2851200</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1.65</v>
+        <v>0.51</v>
       </c>
       <c r="H76" t="n">
-        <v>70.2</v>
+        <v>47.8</v>
       </c>
       <c r="I76" s="16" t="inlineStr">
         <is>
@@ -3901,10 +3901,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.375</v>
+        <v>0.214</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.342</v>
+        <v>0.212</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3917,39 +3917,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>-0.0184</v>
+        <v>0.93</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2744800</v>
+        <v>2839200</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.55</v>
+        <v>0.82</v>
       </c>
       <c r="H77" t="n">
-        <v>37.37</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.5</v>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>1.269</v>
+        <v>0.928</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>1.302</v>
+        <v>0.969</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3962,39 +3962,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>7.45</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>-0.009300000000000001</v>
+        <v>2.55</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2657700</v>
+        <v>2823100</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.39</v>
+        <v>0.48</v>
       </c>
       <c r="H78" t="n">
-        <v>37.74</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.43</v>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>7.667</v>
+        <v>2.567</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>7.835</v>
+        <v>2.54</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4007,39 +4007,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.93</v>
+        <v>1.23</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>-0.0106</v>
+        <v>-0.0184</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2619800</v>
+        <v>2764800</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="H79" t="n">
-        <v>68.43000000000001</v>
-      </c>
-      <c r="I79" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.37</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.888</v>
+        <v>1.269</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.852</v>
+        <v>1.302</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4052,28 +4052,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>0.0197</v>
+        <v>7.45</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2530100</v>
+        <v>2677900</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.62</v>
+        <v>0.39</v>
       </c>
       <c r="H80" t="n">
-        <v>41.27</v>
+        <v>37.74</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4081,10 +4081,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.794</v>
+        <v>7.667</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.846</v>
+        <v>7.835</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4097,39 +4097,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TSH</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>0.024</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>-0.0053</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2483800</v>
+        <v>2629800</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.93</v>
+        <v>0.57</v>
       </c>
       <c r="H81" t="n">
-        <v>37.76</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.83</v>
+      </c>
+      <c r="I81" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.388</v>
+        <v>0.888</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1.317</v>
+        <v>0.852</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4142,39 +4142,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.275</v>
+        <v>0.7</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>-0.0678</v>
+        <v>-0.0071</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2473100</v>
+        <v>2617900</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="H82" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.06</v>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.265</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.222</v>
+        <v>0.664</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4187,39 +4187,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>-0.0071</v>
+        <v>0.775</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>0.0197</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2439200</v>
+        <v>2564600</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.32</v>
+        <v>0.62</v>
       </c>
       <c r="H83" t="n">
-        <v>54.06</v>
-      </c>
-      <c r="I83" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.27</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.794</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.664</v>
+        <v>0.846</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4232,28 +4232,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>1.95</v>
+        <v>1.27</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>0.0052</v>
+        <v>0.016</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2385500</v>
+        <v>2549100</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
       <c r="H84" t="n">
-        <v>39.56</v>
+        <v>36.3</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>1.987</v>
+        <v>1.387</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>2.103</v>
+        <v>1.317</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4277,39 +4277,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E85" s="15" t="n">
-        <v>0.0245</v>
+        <v>0.275</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>-0.0678</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2292100</v>
+        <v>2473100</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>1.01</v>
+        <v>0.28</v>
       </c>
       <c r="H85" t="n">
-        <v>90.11</v>
-      </c>
-      <c r="I85" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.4</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>2.316</v>
+        <v>0.265</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1.974</v>
+        <v>0.222</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4322,39 +4322,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.665</v>
+        <v>1.95</v>
       </c>
       <c r="E86" s="15" t="n">
-        <v>0.031</v>
+        <v>0.0052</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2118400</v>
+        <v>2391400</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.22</v>
+        <v>0.78</v>
       </c>
       <c r="H86" t="n">
-        <v>59.67</v>
-      </c>
-      <c r="I86" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.56</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.635</v>
+        <v>1.987</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.577</v>
+        <v>2.103</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4367,28 +4367,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="E87" s="15" t="n">
-        <v>0.0276</v>
+        <v>0.021</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2093000</v>
+        <v>2317900</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.8</v>
+        <v>1.03</v>
       </c>
       <c r="H87" t="n">
-        <v>90.31999999999999</v>
+        <v>90.01000000000001</v>
       </c>
       <c r="I87" s="16" t="inlineStr">
         <is>
@@ -4396,10 +4396,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>2.263</v>
+        <v>2.315</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1.8</v>
+        <v>1.974</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4412,28 +4412,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0369</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>JSSOLAR</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E88" s="15" t="n">
-        <v>0.0039</v>
+        <v>0.26</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2084100</v>
+        <v>2233500</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.36</v>
+        <v>1.83</v>
       </c>
       <c r="H88" t="n">
-        <v>49.47</v>
+        <v>73.58</v>
       </c>
       <c r="I88" s="16" t="inlineStr">
         <is>
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>2.568</v>
+        <v>0.217</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>2.54</v>
+        <v>0.2</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4472,10 +4472,10 @@
         <v>0.02</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2071300</v>
+        <v>2203100</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="H89" t="n">
         <v>38.96</v>
@@ -4517,10 +4517,10 @@
         <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1999000</v>
+        <v>2143500</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="H90" t="n">
         <v>65.06</v>
@@ -4547,28 +4547,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0369</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>JSSOLAR</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E91" s="15" t="n">
-        <v>0.0192</v>
+        <v>0.29</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1967700</v>
+        <v>2130700</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>1.61</v>
+        <v>0.32</v>
       </c>
       <c r="H91" t="n">
-        <v>74.73999999999999</v>
+        <v>39.08</v>
       </c>
       <c r="I91" s="16" t="inlineStr">
         <is>
@@ -4576,10 +4576,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.217</v>
+        <v>0.297</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.2</v>
+        <v>0.311</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4592,28 +4592,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="E92" s="15" t="n">
-        <v>0.0345</v>
+        <v>0.031</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1957400</v>
+        <v>2122700</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.57</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H92" t="n">
-        <v>57.26</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I92" s="16" t="inlineStr">
         <is>
@@ -4621,9 +4621,11 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>2.874</v>
-      </c>
-      <c r="K92" s="9" t="n"/>
+        <v>2.264</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>1.8</v>
+      </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
     </row>
@@ -4635,31 +4637,40 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BPROP</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>0</v>
+        <v>0.665</v>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>0.031</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1940500</v>
-      </c>
-      <c r="G93" s="12" t="n"/>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J93" s="9" t="n"/>
-      <c r="K93" s="9" t="n"/>
+        <v>2121400</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H93" t="n">
+        <v>59.67</v>
+      </c>
+      <c r="I93" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>0.577</v>
+      </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
     </row>
@@ -4671,28 +4682,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PAVREIT</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E94" s="17" t="n">
-        <v>0</v>
+        <v>1.64</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1924100</v>
+        <v>2011700</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.65</v>
+        <v>0.32</v>
       </c>
       <c r="H94" t="n">
-        <v>39.82</v>
+        <v>33.89</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -4700,10 +4711,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.58</v>
+        <v>1.724</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.645</v>
+        <v>1.839</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4716,28 +4727,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0191</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CABNET</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.26</v>
+        <v>3</v>
       </c>
       <c r="E95" s="15" t="n">
-        <v>0.1064</v>
+        <v>0.0345</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1923800</v>
+        <v>1972500</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>11.94</v>
+        <v>0.58</v>
       </c>
       <c r="H95" t="n">
-        <v>69.84999999999999</v>
+        <v>57.26</v>
       </c>
       <c r="I95" s="16" t="inlineStr">
         <is>
@@ -4745,11 +4756,9 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="K95" s="9" t="n">
-        <v>0.216</v>
-      </c>
+        <v>2.874</v>
+      </c>
+      <c r="K95" s="9" t="n"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
     </row>
@@ -4761,40 +4770,31 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>BPROP</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>-0.0106</v>
+        <v>0.245</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1905600</v>
-      </c>
-      <c r="G96" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H96" t="n">
-        <v>52.58</v>
-      </c>
-      <c r="I96" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J96" s="9" t="n">
-        <v>0.464</v>
-      </c>
-      <c r="K96" s="9" t="n">
-        <v>0.462</v>
-      </c>
+        <v>1940500</v>
+      </c>
+      <c r="G96" s="12" t="n"/>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="n"/>
+      <c r="K96" s="9" t="n"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
     </row>
@@ -4806,39 +4806,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0191</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>CABNET</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>-0.012</v>
+        <v>0.26</v>
+      </c>
+      <c r="E97" s="15" t="n">
+        <v>0.1064</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1897800</v>
+        <v>1933800</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.3</v>
+        <v>12</v>
       </c>
       <c r="H97" t="n">
-        <v>33.89</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.84999999999999</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>1.724</v>
+        <v>0.221</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1.839</v>
+        <v>0.216</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4866,10 +4866,10 @@
         <v>-0.0139</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1859700</v>
+        <v>1909400</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H98" t="n">
         <v>62.3</v>
@@ -4896,39 +4896,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0032</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>REDTONE</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.345</v>
+        <v>0.465</v>
       </c>
       <c r="E99" s="10" t="n">
-        <v>-0.0417</v>
+        <v>-0.0106</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1744500</v>
+        <v>1907900</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H99" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.58</v>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.353</v>
+        <v>0.464</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.32</v>
+        <v>0.462</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4941,39 +4941,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v>0.0486</v>
+        <v>0.235</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1744300</v>
+        <v>1828300</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.52</v>
+        <v>1.11</v>
       </c>
       <c r="H100" t="n">
-        <v>67.68000000000001</v>
-      </c>
-      <c r="I100" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.3</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.712</v>
+        <v>0.24</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.713</v>
+        <v>0.244</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4995,19 +4995,19 @@
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>6.19</v>
+        <v>6.21</v>
       </c>
       <c r="E101" s="15" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0114</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1728700</v>
+        <v>1824900</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H101" t="n">
-        <v>40.64</v>
+        <v>42.18</v>
       </c>
       <c r="I101" s="16" t="inlineStr">
         <is>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>6.29</v>
+        <v>6.292</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>6.483</v>
+        <v>6.484</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5031,39 +5031,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0342</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>RTECH</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>-0.0158</v>
+        <v>0.25</v>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1670400</v>
+        <v>1792900</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.38</v>
+        <v>2.2</v>
       </c>
       <c r="H102" t="n">
-        <v>34.96</v>
-      </c>
-      <c r="I102" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67</v>
+      </c>
+      <c r="I102" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>1.949</v>
+        <v>0.231</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>2.072</v>
+        <v>0.215</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5076,39 +5076,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>1.13</v>
+        <v>1.87</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>-0.0259</v>
+        <v>-0.0158</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1650400</v>
+        <v>1776200</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="H103" t="n">
-        <v>47.24</v>
-      </c>
-      <c r="I103" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.96</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>1.16</v>
+        <v>1.949</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>1.102</v>
+        <v>2.072</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5121,28 +5121,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.75</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1634300</v>
+        <v>1749300</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="H104" t="n">
-        <v>46.45</v>
+        <v>66.39</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.712</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.594</v>
+        <v>0.713</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5166,39 +5166,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>0032</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SENDAI</t>
+          <t>REDTONE</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E105" s="17" t="n">
-        <v>0</v>
+        <v>0.345</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>-0.0417</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1626500</v>
+        <v>1744700</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>59.56</v>
-      </c>
-      <c r="I105" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.4</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.259</v>
+        <v>0.353</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.268</v>
+        <v>0.32</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5211,28 +5211,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.425</v>
+        <v>1.13</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>-0.0116</v>
+        <v>-0.0259</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1625400</v>
+        <v>1704200</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>1.53</v>
+        <v>0.19</v>
       </c>
       <c r="H106" t="n">
-        <v>41.37</v>
+        <v>47.24</v>
       </c>
       <c r="I106" s="16" t="inlineStr">
         <is>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.431</v>
+        <v>1.16</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.452</v>
+        <v>1.102</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5256,28 +5256,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>5.55</v>
+        <v>0.615</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>-0.0107</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1610500</v>
+        <v>1668600</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.53</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H107" t="n">
-        <v>43.8</v>
+        <v>40.73</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>5.77</v>
+        <v>0.635</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>5.767</v>
+        <v>0.634</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5301,28 +5301,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>4.4</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>-0.004500000000000001</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1601500</v>
+        <v>1657700</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.13</v>
+        <v>0.46</v>
       </c>
       <c r="H108" t="n">
-        <v>78.70999999999999</v>
+        <v>46.45</v>
       </c>
       <c r="I108" s="16" t="inlineStr">
         <is>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>3.608</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2.415</v>
+        <v>0.594</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5346,28 +5346,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <v>0</v>
+        <v>4.37</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>-0.0113</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1571200</v>
+        <v>1639400</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="H109" t="n">
-        <v>39.08</v>
+        <v>77.55</v>
       </c>
       <c r="I109" s="16" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.297</v>
+        <v>3.605</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.311</v>
+        <v>2.415</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5391,28 +5391,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.61</v>
+        <v>5.56</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>-0.0161</v>
+        <v>-0.0089</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1569800</v>
+        <v>1632300</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.65</v>
+        <v>0.54</v>
       </c>
       <c r="H110" t="n">
-        <v>39.14</v>
+        <v>44.04</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -5420,10 +5420,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.635</v>
+        <v>5.771</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.634</v>
+        <v>5.767</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5436,39 +5436,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SENDAI</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E111" s="10" t="n">
-        <v>-0.0101</v>
+        <v>0.275</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1554000</v>
+        <v>1626500</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.35</v>
+        <v>0.95</v>
       </c>
       <c r="H111" t="n">
-        <v>32.17</v>
-      </c>
-      <c r="I111" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.56</v>
+      </c>
+      <c r="I111" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.043</v>
+        <v>0.259</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.074</v>
+        <v>0.268</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5481,28 +5481,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AXREIT</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E112" s="17" t="n">
-        <v>0</v>
+        <v>0.425</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>-0.0116</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1516500</v>
+        <v>1625400</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>1.12</v>
+        <v>1.53</v>
       </c>
       <c r="H112" t="n">
-        <v>46.97</v>
+        <v>41.37</v>
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>1.811</v>
+        <v>0.431</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>1.845</v>
+        <v>0.452</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5526,28 +5526,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>-0.0226</v>
+        <v>0.415</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1508100</v>
+        <v>1611300</v>
       </c>
       <c r="G113" s="12" t="n">
         <v>0.28</v>
       </c>
       <c r="H113" t="n">
-        <v>44.47</v>
+        <v>54.69</v>
       </c>
       <c r="I113" s="16" t="inlineStr">
         <is>
@@ -5555,10 +5555,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>1.768</v>
+        <v>0.403</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>1.803</v>
+        <v>0.402</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5571,33 +5571,40 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0470</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>BFIELD</t>
+          <t>GREENTEC</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E114" s="17" t="n">
-        <v>0</v>
+        <v>0.205</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>0.0513</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1491800</v>
+        <v>1603000</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.08</v>
+        <v>42.85</v>
+      </c>
+      <c r="H114" t="n">
+        <v>75.98999999999999</v>
       </c>
       <c r="I114" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J114" s="9" t="n"/>
-      <c r="K114" s="9" t="n"/>
+      <c r="J114" s="9" t="n">
+        <v>0.193</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>0.191</v>
+      </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
     </row>
@@ -5609,39 +5616,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>1601300</v>
+      </c>
+      <c r="G115" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="E115" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" s="11" t="n">
-        <v>1487700</v>
-      </c>
-      <c r="G115" s="12" t="n">
-        <v>1.47</v>
-      </c>
       <c r="H115" t="n">
-        <v>37.51</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.37</v>
+      </c>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.205</v>
+        <v>0.908</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.214</v>
+        <v>0.767</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5654,39 +5661,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="E116" s="15" t="n">
-        <v>0.047</v>
+        <v>0.985</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>-0.0101</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1468800</v>
+        <v>1587800</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.59</v>
+        <v>0.36</v>
       </c>
       <c r="H116" t="n">
-        <v>73.01000000000001</v>
-      </c>
-      <c r="I116" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.17</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>2.972</v>
+        <v>1.043</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>2.548</v>
+        <v>1.074</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5699,39 +5706,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>AXREIT</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>-0.0213</v>
+        <v>1.8</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1442300</v>
+        <v>1520000</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.88</v>
+        <v>1.12</v>
       </c>
       <c r="H117" t="n">
-        <v>41.61</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.97</v>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.24</v>
+        <v>1.811</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.244</v>
+        <v>1.845</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5744,39 +5751,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v>0.0058</v>
+        <v>1.73</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>-0.0226</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1405500</v>
+        <v>1512600</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.46</v>
+        <v>0.28</v>
       </c>
       <c r="H118" t="n">
-        <v>63.83</v>
-      </c>
-      <c r="I118" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.47</v>
+      </c>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.86</v>
+        <v>1.768</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.856</v>
+        <v>1.803</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5789,39 +5796,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E119" s="15" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.2</v>
+      </c>
+      <c r="E119" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1397300</v>
+        <v>1492700</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.53</v>
+        <v>1.48</v>
       </c>
       <c r="H119" t="n">
-        <v>84.36</v>
-      </c>
-      <c r="I119" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.51</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.067</v>
+        <v>0.205</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.9</v>
+        <v>0.214</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5834,40 +5841,33 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0470</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>BFIELD</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>9.94</v>
-      </c>
-      <c r="E120" s="15" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.48</v>
+      </c>
+      <c r="E120" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1378600</v>
+        <v>1491800</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="H120" t="n">
-        <v>65.47</v>
+        <v>0.08</v>
       </c>
       <c r="I120" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J120" s="9" t="n">
-        <v>9.571999999999999</v>
-      </c>
-      <c r="K120" s="9" t="n">
-        <v>9.106999999999999</v>
-      </c>
+      <c r="J120" s="9" t="n"/>
+      <c r="K120" s="9" t="n"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
     </row>
@@ -5894,10 +5894,10 @@
         <v>0.0407</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1353500</v>
+        <v>1476100</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="H121" t="n">
         <v>75.47</v>
@@ -5924,39 +5924,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E122" s="17" t="n">
-        <v>0</v>
+        <v>3.34</v>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v>0.047</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1348400</v>
+        <v>1470800</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>1.73</v>
+        <v>0.6</v>
       </c>
       <c r="H122" t="n">
-        <v>45.51</v>
-      </c>
-      <c r="I122" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.01000000000001</v>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.261</v>
+        <v>2.972</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.266</v>
+        <v>2.548</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5969,28 +5969,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>1.05</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E123" s="15" t="n">
-        <v>0.0194</v>
+        <v>0.0091</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1294600</v>
+        <v>1428800</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.16</v>
+        <v>0.45</v>
       </c>
       <c r="H123" t="n">
-        <v>76.75</v>
+        <v>65.67</v>
       </c>
       <c r="I123" s="16" t="inlineStr">
         <is>
@@ -5998,10 +5998,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.907</v>
+        <v>9.573</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.767</v>
+        <v>9.106999999999999</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6014,28 +6014,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>-0.0241</v>
+        <v>1.27</v>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1286200</v>
+        <v>1414800</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.23</v>
+        <v>0.54</v>
       </c>
       <c r="H124" t="n">
-        <v>51.65</v>
+        <v>84.36</v>
       </c>
       <c r="I124" s="16" t="inlineStr">
         <is>
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.402</v>
+        <v>1.067</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.401</v>
+        <v>0.9</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6059,39 +6059,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E125" s="17" t="n">
-        <v>0</v>
+        <v>1.81</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>0.0169</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1270200</v>
+        <v>1409900</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H125" t="n">
-        <v>43.62</v>
-      </c>
-      <c r="I125" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.45</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.437</v>
+        <v>1.892</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.434</v>
+        <v>1.962</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6104,28 +6104,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E126" s="10" t="n">
-        <v>-0.013</v>
+        <v>0.87</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1260200</v>
+        <v>1405500</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>1.07</v>
+        <v>0.46</v>
       </c>
       <c r="H126" t="n">
-        <v>45.52</v>
+        <v>63.83</v>
       </c>
       <c r="I126" s="13" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.386</v>
+        <v>0.86</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.393</v>
+        <v>0.856</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6149,28 +6149,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0192</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>INTA</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>-0.0118</v>
+        <v>0.425</v>
+      </c>
+      <c r="E127" s="15" t="n">
+        <v>0.0119</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1181100</v>
+        <v>1400800</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.54</v>
+        <v>0.44</v>
       </c>
       <c r="H127" t="n">
-        <v>65.7</v>
+        <v>45.57</v>
       </c>
       <c r="I127" s="16" t="inlineStr">
         <is>
@@ -6178,10 +6178,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.396</v>
+        <v>0.437</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.381</v>
+        <v>0.434</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6194,28 +6194,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>-0.019</v>
+        <v>0.26</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1178100</v>
+        <v>1348400</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.11</v>
+        <v>1.73</v>
       </c>
       <c r="H128" t="n">
-        <v>44.58</v>
+        <v>45.51</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.076</v>
+        <v>0.261</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.024</v>
+        <v>0.266</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6239,40 +6239,36 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E129" s="15" t="n">
-        <v>0.0149</v>
+        <v>0.28</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1166600</v>
+        <v>1284300</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="H129" t="n">
-        <v>82.23999999999999</v>
+        <v>16.86</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J129" s="9" t="n">
-        <v>2.486</v>
-      </c>
-      <c r="K129" s="9" t="n">
-        <v>2.14</v>
-      </c>
+      <c r="J129" s="9" t="n"/>
+      <c r="K129" s="9" t="n"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
     </row>
@@ -6284,39 +6280,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>4.33</v>
+        <v>0.38</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>-0.0356</v>
+        <v>-0.013</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1147500</v>
+        <v>1260200</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.49</v>
+        <v>1.07</v>
       </c>
       <c r="H130" t="n">
-        <v>47.65</v>
-      </c>
-      <c r="I130" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.52</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>4.402</v>
+        <v>0.386</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>4.427</v>
+        <v>0.393</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6329,39 +6325,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E131" s="15" t="n">
-        <v>0.0092</v>
+        <v>1.03</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>-0.019</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1145500</v>
+        <v>1245600</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.24</v>
+        <v>0.11</v>
       </c>
       <c r="H131" t="n">
-        <v>77.52</v>
-      </c>
-      <c r="I131" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.58</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.985</v>
+        <v>1.076</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.8110000000000001</v>
+        <v>1.024</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6374,28 +6370,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>0192</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>INTA</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="E132" s="15" t="n">
-        <v>0.0083</v>
+        <v>0.42</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1145400</v>
+        <v>1243000</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.35</v>
+        <v>0.57</v>
       </c>
       <c r="H132" t="n">
-        <v>75.63</v>
+        <v>65.7</v>
       </c>
       <c r="I132" s="16" t="inlineStr">
         <is>
@@ -6403,10 +6399,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>3.343</v>
+        <v>0.396</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>2.91</v>
+        <v>0.381</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6419,39 +6415,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.57</v>
+        <v>4.35</v>
       </c>
       <c r="E133" s="10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0312</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1143600</v>
+        <v>1227500</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.3</v>
+        <v>0.52</v>
       </c>
       <c r="H133" t="n">
-        <v>36.42</v>
-      </c>
-      <c r="I133" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.29</v>
+      </c>
+      <c r="I133" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.585</v>
+        <v>4.404</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.587</v>
+        <v>4.427</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6464,39 +6460,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0342</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>RTECH</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E134" s="15" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>1173500</v>
+      </c>
+      <c r="G134" s="12" t="n">
         <v>0.25</v>
       </c>
-      <c r="E134" s="15" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="F134" s="11" t="n">
-        <v>1136900</v>
-      </c>
-      <c r="G134" s="12" t="n">
-        <v>1.39</v>
-      </c>
       <c r="H134" t="n">
-        <v>67</v>
-      </c>
-      <c r="I134" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>82.23999999999999</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.231</v>
+        <v>2.486</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.215</v>
+        <v>2.14</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6509,39 +6505,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>8524</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TALIWRK</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>-0.0192</v>
+        <v>0.575</v>
+      </c>
+      <c r="E135" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1126300</v>
+        <v>1166300</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="H135" t="n">
-        <v>48.39</v>
-      </c>
-      <c r="I135" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.59</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.254</v>
+        <v>0.586</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.27</v>
+        <v>0.587</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6554,39 +6550,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>-0.0133</v>
+        <v>3.64</v>
+      </c>
+      <c r="E136" s="15" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1105600</v>
+        <v>1163600</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.15</v>
+        <v>0.36</v>
       </c>
       <c r="H136" t="n">
-        <v>52.06</v>
-      </c>
-      <c r="I136" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.63</v>
+      </c>
+      <c r="I136" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>2.227</v>
+        <v>3.343</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>2.108</v>
+        <v>2.91</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6599,39 +6595,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E137" s="17" t="n">
-        <v>0</v>
+        <v>2.22</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>-0.0177</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1086000</v>
+        <v>1152200</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.42</v>
+        <v>0.15</v>
       </c>
       <c r="H137" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="I137" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.31</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>2.061</v>
+        <v>2.226</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>2.104</v>
+        <v>2.108</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6644,28 +6640,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>-0.0066</v>
+        <v>1.1</v>
+      </c>
+      <c r="E138" s="15" t="n">
+        <v>0.0092</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1070300</v>
+        <v>1146000</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.47</v>
+        <v>0.24</v>
       </c>
       <c r="H138" t="n">
-        <v>31.69</v>
+        <v>77.52</v>
       </c>
       <c r="I138" s="16" t="inlineStr">
         <is>
@@ -6673,10 +6669,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>1.555</v>
+        <v>0.985</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>1.669</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6689,39 +6685,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>TALIWRK</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>-0.0075</v>
+        <v>0.26</v>
+      </c>
+      <c r="E139" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1051500</v>
+        <v>1130200</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
       <c r="H139" t="n">
-        <v>52.26</v>
-      </c>
-      <c r="I139" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.19</v>
+      </c>
+      <c r="I139" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>7.874</v>
+        <v>0.254</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>7.803</v>
+        <v>0.27</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6734,39 +6730,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0285</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>MERSEC</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E140" s="10" t="n">
-        <v>-0.0182</v>
+        <v>2.05</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>0.0049</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1049700</v>
+        <v>1122800</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>1.18</v>
+        <v>0.43</v>
       </c>
       <c r="H140" t="n">
-        <v>36.39</v>
-      </c>
-      <c r="I140" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.9</v>
+      </c>
+      <c r="I140" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.278</v>
+        <v>2.062</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.275</v>
+        <v>2.104</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6779,39 +6775,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>1.06</v>
+        <v>1.5</v>
       </c>
       <c r="E141" s="10" t="n">
-        <v>-0.009300000000000001</v>
+        <v>-0.0066</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>989800</v>
+        <v>1078800</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="H141" t="n">
-        <v>31.18</v>
-      </c>
-      <c r="I141" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>31.69</v>
+      </c>
+      <c r="I141" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>1.11</v>
+        <v>1.555</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>1.148</v>
+        <v>1.669</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6824,28 +6820,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>1.67</v>
+        <v>7.9</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>-0.0234</v>
+        <v>-0.0063</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>971400</v>
+        <v>1056800</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.62</v>
+        <v>0.29</v>
       </c>
       <c r="H142" t="n">
-        <v>36.85</v>
+        <v>52.9</v>
       </c>
       <c r="I142" s="13" t="inlineStr">
         <is>
@@ -6853,10 +6849,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>1.749</v>
+        <v>7.875</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>1.853</v>
+        <v>7.803</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6869,39 +6865,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0285</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>MERSEC</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.63</v>
+        <v>0.27</v>
       </c>
       <c r="E143" s="10" t="n">
-        <v>-0.0156</v>
+        <v>-0.0182</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>950400</v>
+        <v>1049700</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.25</v>
+        <v>1.18</v>
       </c>
       <c r="H143" t="n">
-        <v>54.69</v>
-      </c>
-      <c r="I143" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.39</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.62</v>
+        <v>0.278</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.583</v>
+        <v>0.275</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6914,12 +6910,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
@@ -6929,13 +6925,13 @@
         <v>-0.0156</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>933100</v>
+        <v>1026400</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.71</v>
+        <v>0.27</v>
       </c>
       <c r="H144" t="n">
-        <v>46.62</v>
+        <v>54.69</v>
       </c>
       <c r="I144" s="16" t="inlineStr">
         <is>
@@ -6943,10 +6939,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>0.634</v>
+        <v>0.62</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>0.629</v>
+        <v>0.583</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6959,28 +6955,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E145" s="15" t="n">
-        <v>0.0225</v>
+        <v>1.07</v>
+      </c>
+      <c r="E145" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>930600</v>
+        <v>1015900</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.13</v>
+        <v>0.48</v>
       </c>
       <c r="H145" t="n">
-        <v>39.82</v>
+        <v>33.09</v>
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
@@ -6988,10 +6984,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>1.892</v>
+        <v>1.111</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>1.962</v>
+        <v>1.149</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7004,39 +7000,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PADINI</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E146" s="17" t="n">
-        <v>0</v>
+        <v>0.605</v>
+      </c>
+      <c r="E146" s="15" t="n">
+        <v>0.0254</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>924800</v>
+        <v>1012100</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="H146" t="n">
-        <v>31.36</v>
-      </c>
-      <c r="I146" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.48</v>
+      </c>
+      <c r="I146" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>1.082</v>
+        <v>0.594</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>1.26</v>
+        <v>0.609</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7049,28 +7045,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>TEKSENG</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E147" s="15" t="n">
-        <v>0.0066</v>
+        <v>0.275</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>-0.0517</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>916400</v>
+        <v>1004100</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.36</v>
+        <v>1.49</v>
       </c>
       <c r="H147" t="n">
-        <v>53.02</v>
+        <v>59.37</v>
       </c>
       <c r="I147" s="16" t="inlineStr">
         <is>
@@ -7078,10 +7074,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>0.756</v>
+        <v>0.261</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>0.74</v>
+        <v>0.242</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7094,39 +7090,39 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>QL</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>4.01</v>
+        <v>1.68</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>-0.0074</v>
+        <v>-0.0175</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>909500</v>
+        <v>972900</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.51</v>
+        <v>0.62</v>
       </c>
       <c r="H148" t="n">
-        <v>55.78</v>
-      </c>
-      <c r="I148" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.8</v>
+      </c>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>3.943</v>
+        <v>1.75</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>3.933</v>
+        <v>1.854</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7139,28 +7135,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>0.76</v>
+        <v>0.63</v>
       </c>
       <c r="E149" s="10" t="n">
-        <v>-0.0194</v>
+        <v>-0.0156</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>908900</v>
+        <v>933100</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="H149" t="n">
-        <v>49.12</v>
+        <v>46.62</v>
       </c>
       <c r="I149" s="16" t="inlineStr">
         <is>
@@ -7168,10 +7164,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>0.765</v>
+        <v>0.634</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>0.755</v>
+        <v>0.629</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7184,28 +7180,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>1.28</v>
+        <v>6.79</v>
       </c>
       <c r="E150" s="15" t="n">
-        <v>0.0159</v>
+        <v>0.0044</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>881800</v>
+        <v>929800</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.58</v>
+        <v>0.28</v>
       </c>
       <c r="H150" t="n">
-        <v>47.78</v>
+        <v>55.81</v>
       </c>
       <c r="I150" s="16" t="inlineStr">
         <is>
@@ -7213,10 +7209,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>1.28</v>
+        <v>6.597</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>1.34</v>
+        <v>6.516</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7229,28 +7225,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>6.79</v>
+        <v>2.67</v>
       </c>
       <c r="E151" s="15" t="n">
-        <v>0.0044</v>
+        <v>0.023</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>880500</v>
+        <v>929000</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.27</v>
+        <v>0.11</v>
       </c>
       <c r="H151" t="n">
-        <v>55.81</v>
+        <v>46.42</v>
       </c>
       <c r="I151" s="16" t="inlineStr">
         <is>
@@ -7258,10 +7254,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>6.597</v>
+        <v>2.672</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>6.516</v>
+        <v>2.862</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7274,39 +7270,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>PADINI</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E152" s="15" t="n">
-        <v>0.011</v>
+        <v>1.02</v>
+      </c>
+      <c r="E152" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>858800</v>
+        <v>926800</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.48</v>
+        <v>0.4</v>
       </c>
       <c r="H152" t="n">
-        <v>55.03</v>
-      </c>
-      <c r="I152" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.36</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.907</v>
+        <v>1.082</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.789</v>
+        <v>1.26</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7319,28 +7315,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>QL</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>1.15</v>
+        <v>4.02</v>
       </c>
       <c r="E153" s="10" t="n">
-        <v>-0.0171</v>
+        <v>-0.005</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>855700</v>
+        <v>923900</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="H153" t="n">
-        <v>60.43</v>
+        <v>56.56</v>
       </c>
       <c r="I153" s="16" t="inlineStr">
         <is>
@@ -7348,10 +7344,10 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>1.111</v>
+        <v>3.944</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>1.014</v>
+        <v>3.933</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7364,28 +7360,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E154" s="10" t="n">
-        <v>-0.0092</v>
+        <v>0.765</v>
+      </c>
+      <c r="E154" s="15" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>854700</v>
+        <v>918400</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="H154" t="n">
-        <v>61.03</v>
+        <v>53.02</v>
       </c>
       <c r="I154" s="16" t="inlineStr">
         <is>
@@ -7393,10 +7389,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>0.502</v>
+        <v>0.756</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>0.407</v>
+        <v>0.74</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7409,28 +7405,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="E155" s="15" t="n">
-        <v>0.023</v>
+        <v>0.76</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>-0.0194</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>816400</v>
+        <v>908900</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.1</v>
+        <v>0.63</v>
       </c>
       <c r="H155" t="n">
-        <v>46.42</v>
+        <v>49.12</v>
       </c>
       <c r="I155" s="16" t="inlineStr">
         <is>
@@ -7438,10 +7434,10 @@
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>2.672</v>
+        <v>0.765</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>2.862</v>
+        <v>0.755</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7454,39 +7450,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>WTK</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>0.95</v>
+        <v>1.28</v>
       </c>
       <c r="E156" s="15" t="n">
-        <v>0.0106</v>
+        <v>0.0159</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>811800</v>
+        <v>892800</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.35</v>
+        <v>0.58</v>
       </c>
       <c r="H156" t="n">
-        <v>35.85</v>
-      </c>
-      <c r="I156" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.78</v>
+      </c>
+      <c r="I156" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>1.034</v>
+        <v>1.28</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>1.017</v>
+        <v>1.34</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7499,39 +7495,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>2.94</v>
+        <v>0.915</v>
       </c>
       <c r="E157" s="15" t="n">
-        <v>0.0034</v>
+        <v>0.011</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>811400</v>
+        <v>866200</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.27</v>
+        <v>0.49</v>
       </c>
       <c r="H157" t="n">
-        <v>43.79</v>
-      </c>
-      <c r="I157" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.03</v>
+      </c>
+      <c r="I157" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>2.999</v>
+        <v>0.907</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>3.04</v>
+        <v>0.789</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7544,39 +7540,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0271</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E158" s="17" t="n">
-        <v>0</v>
+        <v>1.14</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>800000</v>
+        <v>858700</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.83</v>
+        <v>0.24</v>
       </c>
       <c r="H158" t="n">
-        <v>48.02</v>
-      </c>
-      <c r="I158" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.55</v>
+      </c>
+      <c r="I158" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>0.631</v>
+        <v>1.11</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>0.637</v>
+        <v>1.014</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7589,28 +7585,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E159" s="15" t="n">
-        <v>0.0072</v>
+        <v>0.54</v>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>-0.0092</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>787100</v>
+        <v>855900</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="H159" t="n">
-        <v>70.84</v>
+        <v>61.03</v>
       </c>
       <c r="I159" s="16" t="inlineStr">
         <is>
@@ -7618,10 +7614,10 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>1.359</v>
+        <v>0.502</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>1.326</v>
+        <v>0.407</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7634,28 +7630,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>7.99</v>
-      </c>
-      <c r="E160" s="15" t="n">
-        <v>0.0044</v>
+        <v>0.835</v>
+      </c>
+      <c r="E160" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>781000</v>
+        <v>837400</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="H160" t="n">
-        <v>52.87</v>
+        <v>62.68</v>
       </c>
       <c r="I160" s="16" t="inlineStr">
         <is>
@@ -7663,10 +7659,10 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>7.904</v>
+        <v>0.804</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>8.087</v>
+        <v>0.725</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7679,39 +7675,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E161" s="10" t="n">
-        <v>-0.006</v>
+        <v>2.94</v>
+      </c>
+      <c r="E161" s="15" t="n">
+        <v>0.0034</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>758000</v>
+        <v>826900</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="H161" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="I161" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.79</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>0.804</v>
+        <v>2.999</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>0.725</v>
+        <v>3.04</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7724,39 +7720,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>WTK</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>-0.0044</v>
+        <v>0.95</v>
+      </c>
+      <c r="E162" s="15" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>738300</v>
+        <v>812500</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.16</v>
+        <v>0.35</v>
       </c>
       <c r="H162" t="n">
-        <v>33.09</v>
-      </c>
-      <c r="I162" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.85</v>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>4.702</v>
+        <v>1.034</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>4.978</v>
+        <v>1.017</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7769,39 +7765,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="E163" s="10" t="n">
-        <v>-0.009000000000000001</v>
+        <v>7.96</v>
+      </c>
+      <c r="E163" s="15" t="n">
+        <v>0.0005999999999999999</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>724700</v>
+        <v>807700</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="H163" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="I163" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.38</v>
+      </c>
+      <c r="I163" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>4.564</v>
+        <v>7.901</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>4.532</v>
+        <v>8.086</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7814,28 +7810,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>AFFIN</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>2.02</v>
+        <v>4.51</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>-0.0098</v>
+        <v>-0.0066</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>707300</v>
+        <v>800200</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>1.07</v>
+        <v>0.17</v>
       </c>
       <c r="H164" t="n">
-        <v>38.31</v>
+        <v>32.67</v>
       </c>
       <c r="I164" s="16" t="inlineStr">
         <is>
@@ -7843,10 +7839,10 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>2.042</v>
+        <v>4.701</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>2.117</v>
+        <v>4.978</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7859,39 +7855,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0271</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E165" s="10" t="n">
-        <v>-0.0135</v>
+        <v>0.63</v>
+      </c>
+      <c r="E165" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>705200</v>
+        <v>800000</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.28</v>
+        <v>0.83</v>
       </c>
       <c r="H165" t="n">
-        <v>44.31</v>
-      </c>
-      <c r="I165" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.02</v>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>1.476</v>
+        <v>0.631</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>1.526</v>
+        <v>0.637</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7904,39 +7900,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="E166" s="10" t="n">
-        <v>-0.0076</v>
+        <v>1.4</v>
+      </c>
+      <c r="E166" s="15" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>697900</v>
+        <v>787100</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.16</v>
+        <v>0.42</v>
       </c>
       <c r="H166" t="n">
-        <v>32.59</v>
-      </c>
-      <c r="I166" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.84</v>
+      </c>
+      <c r="I166" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>6.712</v>
+        <v>1.359</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>6.877</v>
+        <v>1.326</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7949,28 +7945,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>2.11</v>
+        <v>0.57</v>
       </c>
       <c r="E167" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>695400</v>
+        <v>771400</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="H167" t="n">
-        <v>57.6</v>
+        <v>50.34</v>
       </c>
       <c r="I167" s="16" t="inlineStr">
         <is>
@@ -7978,10 +7974,10 @@
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>2.059</v>
+        <v>0.569</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>1.997</v>
+        <v>0.575</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -7994,28 +7990,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>0.505</v>
+        <v>4.39</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>-0.0194</v>
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>681400</v>
+        <v>729100</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="H168" t="n">
-        <v>50.72</v>
+        <v>44.1</v>
       </c>
       <c r="I168" s="13" t="inlineStr">
         <is>
@@ -8023,10 +8019,10 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>0.511</v>
+        <v>4.564</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>0.467</v>
+        <v>4.532</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8039,28 +8035,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>AFFIN</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>2.02</v>
       </c>
       <c r="E169" s="10" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0098</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>680900</v>
+        <v>713400</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.23</v>
+        <v>1.08</v>
       </c>
       <c r="H169" t="n">
-        <v>49.04</v>
+        <v>38.31</v>
       </c>
       <c r="I169" s="16" t="inlineStr">
         <is>
@@ -8068,10 +8064,10 @@
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>2.042</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>0.575</v>
+        <v>2.117</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8084,39 +8080,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="E170" s="15" t="n">
-        <v>0.0076</v>
+        <v>6.55</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>677800</v>
+        <v>706200</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="H170" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="I170" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.59</v>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>3.77</v>
+        <v>6.712</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>3.419</v>
+        <v>6.877</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8129,28 +8125,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E171" s="15" t="n">
-        <v>0.0169</v>
+        <v>1.46</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>669000</v>
+        <v>705200</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H171" t="n">
-        <v>50.92</v>
+        <v>44.31</v>
       </c>
       <c r="I171" s="16" t="inlineStr">
         <is>
@@ -8158,10 +8154,10 @@
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>0.594</v>
+        <v>1.476</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>0.609</v>
+        <v>1.526</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8174,39 +8170,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="E172" s="10" t="n">
-        <v>-0.01</v>
+        <v>2.12</v>
+      </c>
+      <c r="E172" s="15" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>659700</v>
+        <v>702100</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.57</v>
+        <v>0.23</v>
       </c>
       <c r="H172" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="I172" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.55</v>
+      </c>
+      <c r="I172" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>3.061</v>
+        <v>2.06</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>3.147</v>
+        <v>1.997</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8219,28 +8215,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="E173" s="17" t="n">
-        <v>0</v>
+        <v>2.96</v>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>-0.01</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>641200</v>
+        <v>693700</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.26</v>
+        <v>0.6</v>
       </c>
       <c r="H173" t="n">
-        <v>47.73</v>
+        <v>31.76</v>
       </c>
       <c r="I173" s="13" t="inlineStr">
         <is>
@@ -8248,10 +8244,10 @@
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>5.271</v>
+        <v>3.061</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>5.281</v>
+        <v>3.147</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8264,39 +8260,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="E174" s="10" t="n">
-        <v>-0.0186</v>
+        <v>4</v>
+      </c>
+      <c r="E174" s="15" t="n">
+        <v>0.0101</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>635800</v>
+        <v>689400</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>1.1</v>
+        <v>0.21</v>
       </c>
       <c r="H174" t="n">
-        <v>52.33</v>
-      </c>
-      <c r="I174" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.64</v>
+      </c>
+      <c r="I174" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>1.584</v>
+        <v>3.771</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>1.504</v>
+        <v>3.419</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8309,39 +8305,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E175" s="15" t="n">
-        <v>0.0179</v>
+        <v>0.51</v>
+      </c>
+      <c r="E175" s="10" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>633700</v>
+        <v>684400</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>1.17</v>
+        <v>0.18</v>
       </c>
       <c r="H175" t="n">
-        <v>77.31999999999999</v>
-      </c>
-      <c r="I175" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.23</v>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>0.515</v>
+        <v>0.512</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>0.496</v>
+        <v>0.467</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8354,28 +8350,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>6.73</v>
+        <v>0.92</v>
       </c>
       <c r="E176" s="10" t="n">
-        <v>-0.0015</v>
+        <v>-0.0054</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>633400</v>
+        <v>651300</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="H176" t="n">
-        <v>45.79</v>
+        <v>42.02</v>
       </c>
       <c r="I176" s="13" t="inlineStr">
         <is>
@@ -8383,10 +8379,10 @@
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>6.775</v>
+        <v>0.931</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>6.818</v>
+        <v>0.95</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8399,39 +8395,39 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>5258</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>BIMB</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>2.06</v>
+        <v>6.72</v>
       </c>
       <c r="E177" s="10" t="n">
-        <v>-0.0048</v>
+        <v>-0.003</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>627800</v>
+        <v>646900</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.57</v>
+        <v>0.15</v>
       </c>
       <c r="H177" t="n">
-        <v>39.91</v>
-      </c>
-      <c r="I177" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.02</v>
+      </c>
+      <c r="I177" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>2.08</v>
+        <v>6.775</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>2.109</v>
+        <v>6.818</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8444,28 +8440,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>0.92</v>
+        <v>0.715</v>
       </c>
       <c r="E178" s="10" t="n">
-        <v>-0.0054</v>
+        <v>-0.0069</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>621000</v>
+        <v>644100</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
       <c r="H178" t="n">
-        <v>42.02</v>
+        <v>38.97</v>
       </c>
       <c r="I178" s="13" t="inlineStr">
         <is>
@@ -8473,10 +8469,10 @@
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>0.931</v>
+        <v>0.734</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>0.95</v>
+        <v>0.752</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8489,39 +8485,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E179" s="15" t="n">
-        <v>0.008100000000000001</v>
+        <v>5.2</v>
+      </c>
+      <c r="E179" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>615500</v>
+        <v>642600</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.49</v>
+        <v>0.26</v>
       </c>
       <c r="H179" t="n">
-        <v>51.17</v>
-      </c>
-      <c r="I179" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.73</v>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>0.626</v>
+        <v>5.271</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>0.603</v>
+        <v>5.281</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8534,39 +8530,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ORKIM</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E180" s="10" t="n">
-        <v>-0.0125</v>
+        <v>0.57</v>
+      </c>
+      <c r="E180" s="15" t="n">
+        <v>0.0179</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>606700</v>
+        <v>637800</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>3.05</v>
+        <v>1.18</v>
       </c>
       <c r="H180" t="n">
-        <v>36.88</v>
-      </c>
-      <c r="I180" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>77.31999999999999</v>
+      </c>
+      <c r="I180" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>0.802</v>
+        <v>0.515</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>0.84</v>
+        <v>0.496</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8579,28 +8575,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>0.715</v>
+        <v>1.58</v>
       </c>
       <c r="E181" s="10" t="n">
-        <v>-0.0069</v>
+        <v>-0.0186</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>591800</v>
+        <v>635800</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>0.37</v>
+        <v>1.1</v>
       </c>
       <c r="H181" t="n">
-        <v>38.97</v>
+        <v>52.33</v>
       </c>
       <c r="I181" s="13" t="inlineStr">
         <is>
@@ -8608,10 +8604,10 @@
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>0.734</v>
+        <v>1.584</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>0.752</v>
+        <v>1.504</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8624,39 +8620,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>BIMB</t>
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>0.635</v>
+        <v>2.06</v>
       </c>
       <c r="E182" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0048</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>575700</v>
+        <v>628000</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="H182" t="n">
-        <v>57.11</v>
-      </c>
-      <c r="I182" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.91</v>
+      </c>
+      <c r="I182" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J182" s="9" t="n">
-        <v>0.634</v>
+        <v>2.08</v>
       </c>
       <c r="K182" s="9" t="n">
-        <v>0.594</v>
+        <v>2.109</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="14" t="inlineStr"/>
@@ -8669,39 +8665,39 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D183" s="9" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="E183" s="10" t="n">
-        <v>-0.0063</v>
+        <v>0.625</v>
+      </c>
+      <c r="E183" s="15" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>553200</v>
+        <v>615500</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>0.18</v>
+        <v>0.49</v>
       </c>
       <c r="H183" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="I183" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.17</v>
+      </c>
+      <c r="I183" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J183" s="9" t="n">
-        <v>3.288</v>
+        <v>0.626</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>3.477</v>
+        <v>0.603</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="14" t="inlineStr"/>
@@ -8714,39 +8710,39 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>SKYGATE</t>
+          <t>ORKIM</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E184" s="10" t="n">
+        <v>-0.0125</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>606700</v>
+      </c>
+      <c r="G184" s="12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H184" t="n">
+        <v>36.88</v>
+      </c>
+      <c r="I184" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J184" s="9" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="K184" s="9" t="n">
         <v>0.84</v>
-      </c>
-      <c r="E184" s="10" t="n">
-        <v>-0.0508</v>
-      </c>
-      <c r="F184" s="11" t="n">
-        <v>540000</v>
-      </c>
-      <c r="G184" s="12" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="H184" t="n">
-        <v>44.13</v>
-      </c>
-      <c r="I184" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J184" s="9" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K184" s="9" t="n">
-        <v>0.802</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
@@ -8759,28 +8755,28 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D185" s="9" t="n">
-        <v>1.81</v>
+        <v>3.18</v>
       </c>
       <c r="E185" s="10" t="n">
-        <v>-0.0109</v>
+        <v>-0.0063</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>533700</v>
+        <v>577200</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>0.45</v>
+        <v>0.19</v>
       </c>
       <c r="H185" t="n">
-        <v>32.92</v>
+        <v>33.3</v>
       </c>
       <c r="I185" s="13" t="inlineStr">
         <is>
@@ -8788,10 +8784,10 @@
         </is>
       </c>
       <c r="J185" s="9" t="n">
-        <v>1.899</v>
+        <v>3.288</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>1.959</v>
+        <v>3.477</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="14" t="inlineStr"/>
@@ -8804,28 +8800,28 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D186" s="9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E186" s="15" t="n">
-        <v>0.0221</v>
+        <v>0.635</v>
+      </c>
+      <c r="E186" s="10" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>529600</v>
+        <v>575700</v>
       </c>
       <c r="G186" s="12" t="n">
         <v>0.17</v>
       </c>
       <c r="H186" t="n">
-        <v>58.45</v>
+        <v>57.11</v>
       </c>
       <c r="I186" s="13" t="inlineStr">
         <is>
@@ -8833,10 +8829,10 @@
         </is>
       </c>
       <c r="J186" s="9" t="n">
-        <v>1.347</v>
+        <v>0.634</v>
       </c>
       <c r="K186" s="9" t="n">
-        <v>1.158</v>
+        <v>0.594</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="14" t="inlineStr"/>
@@ -8849,28 +8845,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>SKYGATE</t>
         </is>
       </c>
       <c r="D187" s="9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E187" s="15" t="n">
-        <v>0.0098</v>
+        <v>0.84</v>
+      </c>
+      <c r="E187" s="10" t="n">
+        <v>-0.0508</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>520900</v>
+        <v>551400</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="H187" t="n">
-        <v>50.78</v>
+        <v>44.13</v>
       </c>
       <c r="I187" s="13" t="inlineStr">
         <is>
@@ -8878,10 +8874,10 @@
         </is>
       </c>
       <c r="J187" s="9" t="n">
-        <v>1.03</v>
+        <v>0.88</v>
       </c>
       <c r="K187" s="9" t="n">
-        <v>1.008</v>
+        <v>0.802</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="14" t="inlineStr"/>
@@ -8894,28 +8890,28 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D188" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E188" s="17" t="n">
-        <v>0</v>
+        <v>1.82</v>
+      </c>
+      <c r="E188" s="10" t="n">
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>510100</v>
+        <v>545500</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>0.08</v>
+        <v>0.46</v>
       </c>
       <c r="H188" t="n">
-        <v>37.41</v>
+        <v>33.96</v>
       </c>
       <c r="I188" s="13" t="inlineStr">
         <is>
@@ -8923,10 +8919,10 @@
         </is>
       </c>
       <c r="J188" s="9" t="n">
-        <v>0.5590000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="K188" s="9" t="n">
-        <v>0.588</v>
+        <v>1.959</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="14" t="inlineStr"/>
@@ -8939,28 +8935,28 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D189" s="9" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E189" s="10" t="n">
-        <v>-0.0035</v>
+        <v>1.4</v>
+      </c>
+      <c r="E189" s="15" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>507800</v>
+        <v>542600</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>0.39</v>
+        <v>0.17</v>
       </c>
       <c r="H189" t="n">
-        <v>45.02</v>
+        <v>59.28</v>
       </c>
       <c r="I189" s="13" t="inlineStr">
         <is>
@@ -8968,16 +8964,196 @@
         </is>
       </c>
       <c r="J189" s="9" t="n">
-        <v>2.964</v>
+        <v>1.348</v>
       </c>
       <c r="K189" s="9" t="n">
-        <v>2.81</v>
+        <v>1.159</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="14" t="inlineStr"/>
     </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>TMK</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E190" s="10" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>527100</v>
+      </c>
+      <c r="G190" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H190" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="I190" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="9" t="n">
+        <v>2.963</v>
+      </c>
+      <c r="K190" s="9" t="n">
+        <v>2.809</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="14" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E191" s="15" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>520900</v>
+      </c>
+      <c r="G191" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H191" t="n">
+        <v>50.78</v>
+      </c>
+      <c r="I191" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J191" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K191" s="9" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="14" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>BMGREEN</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="E192" s="10" t="n">
+        <v>-0.0121</v>
+      </c>
+      <c r="F192" s="11" t="n">
+        <v>515800</v>
+      </c>
+      <c r="G192" s="12" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H192" t="n">
+        <v>46.72</v>
+      </c>
+      <c r="I192" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J192" s="9" t="n">
+        <v>1.647</v>
+      </c>
+      <c r="K192" s="9" t="n">
+        <v>1.719</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="14" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>UEMS</t>
+        </is>
+      </c>
+      <c r="D193" s="9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E193" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>510300</v>
+      </c>
+      <c r="G193" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H193" t="n">
+        <v>37.41</v>
+      </c>
+      <c r="I193" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J193" s="9" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="K193" s="9" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M189"/>
+  <autoFilter ref="A1:M193"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>